--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G11">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G12">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G22">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G40">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G42">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G43">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="G49">

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU49"/>
+  <dimension ref="A1:AU51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -593,22 +593,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G2">
@@ -756,7 +756,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G3">
@@ -914,12 +914,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Shahr-e Babak</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G4">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-09-03 12:30:00</t>
+          <t>2026-09-03 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Mes Shahr-e Babak</t>
         </is>
       </c>
       <c r="G5">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-09-03 12:55:00</t>
+          <t>2026-09-03 12:30:00</t>
         </is>
       </c>
     </row>
@@ -1240,27 +1240,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G6">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-09-03 13:00:00</t>
+          <t>2026-09-03 12:55:00</t>
         </is>
       </c>
     </row>
@@ -1408,22 +1408,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G7">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G8">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-09-03 13:15:00</t>
+          <t>2026-09-03 13:00:00</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-09-03 13:30:00</t>
+          <t>2026-09-03 13:15:00</t>
         </is>
       </c>
     </row>
@@ -1892,27 +1892,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK10">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-09-03 14:00:00</t>
+          <t>2026-09-03 13:30:00</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G11">
@@ -2223,22 +2223,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G13">
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G14">
@@ -2587,68 +2587,68 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N14">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X14">
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK14">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-09-03 14:30:00</t>
+          <t>2026-09-03 14:00:00</t>
         </is>
       </c>
     </row>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G15">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-09-03 14:30:00</t>
+          <t>2026-09-03 14:00:00</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G16">
@@ -2913,68 +2913,68 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X16">
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-09-03 15:00:00</t>
+          <t>2026-09-03 14:30:00</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G17">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-09-03 15:00:00</t>
+          <t>2026-09-03 14:30:00</t>
         </is>
       </c>
     </row>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G18">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-09-03 15:30:00</t>
+          <t>2026-09-03 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G19">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-09-03 15:30:00</t>
+          <t>2026-09-03 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G20">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G21">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G22">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G23">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-09-03 15:45:00</t>
+          <t>2026-09-03 15:30:00</t>
         </is>
       </c>
     </row>
@@ -4174,12 +4174,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G24">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-09-03 15:45:00</t>
+          <t>2026-09-03 15:30:00</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G25">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G26">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-09-03 16:00:00</t>
+          <t>2026-09-03 15:45:00</t>
         </is>
       </c>
     </row>
@@ -4663,27 +4663,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G27">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2026-09-03 16:00:00</t>
+          <t>2026-09-03 15:45:00</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="G28">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G29">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-09-03 18:30:00</t>
+          <t>2026-09-03 16:00:00</t>
         </is>
       </c>
     </row>
@@ -5152,27 +5152,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G30">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-09-03 20:00:00</t>
+          <t>2026-09-03 16:00:00</t>
         </is>
       </c>
     </row>
@@ -5315,27 +5315,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G31">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-09-03 21:00:00</t>
+          <t>2026-09-03 18:30:00</t>
         </is>
       </c>
     </row>
@@ -5478,27 +5478,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Safa</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G32">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-09-03 21:00:00</t>
+          <t>2026-09-03 20:00:00</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G36">
@@ -6298,22 +6298,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Safa</t>
         </is>
       </c>
       <c r="G37">
@@ -6461,22 +6461,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G40">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G41">
@@ -7113,22 +7113,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G42">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N42">
@@ -7276,22 +7276,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G44">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G45">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,141 +8264,467 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
+          <t>Ben Guerdane</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>CS Sfaxien</t>
+        </is>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0</v>
+      </c>
+      <c r="X49">
+        <v>0</v>
+      </c>
+      <c r="Y49">
+        <v>0</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+      <c r="AA49">
+        <v>0</v>
+      </c>
+      <c r="AB49">
+        <v>0</v>
+      </c>
+      <c r="AC49">
+        <v>0</v>
+      </c>
+      <c r="AD49">
+        <v>0</v>
+      </c>
+      <c r="AE49">
+        <v>0</v>
+      </c>
+      <c r="AF49">
+        <v>0</v>
+      </c>
+      <c r="AG49">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>0</v>
+      </c>
+      <c r="AK49">
+        <v>0</v>
+      </c>
+      <c r="AL49">
+        <v>0</v>
+      </c>
+      <c r="AM49">
+        <v>-1</v>
+      </c>
+      <c r="AN49">
+        <v>-1</v>
+      </c>
+      <c r="AO49">
+        <v>-1</v>
+      </c>
+      <c r="AP49">
+        <v>-1</v>
+      </c>
+      <c r="AQ49">
+        <v>0</v>
+      </c>
+      <c r="AR49">
+        <v>0</v>
+      </c>
+      <c r="AS49">
+        <v>0</v>
+      </c>
+      <c r="AT49">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>2026-09-03 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Tunisia Ligue 1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Métlaoui</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Hammam-Sousse</t>
+        </is>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0</v>
+      </c>
+      <c r="X50">
+        <v>0</v>
+      </c>
+      <c r="Y50">
+        <v>0</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+      <c r="AA50">
+        <v>0</v>
+      </c>
+      <c r="AB50">
+        <v>0</v>
+      </c>
+      <c r="AC50">
+        <v>0</v>
+      </c>
+      <c r="AD50">
+        <v>0</v>
+      </c>
+      <c r="AE50">
+        <v>0</v>
+      </c>
+      <c r="AF50">
+        <v>0</v>
+      </c>
+      <c r="AG50">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>0</v>
+      </c>
+      <c r="AK50">
+        <v>0</v>
+      </c>
+      <c r="AL50">
+        <v>0</v>
+      </c>
+      <c r="AM50">
+        <v>-1</v>
+      </c>
+      <c r="AN50">
+        <v>-1</v>
+      </c>
+      <c r="AO50">
+        <v>-1</v>
+      </c>
+      <c r="AP50">
+        <v>-1</v>
+      </c>
+      <c r="AQ50">
+        <v>0</v>
+      </c>
+      <c r="AR50">
+        <v>0</v>
+      </c>
+      <c r="AS50">
+        <v>0</v>
+      </c>
+      <c r="AT50">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>2026-09-03 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Tunisia Ligue 1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Hammam-Lif</t>
         </is>
       </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>0</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49" t="inlineStr">
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
-      <c r="O49">
-        <v>0</v>
-      </c>
-      <c r="P49">
-        <v>0</v>
-      </c>
-      <c r="Q49">
-        <v>0</v>
-      </c>
-      <c r="R49">
-        <v>0</v>
-      </c>
-      <c r="S49">
-        <v>0</v>
-      </c>
-      <c r="T49">
-        <v>0</v>
-      </c>
-      <c r="U49">
-        <v>0</v>
-      </c>
-      <c r="V49">
-        <v>0</v>
-      </c>
-      <c r="W49">
-        <v>0</v>
-      </c>
-      <c r="X49">
-        <v>0</v>
-      </c>
-      <c r="Y49">
-        <v>0</v>
-      </c>
-      <c r="Z49">
-        <v>0</v>
-      </c>
-      <c r="AA49">
-        <v>0</v>
-      </c>
-      <c r="AB49">
-        <v>0</v>
-      </c>
-      <c r="AC49">
-        <v>0</v>
-      </c>
-      <c r="AD49">
-        <v>0</v>
-      </c>
-      <c r="AE49">
-        <v>0</v>
-      </c>
-      <c r="AF49">
-        <v>0</v>
-      </c>
-      <c r="AG49">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>0</v>
-      </c>
-      <c r="AK49">
-        <v>0</v>
-      </c>
-      <c r="AL49">
-        <v>0</v>
-      </c>
-      <c r="AM49">
-        <v>-1</v>
-      </c>
-      <c r="AN49">
-        <v>-1</v>
-      </c>
-      <c r="AO49">
-        <v>-1</v>
-      </c>
-      <c r="AP49">
-        <v>-1</v>
-      </c>
-      <c r="AQ49">
-        <v>0</v>
-      </c>
-      <c r="AR49">
-        <v>0</v>
-      </c>
-      <c r="AS49">
-        <v>0</v>
-      </c>
-      <c r="AT49">
-        <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>0</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51">
+        <v>0</v>
+      </c>
+      <c r="U51">
+        <v>0</v>
+      </c>
+      <c r="V51">
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <v>0</v>
+      </c>
+      <c r="X51">
+        <v>0</v>
+      </c>
+      <c r="Y51">
+        <v>0</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+      <c r="AA51">
+        <v>0</v>
+      </c>
+      <c r="AB51">
+        <v>0</v>
+      </c>
+      <c r="AC51">
+        <v>0</v>
+      </c>
+      <c r="AD51">
+        <v>0</v>
+      </c>
+      <c r="AE51">
+        <v>0</v>
+      </c>
+      <c r="AF51">
+        <v>0</v>
+      </c>
+      <c r="AG51">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>0</v>
+      </c>
+      <c r="AK51">
+        <v>0</v>
+      </c>
+      <c r="AL51">
+        <v>0</v>
+      </c>
+      <c r="AM51">
+        <v>-1</v>
+      </c>
+      <c r="AN51">
+        <v>-1</v>
+      </c>
+      <c r="AO51">
+        <v>-1</v>
+      </c>
+      <c r="AP51">
+        <v>-1</v>
+      </c>
+      <c r="AQ51">
+        <v>0</v>
+      </c>
+      <c r="AR51">
+        <v>0</v>
+      </c>
+      <c r="AS51">
+        <v>0</v>
+      </c>
+      <c r="AT51">
+        <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
         <is>
           <t>2026-09-03 21:00:00</t>
         </is>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G47">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G48">
@@ -8129,7 +8129,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G49">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G50">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N50">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G51">

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU51"/>
+  <dimension ref="A1:AU52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G19">
@@ -3402,68 +3402,68 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3522,12 +3522,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G20">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-09-03 15:30:00</t>
+          <t>2026-09-03 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G21">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G22">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G24">
@@ -4337,12 +4337,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G25">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-09-03 15:45:00</t>
+          <t>2026-09-03 15:30:00</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G26">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G27">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G28">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-09-03 16:00:00</t>
+          <t>2026-09-03 15:45:00</t>
         </is>
       </c>
     </row>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="G29">
@@ -5157,22 +5157,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G30">
@@ -5315,27 +5315,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G31">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-09-03 18:30:00</t>
+          <t>2026-09-03 16:00:00</t>
         </is>
       </c>
     </row>
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G32">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-09-03 20:00:00</t>
+          <t>2026-09-03 18:30:00</t>
         </is>
       </c>
     </row>
@@ -5641,27 +5641,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G33">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-09-03 21:00:00</t>
+          <t>2026-09-03 20:00:00</t>
         </is>
       </c>
     </row>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Safa</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Safa</t>
         </is>
       </c>
       <c r="G38">
@@ -6624,22 +6624,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G42">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G43">
@@ -7439,22 +7439,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G44">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G45">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G48">
@@ -8129,7 +8129,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G49">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G50">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N50">
@@ -8590,141 +8590,304 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>Ben Guerdane</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>CS Sfaxien</t>
+        </is>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>0</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51">
+        <v>0</v>
+      </c>
+      <c r="U51">
+        <v>0</v>
+      </c>
+      <c r="V51">
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <v>0</v>
+      </c>
+      <c r="X51">
+        <v>0</v>
+      </c>
+      <c r="Y51">
+        <v>0</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+      <c r="AA51">
+        <v>0</v>
+      </c>
+      <c r="AB51">
+        <v>0</v>
+      </c>
+      <c r="AC51">
+        <v>0</v>
+      </c>
+      <c r="AD51">
+        <v>0</v>
+      </c>
+      <c r="AE51">
+        <v>0</v>
+      </c>
+      <c r="AF51">
+        <v>0</v>
+      </c>
+      <c r="AG51">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>0</v>
+      </c>
+      <c r="AK51">
+        <v>0</v>
+      </c>
+      <c r="AL51">
+        <v>0</v>
+      </c>
+      <c r="AM51">
+        <v>-1</v>
+      </c>
+      <c r="AN51">
+        <v>-1</v>
+      </c>
+      <c r="AO51">
+        <v>-1</v>
+      </c>
+      <c r="AP51">
+        <v>-1</v>
+      </c>
+      <c r="AQ51">
+        <v>0</v>
+      </c>
+      <c r="AR51">
+        <v>0</v>
+      </c>
+      <c r="AS51">
+        <v>0</v>
+      </c>
+      <c r="AT51">
+        <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>2026-09-03 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Tunisia Ligue 1</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>Métlaoui</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Hammam-Sousse</t>
         </is>
       </c>
-      <c r="G51">
-        <v>0</v>
-      </c>
-      <c r="H51">
-        <v>0</v>
-      </c>
-      <c r="I51">
-        <v>0</v>
-      </c>
-      <c r="J51">
-        <v>0</v>
-      </c>
-      <c r="K51">
-        <v>0</v>
-      </c>
-      <c r="L51">
-        <v>0</v>
-      </c>
-      <c r="M51" t="inlineStr">
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N51">
-        <v>0</v>
-      </c>
-      <c r="O51">
-        <v>0</v>
-      </c>
-      <c r="P51">
-        <v>0</v>
-      </c>
-      <c r="Q51">
-        <v>0</v>
-      </c>
-      <c r="R51">
-        <v>0</v>
-      </c>
-      <c r="S51">
-        <v>0</v>
-      </c>
-      <c r="T51">
-        <v>0</v>
-      </c>
-      <c r="U51">
-        <v>0</v>
-      </c>
-      <c r="V51">
-        <v>0</v>
-      </c>
-      <c r="W51">
-        <v>0</v>
-      </c>
-      <c r="X51">
-        <v>0</v>
-      </c>
-      <c r="Y51">
-        <v>0</v>
-      </c>
-      <c r="Z51">
-        <v>0</v>
-      </c>
-      <c r="AA51">
-        <v>0</v>
-      </c>
-      <c r="AB51">
-        <v>0</v>
-      </c>
-      <c r="AC51">
-        <v>0</v>
-      </c>
-      <c r="AD51">
-        <v>0</v>
-      </c>
-      <c r="AE51">
-        <v>0</v>
-      </c>
-      <c r="AF51">
-        <v>0</v>
-      </c>
-      <c r="AG51">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>0</v>
-      </c>
-      <c r="AK51">
-        <v>0</v>
-      </c>
-      <c r="AL51">
-        <v>0</v>
-      </c>
-      <c r="AM51">
-        <v>-1</v>
-      </c>
-      <c r="AN51">
-        <v>-1</v>
-      </c>
-      <c r="AO51">
-        <v>-1</v>
-      </c>
-      <c r="AP51">
-        <v>-1</v>
-      </c>
-      <c r="AQ51">
-        <v>0</v>
-      </c>
-      <c r="AR51">
-        <v>0</v>
-      </c>
-      <c r="AS51">
-        <v>0</v>
-      </c>
-      <c r="AT51">
-        <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>0</v>
+      </c>
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <v>0</v>
+      </c>
+      <c r="U52">
+        <v>0</v>
+      </c>
+      <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <v>0</v>
+      </c>
+      <c r="X52">
+        <v>0</v>
+      </c>
+      <c r="Y52">
+        <v>0</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+      <c r="AA52">
+        <v>0</v>
+      </c>
+      <c r="AB52">
+        <v>0</v>
+      </c>
+      <c r="AC52">
+        <v>0</v>
+      </c>
+      <c r="AD52">
+        <v>0</v>
+      </c>
+      <c r="AE52">
+        <v>0</v>
+      </c>
+      <c r="AF52">
+        <v>0</v>
+      </c>
+      <c r="AG52">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
+        <v>0</v>
+      </c>
+      <c r="AK52">
+        <v>0</v>
+      </c>
+      <c r="AL52">
+        <v>0</v>
+      </c>
+      <c r="AM52">
+        <v>-1</v>
+      </c>
+      <c r="AN52">
+        <v>-1</v>
+      </c>
+      <c r="AO52">
+        <v>-1</v>
+      </c>
+      <c r="AP52">
+        <v>-1</v>
+      </c>
+      <c r="AQ52">
+        <v>0</v>
+      </c>
+      <c r="AR52">
+        <v>0</v>
+      </c>
+      <c r="AS52">
+        <v>0</v>
+      </c>
+      <c r="AT52">
+        <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
         <is>
           <t>2026-09-03 21:00:00</t>
         </is>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU52"/>
+  <dimension ref="A1:AU51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G19">
@@ -3402,68 +3402,68 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N19">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="T19">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V19">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X19">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y19">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z19">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA19">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB19">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC19">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AD19">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE19">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF19">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AG19">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK19">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3522,12 +3522,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G20">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-09-03 15:00:00</t>
+          <t>2026-09-03 15:30:00</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G21">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G22">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G24">
@@ -4337,12 +4337,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G25">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-09-03 15:30:00</t>
+          <t>2026-09-03 15:45:00</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G26">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G27">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="G28">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-09-03 15:45:00</t>
+          <t>2026-09-03 16:00:00</t>
         </is>
       </c>
     </row>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G29">
@@ -5157,22 +5157,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G30">
@@ -5315,27 +5315,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G31">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-09-03 16:00:00</t>
+          <t>2026-09-03 18:30:00</t>
         </is>
       </c>
     </row>
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G32">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-09-03 18:30:00</t>
+          <t>2026-09-03 20:00:00</t>
         </is>
       </c>
     </row>
@@ -5641,27 +5641,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G33">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-09-03 20:00:00</t>
+          <t>2026-09-03 21:00:00</t>
         </is>
       </c>
     </row>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Safa</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Safa</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G38">
@@ -6624,22 +6624,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G42">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G43">
@@ -7439,22 +7439,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G44">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G45">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G48">
@@ -8129,7 +8129,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G49">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G50">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N50">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G51">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N51">
@@ -8725,169 +8725,6 @@
         <v>0</v>
       </c>
       <c r="AU51" t="inlineStr">
-        <is>
-          <t>2026-09-03 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Tunisia Ligue 1</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Métlaoui</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Hammam-Sousse</t>
-        </is>
-      </c>
-      <c r="G52">
-        <v>0</v>
-      </c>
-      <c r="H52">
-        <v>0</v>
-      </c>
-      <c r="I52">
-        <v>0</v>
-      </c>
-      <c r="J52">
-        <v>0</v>
-      </c>
-      <c r="K52">
-        <v>0</v>
-      </c>
-      <c r="L52">
-        <v>0</v>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N52">
-        <v>0</v>
-      </c>
-      <c r="O52">
-        <v>0</v>
-      </c>
-      <c r="P52">
-        <v>0</v>
-      </c>
-      <c r="Q52">
-        <v>0</v>
-      </c>
-      <c r="R52">
-        <v>0</v>
-      </c>
-      <c r="S52">
-        <v>0</v>
-      </c>
-      <c r="T52">
-        <v>0</v>
-      </c>
-      <c r="U52">
-        <v>0</v>
-      </c>
-      <c r="V52">
-        <v>0</v>
-      </c>
-      <c r="W52">
-        <v>0</v>
-      </c>
-      <c r="X52">
-        <v>0</v>
-      </c>
-      <c r="Y52">
-        <v>0</v>
-      </c>
-      <c r="Z52">
-        <v>0</v>
-      </c>
-      <c r="AA52">
-        <v>0</v>
-      </c>
-      <c r="AB52">
-        <v>0</v>
-      </c>
-      <c r="AC52">
-        <v>0</v>
-      </c>
-      <c r="AD52">
-        <v>0</v>
-      </c>
-      <c r="AE52">
-        <v>0</v>
-      </c>
-      <c r="AF52">
-        <v>0</v>
-      </c>
-      <c r="AG52">
-        <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>0</v>
-      </c>
-      <c r="AK52">
-        <v>0</v>
-      </c>
-      <c r="AL52">
-        <v>0</v>
-      </c>
-      <c r="AM52">
-        <v>-1</v>
-      </c>
-      <c r="AN52">
-        <v>-1</v>
-      </c>
-      <c r="AO52">
-        <v>-1</v>
-      </c>
-      <c r="AP52">
-        <v>-1</v>
-      </c>
-      <c r="AQ52">
-        <v>0</v>
-      </c>
-      <c r="AR52">
-        <v>0</v>
-      </c>
-      <c r="AS52">
-        <v>0</v>
-      </c>
-      <c r="AT52">
-        <v>0</v>
-      </c>
-      <c r="AU52" t="inlineStr">
         <is>
           <t>2026-09-03 21:00:00</t>
         </is>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU51"/>
+  <dimension ref="A1:AU47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G39">
@@ -6787,22 +6787,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G40">
@@ -6950,22 +6950,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G41">
@@ -7113,22 +7113,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="G42">
@@ -7276,22 +7276,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G44">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G47">
@@ -8073,658 +8073,6 @@
         <v>0</v>
       </c>
       <c r="AU47" t="inlineStr">
-        <is>
-          <t>2026-09-03 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Tunisia Ligue 1</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Stade Tunisien</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Club Africain</t>
-        </is>
-      </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48">
-        <v>0</v>
-      </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
-      <c r="O48">
-        <v>0</v>
-      </c>
-      <c r="P48">
-        <v>0</v>
-      </c>
-      <c r="Q48">
-        <v>0</v>
-      </c>
-      <c r="R48">
-        <v>0</v>
-      </c>
-      <c r="S48">
-        <v>0</v>
-      </c>
-      <c r="T48">
-        <v>0</v>
-      </c>
-      <c r="U48">
-        <v>0</v>
-      </c>
-      <c r="V48">
-        <v>0</v>
-      </c>
-      <c r="W48">
-        <v>0</v>
-      </c>
-      <c r="X48">
-        <v>0</v>
-      </c>
-      <c r="Y48">
-        <v>0</v>
-      </c>
-      <c r="Z48">
-        <v>0</v>
-      </c>
-      <c r="AA48">
-        <v>0</v>
-      </c>
-      <c r="AB48">
-        <v>0</v>
-      </c>
-      <c r="AC48">
-        <v>0</v>
-      </c>
-      <c r="AD48">
-        <v>0</v>
-      </c>
-      <c r="AE48">
-        <v>0</v>
-      </c>
-      <c r="AF48">
-        <v>0</v>
-      </c>
-      <c r="AG48">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>0</v>
-      </c>
-      <c r="AK48">
-        <v>0</v>
-      </c>
-      <c r="AL48">
-        <v>0</v>
-      </c>
-      <c r="AM48">
-        <v>-1</v>
-      </c>
-      <c r="AN48">
-        <v>-1</v>
-      </c>
-      <c r="AO48">
-        <v>-1</v>
-      </c>
-      <c r="AP48">
-        <v>-1</v>
-      </c>
-      <c r="AQ48">
-        <v>0</v>
-      </c>
-      <c r="AR48">
-        <v>0</v>
-      </c>
-      <c r="AS48">
-        <v>0</v>
-      </c>
-      <c r="AT48">
-        <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>2026-09-03 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Tunisia Ligue 1</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>ES Tunis</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Marsa</t>
-        </is>
-      </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>0</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
-      <c r="O49">
-        <v>0</v>
-      </c>
-      <c r="P49">
-        <v>0</v>
-      </c>
-      <c r="Q49">
-        <v>0</v>
-      </c>
-      <c r="R49">
-        <v>0</v>
-      </c>
-      <c r="S49">
-        <v>0</v>
-      </c>
-      <c r="T49">
-        <v>0</v>
-      </c>
-      <c r="U49">
-        <v>0</v>
-      </c>
-      <c r="V49">
-        <v>0</v>
-      </c>
-      <c r="W49">
-        <v>0</v>
-      </c>
-      <c r="X49">
-        <v>0</v>
-      </c>
-      <c r="Y49">
-        <v>0</v>
-      </c>
-      <c r="Z49">
-        <v>0</v>
-      </c>
-      <c r="AA49">
-        <v>0</v>
-      </c>
-      <c r="AB49">
-        <v>0</v>
-      </c>
-      <c r="AC49">
-        <v>0</v>
-      </c>
-      <c r="AD49">
-        <v>0</v>
-      </c>
-      <c r="AE49">
-        <v>0</v>
-      </c>
-      <c r="AF49">
-        <v>0</v>
-      </c>
-      <c r="AG49">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>0</v>
-      </c>
-      <c r="AK49">
-        <v>0</v>
-      </c>
-      <c r="AL49">
-        <v>0</v>
-      </c>
-      <c r="AM49">
-        <v>-1</v>
-      </c>
-      <c r="AN49">
-        <v>-1</v>
-      </c>
-      <c r="AO49">
-        <v>-1</v>
-      </c>
-      <c r="AP49">
-        <v>-1</v>
-      </c>
-      <c r="AQ49">
-        <v>0</v>
-      </c>
-      <c r="AR49">
-        <v>0</v>
-      </c>
-      <c r="AS49">
-        <v>0</v>
-      </c>
-      <c r="AT49">
-        <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>2026-09-03 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Tunisia Ligue 1</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Ben Guerdane</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>CS Sfaxien</t>
-        </is>
-      </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
-      <c r="H50">
-        <v>0</v>
-      </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50">
-        <v>0</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="N50">
-        <v>0</v>
-      </c>
-      <c r="O50">
-        <v>0</v>
-      </c>
-      <c r="P50">
-        <v>0</v>
-      </c>
-      <c r="Q50">
-        <v>0</v>
-      </c>
-      <c r="R50">
-        <v>0</v>
-      </c>
-      <c r="S50">
-        <v>0</v>
-      </c>
-      <c r="T50">
-        <v>0</v>
-      </c>
-      <c r="U50">
-        <v>0</v>
-      </c>
-      <c r="V50">
-        <v>0</v>
-      </c>
-      <c r="W50">
-        <v>0</v>
-      </c>
-      <c r="X50">
-        <v>0</v>
-      </c>
-      <c r="Y50">
-        <v>0</v>
-      </c>
-      <c r="Z50">
-        <v>0</v>
-      </c>
-      <c r="AA50">
-        <v>0</v>
-      </c>
-      <c r="AB50">
-        <v>0</v>
-      </c>
-      <c r="AC50">
-        <v>0</v>
-      </c>
-      <c r="AD50">
-        <v>0</v>
-      </c>
-      <c r="AE50">
-        <v>0</v>
-      </c>
-      <c r="AF50">
-        <v>0</v>
-      </c>
-      <c r="AG50">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>0</v>
-      </c>
-      <c r="AK50">
-        <v>0</v>
-      </c>
-      <c r="AL50">
-        <v>0</v>
-      </c>
-      <c r="AM50">
-        <v>-1</v>
-      </c>
-      <c r="AN50">
-        <v>-1</v>
-      </c>
-      <c r="AO50">
-        <v>-1</v>
-      </c>
-      <c r="AP50">
-        <v>-1</v>
-      </c>
-      <c r="AQ50">
-        <v>0</v>
-      </c>
-      <c r="AR50">
-        <v>0</v>
-      </c>
-      <c r="AS50">
-        <v>0</v>
-      </c>
-      <c r="AT50">
-        <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>2026-09-03 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Tunisia Ligue 1</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Métlaoui</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Hammam-Sousse</t>
-        </is>
-      </c>
-      <c r="G51">
-        <v>0</v>
-      </c>
-      <c r="H51">
-        <v>0</v>
-      </c>
-      <c r="I51">
-        <v>0</v>
-      </c>
-      <c r="J51">
-        <v>0</v>
-      </c>
-      <c r="K51">
-        <v>0</v>
-      </c>
-      <c r="L51">
-        <v>0</v>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N51">
-        <v>0</v>
-      </c>
-      <c r="O51">
-        <v>0</v>
-      </c>
-      <c r="P51">
-        <v>0</v>
-      </c>
-      <c r="Q51">
-        <v>0</v>
-      </c>
-      <c r="R51">
-        <v>0</v>
-      </c>
-      <c r="S51">
-        <v>0</v>
-      </c>
-      <c r="T51">
-        <v>0</v>
-      </c>
-      <c r="U51">
-        <v>0</v>
-      </c>
-      <c r="V51">
-        <v>0</v>
-      </c>
-      <c r="W51">
-        <v>0</v>
-      </c>
-      <c r="X51">
-        <v>0</v>
-      </c>
-      <c r="Y51">
-        <v>0</v>
-      </c>
-      <c r="Z51">
-        <v>0</v>
-      </c>
-      <c r="AA51">
-        <v>0</v>
-      </c>
-      <c r="AB51">
-        <v>0</v>
-      </c>
-      <c r="AC51">
-        <v>0</v>
-      </c>
-      <c r="AD51">
-        <v>0</v>
-      </c>
-      <c r="AE51">
-        <v>0</v>
-      </c>
-      <c r="AF51">
-        <v>0</v>
-      </c>
-      <c r="AG51">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>0</v>
-      </c>
-      <c r="AK51">
-        <v>0</v>
-      </c>
-      <c r="AL51">
-        <v>0</v>
-      </c>
-      <c r="AM51">
-        <v>-1</v>
-      </c>
-      <c r="AN51">
-        <v>-1</v>
-      </c>
-      <c r="AO51">
-        <v>-1</v>
-      </c>
-      <c r="AP51">
-        <v>-1</v>
-      </c>
-      <c r="AQ51">
-        <v>0</v>
-      </c>
-      <c r="AR51">
-        <v>0</v>
-      </c>
-      <c r="AS51">
-        <v>0</v>
-      </c>
-      <c r="AT51">
-        <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
         <is>
           <t>2026-09-03 21:00:00</t>
         </is>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G21">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G24">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N28">

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU47"/>
+  <dimension ref="A1:AU49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3522,12 +3522,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G20">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-09-03 15:30:00</t>
+          <t>2026-09-03 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G21">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G22">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G24">
@@ -4337,12 +4337,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G25">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-09-03 15:45:00</t>
+          <t>2026-09-03 15:30:00</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G26">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G27">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G28">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N28">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-09-03 16:00:00</t>
+          <t>2026-09-03 15:45:00</t>
         </is>
       </c>
     </row>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="G29">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N29">
@@ -5157,22 +5157,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G30">
@@ -5315,27 +5315,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G31">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-09-03 18:30:00</t>
+          <t>2026-09-03 16:00:00</t>
         </is>
       </c>
     </row>
@@ -5478,27 +5478,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-09-03 20:00:00</t>
+          <t>2026-09-03 17:00:00</t>
         </is>
       </c>
     </row>
@@ -5641,27 +5641,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G33">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-09-03 21:00:00</t>
+          <t>2026-09-03 18:30:00</t>
         </is>
       </c>
     </row>
@@ -5804,27 +5804,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G34">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-09-03 21:00:00</t>
+          <t>2026-09-03 20:00:00</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Safa</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G38">
@@ -6624,22 +6624,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Safa</t>
         </is>
       </c>
       <c r="G39">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G40">
@@ -6950,22 +6950,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,141 +7938,467 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>Métlaoui</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Hammam-Sousse</t>
+        </is>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <v>0</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0</v>
+      </c>
+      <c r="X47">
+        <v>0</v>
+      </c>
+      <c r="Y47">
+        <v>0</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+      <c r="AA47">
+        <v>0</v>
+      </c>
+      <c r="AB47">
+        <v>0</v>
+      </c>
+      <c r="AC47">
+        <v>0</v>
+      </c>
+      <c r="AD47">
+        <v>0</v>
+      </c>
+      <c r="AE47">
+        <v>0</v>
+      </c>
+      <c r="AF47">
+        <v>0</v>
+      </c>
+      <c r="AG47">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47">
+        <v>0</v>
+      </c>
+      <c r="AK47">
+        <v>0</v>
+      </c>
+      <c r="AL47">
+        <v>0</v>
+      </c>
+      <c r="AM47">
+        <v>-1</v>
+      </c>
+      <c r="AN47">
+        <v>-1</v>
+      </c>
+      <c r="AO47">
+        <v>-1</v>
+      </c>
+      <c r="AP47">
+        <v>-1</v>
+      </c>
+      <c r="AQ47">
+        <v>0</v>
+      </c>
+      <c r="AR47">
+        <v>0</v>
+      </c>
+      <c r="AS47">
+        <v>0</v>
+      </c>
+      <c r="AT47">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>2026-09-03 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Tunisia Ligue 1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Ben Guerdane</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>CS Sfaxien</t>
+        </is>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>0</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>0</v>
+      </c>
+      <c r="X48">
+        <v>0</v>
+      </c>
+      <c r="Y48">
+        <v>0</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+      <c r="AA48">
+        <v>0</v>
+      </c>
+      <c r="AB48">
+        <v>0</v>
+      </c>
+      <c r="AC48">
+        <v>0</v>
+      </c>
+      <c r="AD48">
+        <v>0</v>
+      </c>
+      <c r="AE48">
+        <v>0</v>
+      </c>
+      <c r="AF48">
+        <v>0</v>
+      </c>
+      <c r="AG48">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>0</v>
+      </c>
+      <c r="AK48">
+        <v>0</v>
+      </c>
+      <c r="AL48">
+        <v>0</v>
+      </c>
+      <c r="AM48">
+        <v>-1</v>
+      </c>
+      <c r="AN48">
+        <v>-1</v>
+      </c>
+      <c r="AO48">
+        <v>-1</v>
+      </c>
+      <c r="AP48">
+        <v>-1</v>
+      </c>
+      <c r="AQ48">
+        <v>0</v>
+      </c>
+      <c r="AR48">
+        <v>0</v>
+      </c>
+      <c r="AS48">
+        <v>0</v>
+      </c>
+      <c r="AT48">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>2026-09-03 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Tunisia Ligue 1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>Stade Tunisien</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Club Africain</t>
         </is>
       </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-      <c r="H47">
-        <v>0</v>
-      </c>
-      <c r="I47">
-        <v>0</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47">
-        <v>0</v>
-      </c>
-      <c r="L47">
-        <v>0</v>
-      </c>
-      <c r="M47" t="inlineStr">
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N47">
-        <v>0</v>
-      </c>
-      <c r="O47">
-        <v>0</v>
-      </c>
-      <c r="P47">
-        <v>0</v>
-      </c>
-      <c r="Q47">
-        <v>0</v>
-      </c>
-      <c r="R47">
-        <v>0</v>
-      </c>
-      <c r="S47">
-        <v>0</v>
-      </c>
-      <c r="T47">
-        <v>0</v>
-      </c>
-      <c r="U47">
-        <v>0</v>
-      </c>
-      <c r="V47">
-        <v>0</v>
-      </c>
-      <c r="W47">
-        <v>0</v>
-      </c>
-      <c r="X47">
-        <v>0</v>
-      </c>
-      <c r="Y47">
-        <v>0</v>
-      </c>
-      <c r="Z47">
-        <v>0</v>
-      </c>
-      <c r="AA47">
-        <v>0</v>
-      </c>
-      <c r="AB47">
-        <v>0</v>
-      </c>
-      <c r="AC47">
-        <v>0</v>
-      </c>
-      <c r="AD47">
-        <v>0</v>
-      </c>
-      <c r="AE47">
-        <v>0</v>
-      </c>
-      <c r="AF47">
-        <v>0</v>
-      </c>
-      <c r="AG47">
-        <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47">
-        <v>0</v>
-      </c>
-      <c r="AK47">
-        <v>0</v>
-      </c>
-      <c r="AL47">
-        <v>0</v>
-      </c>
-      <c r="AM47">
-        <v>-1</v>
-      </c>
-      <c r="AN47">
-        <v>-1</v>
-      </c>
-      <c r="AO47">
-        <v>-1</v>
-      </c>
-      <c r="AP47">
-        <v>-1</v>
-      </c>
-      <c r="AQ47">
-        <v>0</v>
-      </c>
-      <c r="AR47">
-        <v>0</v>
-      </c>
-      <c r="AS47">
-        <v>0</v>
-      </c>
-      <c r="AT47">
-        <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0</v>
+      </c>
+      <c r="X49">
+        <v>0</v>
+      </c>
+      <c r="Y49">
+        <v>0</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+      <c r="AA49">
+        <v>0</v>
+      </c>
+      <c r="AB49">
+        <v>0</v>
+      </c>
+      <c r="AC49">
+        <v>0</v>
+      </c>
+      <c r="AD49">
+        <v>0</v>
+      </c>
+      <c r="AE49">
+        <v>0</v>
+      </c>
+      <c r="AF49">
+        <v>0</v>
+      </c>
+      <c r="AG49">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>0</v>
+      </c>
+      <c r="AK49">
+        <v>0</v>
+      </c>
+      <c r="AL49">
+        <v>0</v>
+      </c>
+      <c r="AM49">
+        <v>-1</v>
+      </c>
+      <c r="AN49">
+        <v>-1</v>
+      </c>
+      <c r="AO49">
+        <v>-1</v>
+      </c>
+      <c r="AP49">
+        <v>-1</v>
+      </c>
+      <c r="AQ49">
+        <v>0</v>
+      </c>
+      <c r="AR49">
+        <v>0</v>
+      </c>
+      <c r="AS49">
+        <v>0</v>
+      </c>
+      <c r="AT49">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
         <is>
           <t>2026-09-03 21:00:00</t>
         </is>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G46">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G47">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G49">

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -2913,7 +2913,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N16">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G49">

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -807,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -819,43 +819,43 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X3">
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -1459,55 +1459,55 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,31 +1613,31 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W8">
         <v>0</v>
@@ -1646,31 +1646,31 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL8">
         <v>0</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1948,55 +1948,55 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G13">
@@ -2437,55 +2437,55 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G14">
@@ -2600,55 +2600,55 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -4079,10 +4079,10 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W23">
         <v>0</v>
@@ -4091,31 +4091,31 @@
         <v>0</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL31">
         <v>0</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q34">
         <v>0</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -973,7 +973,7 @@
         <v>2.77</v>
       </c>
       <c r="R4">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="S4">
         <v>1.26</v>
@@ -982,13 +982,13 @@
         <v>3.2</v>
       </c>
       <c r="U4">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="V4">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W4">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X4">
         <v>1.01</v>
@@ -997,7 +997,7 @@
         <v>1.13</v>
       </c>
       <c r="Z4">
-        <v>4.87</v>
+        <v>5</v>
       </c>
       <c r="AA4">
         <v>1.54</v>
@@ -1012,7 +1012,7 @@
         <v>1.5</v>
       </c>
       <c r="AE4">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF4">
         <v>1.45</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q3">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="R3">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U3">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="V3">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W3">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z3">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="AA3">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB3">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC3">
-        <v>2.87</v>
+        <v>3.04</v>
       </c>
       <c r="AD3">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE3">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG3">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK3">
         <v>1.56</v>
@@ -1640,10 +1640,10 @@
         <v>1.38</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
         <v>1.28</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5860,55 +5860,55 @@
         <v>3.75</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL34">
         <v>0</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -843,13 +843,13 @@
         <v>1.87</v>
       </c>
       <c r="AC3">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AD3">
         <v>1.3</v>
       </c>
       <c r="AE3">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF3">
         <v>1.67</v>
@@ -1287,34 +1287,34 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="O6">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="P6">
-        <v>2.59</v>
+        <v>2.71</v>
       </c>
       <c r="Q6">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="R6">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="S6">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T6">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="U6">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="V6">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X6">
         <v>1.03</v>
@@ -1326,25 +1326,25 @@
         <v>2.83</v>
       </c>
       <c r="AA6">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AB6">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC6">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="AD6">
         <v>1.21</v>
       </c>
       <c r="AE6">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF6">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG6">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK6">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q7">
         <v>2.16</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="O8">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P8">
-        <v>3.26</v>
+        <v>3.11</v>
       </c>
       <c r="Q8">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="R8">
         <v>2.12</v>
       </c>
       <c r="S8">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T8">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="U8">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="V8">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W8">
+        <v>1.06</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>1.21</v>
+      </c>
+      <c r="Z8">
+        <v>3.58</v>
+      </c>
+      <c r="AA8">
+        <v>1.79</v>
+      </c>
+      <c r="AB8">
+        <v>1.97</v>
+      </c>
+      <c r="AC8">
+        <v>2.83</v>
+      </c>
+      <c r="AD8">
+        <v>1.33</v>
+      </c>
+      <c r="AE8">
         <v>1.09</v>
-      </c>
-      <c r="X8">
-        <v>1.02</v>
-      </c>
-      <c r="Y8">
-        <v>1.28</v>
-      </c>
-      <c r="Z8">
-        <v>3.3</v>
-      </c>
-      <c r="AA8">
-        <v>1.95</v>
-      </c>
-      <c r="AB8">
-        <v>1.74</v>
-      </c>
-      <c r="AC8">
-        <v>3.45</v>
-      </c>
-      <c r="AD8">
-        <v>1.25</v>
-      </c>
-      <c r="AE8">
-        <v>1.06</v>
       </c>
       <c r="AF8">
         <v>1.75</v>
       </c>
       <c r="AG8">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1948,22 +1948,22 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R10">
         <v>2.25</v>
       </c>
       <c r="S10">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T10">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U10">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W10">
         <v>1.07</v>
@@ -1972,7 +1972,7 @@
         <v>1</v>
       </c>
       <c r="Y10">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z10">
         <v>3.58</v>
@@ -1981,16 +1981,16 @@
         <v>1.8</v>
       </c>
       <c r="AB10">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AC10">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AD10">
         <v>1.32</v>
       </c>
       <c r="AE10">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF10">
         <v>1.66</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK10">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="R13">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="S13">
         <v>1.33</v>
@@ -2455,16 +2455,16 @@
         <v>1.44</v>
       </c>
       <c r="W13">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z13">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AA13">
         <v>1.8</v>
@@ -2485,7 +2485,7 @@
         <v>1.63</v>
       </c>
       <c r="AG13">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK13">
         <v>1.46</v>
@@ -2591,19 +2591,19 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q14">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="R14">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S14">
         <v>1.27</v>
@@ -2642,13 +2642,13 @@
         <v>1.44</v>
       </c>
       <c r="AE14">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF14">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AG14">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.01</v>
+        <v>2.68</v>
       </c>
       <c r="O21">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P21">
-        <v>3.07</v>
+        <v>2.42</v>
       </c>
       <c r="Q21">
-        <v>2.6</v>
+        <v>3.18</v>
       </c>
       <c r="R21">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S21">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="T21">
         <v>3.34</v>
       </c>
       <c r="U21">
-        <v>2.39</v>
+        <v>2.21</v>
       </c>
       <c r="V21">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="W21">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X21">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="Z21">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="AA21">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="AB21">
-        <v>2.19</v>
+        <v>2.34</v>
       </c>
       <c r="AC21">
-        <v>2.54</v>
+        <v>2.31</v>
       </c>
       <c r="AD21">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="AE21">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AF21">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AG21">
-        <v>2.32</v>
+        <v>2.63</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK21">
-        <v>1.74</v>
+        <v>1.44</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.52</v>
+        <v>2.01</v>
       </c>
       <c r="O22">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P22">
-        <v>2.32</v>
+        <v>3.07</v>
       </c>
       <c r="Q22">
-        <v>3.14</v>
+        <v>2.6</v>
       </c>
       <c r="R22">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S22">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T22">
         <v>3.34</v>
       </c>
       <c r="U22">
-        <v>2.21</v>
+        <v>2.39</v>
       </c>
       <c r="V22">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="W22">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X22">
         <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="Z22">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="AA22">
+        <v>1.65</v>
+      </c>
+      <c r="AB22">
+        <v>2.19</v>
+      </c>
+      <c r="AC22">
+        <v>2.54</v>
+      </c>
+      <c r="AD22">
         <v>1.48</v>
       </c>
-      <c r="AB22">
-        <v>2.34</v>
-      </c>
-      <c r="AC22">
-        <v>2.27</v>
-      </c>
-      <c r="AD22">
-        <v>1.61</v>
-      </c>
       <c r="AE22">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AF22">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AG22">
-        <v>2.63</v>
+        <v>2.32</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK22">
-        <v>1.45</v>
+        <v>1.74</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="O23">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="P23">
-        <v>3.99</v>
+        <v>4.86</v>
       </c>
       <c r="Q23">
         <v>2.25</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK23">
         <v>1.92</v>
@@ -4556,10 +4556,10 @@
         <v>2.3</v>
       </c>
       <c r="Q26">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="R26">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S26">
         <v>1.45</v>
@@ -4586,10 +4586,10 @@
         <v>3.14</v>
       </c>
       <c r="AA26">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB26">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AC26">
         <v>3.4</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5362,80 +5362,80 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="O31">
-        <v>3.18</v>
+        <v>3.42</v>
       </c>
       <c r="P31">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="Q31">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="R31">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="S31">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="T31">
-        <v>2.6</v>
+        <v>3.03</v>
       </c>
       <c r="U31">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="V31">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="W31">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X31">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y31">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="Z31">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="AA31">
-        <v>2.57</v>
+        <v>1.85</v>
       </c>
       <c r="AB31">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC31">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD31">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AE31">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF31">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AG31">
+        <v>2.04</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
+        <v>1.25</v>
+      </c>
+      <c r="AK31">
         <v>1.67</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.38</v>
-      </c>
-      <c r="AK31">
-        <v>1.57</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G38">

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -5851,19 +5851,19 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="O34">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P34">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="Q34">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="R34">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S34">
         <v>1.43</v>
@@ -5872,10 +5872,10 @@
         <v>2.74</v>
       </c>
       <c r="U34">
-        <v>3.05</v>
+        <v>3.16</v>
       </c>
       <c r="V34">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W34">
         <v>1.02</v>
@@ -5899,7 +5899,7 @@
         <v>3.74</v>
       </c>
       <c r="AD34">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE34">
         <v>1.02</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK34">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL34">
         <v>0</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -5202,10 +5202,10 @@
         <v>1.81</v>
       </c>
       <c r="O30">
-        <v>3.52</v>
+        <v>3.59</v>
       </c>
       <c r="P30">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q33">
         <v>0</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -807,19 +807,19 @@
         <v>3</v>
       </c>
       <c r="Q3">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="R3">
         <v>2.18</v>
       </c>
       <c r="S3">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T3">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U3">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="V3">
         <v>1.39</v>
@@ -828,28 +828,28 @@
         <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y3">
         <v>1.23</v>
       </c>
       <c r="Z3">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="AA3">
         <v>1.83</v>
       </c>
       <c r="AB3">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC3">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AD3">
         <v>1.3</v>
       </c>
       <c r="AE3">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF3">
         <v>1.67</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK3">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -964,22 +964,22 @@
         <v>2.25</v>
       </c>
       <c r="O4">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P4">
         <v>2.75</v>
       </c>
       <c r="Q4">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="R4">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="S4">
         <v>1.26</v>
       </c>
       <c r="T4">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="U4">
         <v>2.28</v>
@@ -988,7 +988,7 @@
         <v>1.55</v>
       </c>
       <c r="W4">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X4">
         <v>1.01</v>
@@ -1009,10 +1009,10 @@
         <v>2.28</v>
       </c>
       <c r="AD4">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AE4">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF4">
         <v>1.45</v>
@@ -1287,34 +1287,34 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O6">
+        <v>3.15</v>
+      </c>
+      <c r="P6">
+        <v>2.65</v>
+      </c>
+      <c r="Q6">
+        <v>3.16</v>
+      </c>
+      <c r="R6">
+        <v>1.98</v>
+      </c>
+      <c r="S6">
+        <v>1.41</v>
+      </c>
+      <c r="T6">
+        <v>2.75</v>
+      </c>
+      <c r="U6">
         <v>3.1</v>
       </c>
-      <c r="P6">
-        <v>2.71</v>
-      </c>
-      <c r="Q6">
-        <v>3.3</v>
-      </c>
-      <c r="R6">
-        <v>2</v>
-      </c>
-      <c r="S6">
-        <v>1.43</v>
-      </c>
-      <c r="T6">
-        <v>2.53</v>
-      </c>
-      <c r="U6">
-        <v>2.96</v>
-      </c>
       <c r="V6">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="W6">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X6">
         <v>1.03</v>
@@ -1329,16 +1329,16 @@
         <v>2.1</v>
       </c>
       <c r="AB6">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AC6">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="AD6">
         <v>1.21</v>
       </c>
       <c r="AE6">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF6">
         <v>1.83</v>
@@ -1459,10 +1459,10 @@
         <v>4.33</v>
       </c>
       <c r="Q7">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R7">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="S7">
         <v>1.3</v>
@@ -1471,7 +1471,7 @@
         <v>3.04</v>
       </c>
       <c r="U7">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V7">
         <v>1.43</v>
@@ -1486,16 +1486,16 @@
         <v>1.22</v>
       </c>
       <c r="Z7">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="AA7">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AB7">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AC7">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="AD7">
         <v>1.33</v>
@@ -1504,10 +1504,10 @@
         <v>1.1</v>
       </c>
       <c r="AF7">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG7">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK7">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1625,13 +1625,13 @@
         <v>2.71</v>
       </c>
       <c r="R8">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S8">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T8">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="U8">
         <v>2.59</v>
@@ -1658,19 +1658,19 @@
         <v>1.97</v>
       </c>
       <c r="AC8">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AD8">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE8">
         <v>1.09</v>
       </c>
       <c r="AF8">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AG8">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1785,22 +1785,22 @@
         <v>1.68</v>
       </c>
       <c r="Q9">
-        <v>4.4</v>
+        <v>4.46</v>
       </c>
       <c r="R9">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="S9">
         <v>1.25</v>
       </c>
       <c r="T9">
-        <v>3.7</v>
+        <v>3.48</v>
       </c>
       <c r="U9">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="V9">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W9">
         <v>1.12</v>
@@ -1812,25 +1812,25 @@
         <v>1.1</v>
       </c>
       <c r="Z9">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AA9">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB9">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="AC9">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AD9">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE9">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF9">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AG9">
         <v>2.45</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
+        <v>2.05</v>
+      </c>
+      <c r="AK9">
         <v>1.17</v>
-      </c>
-      <c r="AK9">
-        <v>1.16</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1948,25 +1948,25 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="R10">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S10">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="U10">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="V10">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W10">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
         <v>1</v>
@@ -1975,22 +1975,22 @@
         <v>1.25</v>
       </c>
       <c r="Z10">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="AA10">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB10">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC10">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD10">
         <v>1.32</v>
       </c>
       <c r="AE10">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF10">
         <v>1.66</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AK10">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2105,7 +2105,7 @@
         <v>1.4</v>
       </c>
       <c r="O11">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P11">
         <v>6.5</v>
@@ -2117,7 +2117,7 @@
         <v>2.12</v>
       </c>
       <c r="S11">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T11">
         <v>2.59</v>
@@ -2126,7 +2126,7 @@
         <v>3</v>
       </c>
       <c r="V11">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W11">
         <v>1.02</v>
@@ -2141,13 +2141,13 @@
         <v>3.24</v>
       </c>
       <c r="AA11">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AB11">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AC11">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="AD11">
         <v>1.23</v>
@@ -2156,7 +2156,7 @@
         <v>1.06</v>
       </c>
       <c r="AF11">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AG11">
         <v>1.59</v>
@@ -2274,25 +2274,25 @@
         <v>2.63</v>
       </c>
       <c r="Q12">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="R12">
         <v>2.25</v>
       </c>
       <c r="S12">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="U12">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V12">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W12">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X12">
         <v>1.04</v>
@@ -2301,10 +2301,10 @@
         <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AA12">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB12">
         <v>2</v>
@@ -2319,7 +2319,7 @@
         <v>1.11</v>
       </c>
       <c r="AF12">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG12">
         <v>2.15</v>
@@ -2437,55 +2437,55 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>2.95</v>
+        <v>3.44</v>
       </c>
       <c r="R13">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="S13">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="T13">
+        <v>2.53</v>
+      </c>
+      <c r="U13">
         <v>2.91</v>
       </c>
-      <c r="U13">
-        <v>2.62</v>
-      </c>
       <c r="V13">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W13">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y13">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z13">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA13">
-        <v>1.8</v>
+        <v>2.09</v>
       </c>
       <c r="AB13">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AC13">
-        <v>2.92</v>
+        <v>3.57</v>
       </c>
       <c r="AD13">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AE13">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF13">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="AG13">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK13">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2600,25 +2600,25 @@
         <v>6</v>
       </c>
       <c r="Q14">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="R14">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="S14">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T14">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U14">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="V14">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W14">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X14">
         <v>1.01</v>
@@ -2633,13 +2633,13 @@
         <v>1.59</v>
       </c>
       <c r="AB14">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AC14">
         <v>2.43</v>
       </c>
       <c r="AD14">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE14">
         <v>1.15</v>
@@ -2648,7 +2648,7 @@
         <v>1.75</v>
       </c>
       <c r="AG14">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>1.13</v>
       </c>
       <c r="AK14">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.66</v>
+        <v>3.95</v>
       </c>
       <c r="O16">
-        <v>3.72</v>
+        <v>3.55</v>
       </c>
       <c r="P16">
-        <v>2.32</v>
+        <v>1.78</v>
       </c>
       <c r="Q16">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="R16">
-        <v>2.39</v>
+        <v>2.23</v>
       </c>
       <c r="S16">
+        <v>1.28</v>
+      </c>
+      <c r="T16">
+        <v>3.15</v>
+      </c>
+      <c r="U16">
+        <v>2.31</v>
+      </c>
+      <c r="V16">
+        <v>1.51</v>
+      </c>
+      <c r="W16">
+        <v>1.1</v>
+      </c>
+      <c r="X16">
+        <v>1.04</v>
+      </c>
+      <c r="Y16">
         <v>1.18</v>
       </c>
-      <c r="T16">
-        <v>3.82</v>
-      </c>
-      <c r="U16">
-        <v>2.12</v>
-      </c>
-      <c r="V16">
-        <v>1.61</v>
-      </c>
-      <c r="W16">
-        <v>1.13</v>
-      </c>
-      <c r="X16">
-        <v>0</v>
-      </c>
-      <c r="Y16">
-        <v>1.08</v>
-      </c>
       <c r="Z16">
-        <v>5.65</v>
+        <v>4.64</v>
       </c>
       <c r="AA16">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AB16">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="AC16">
-        <v>2.09</v>
+        <v>2.5</v>
       </c>
       <c r="AD16">
+        <v>1.51</v>
+      </c>
+      <c r="AE16">
+        <v>1.22</v>
+      </c>
+      <c r="AF16">
         <v>1.57</v>
       </c>
-      <c r="AE16">
-        <v>1.23</v>
-      </c>
-      <c r="AF16">
-        <v>1.42</v>
-      </c>
       <c r="AG16">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
+        <v>1.21</v>
+      </c>
+      <c r="AK16">
         <v>1.19</v>
-      </c>
-      <c r="AK16">
-        <v>1.41</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="O19">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P19">
-        <v>5.53</v>
+        <v>4.8</v>
       </c>
       <c r="Q19">
-        <v>2.38</v>
+        <v>2.13</v>
       </c>
       <c r="R19">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="S19">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="T19">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="U19">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="V19">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
         <v>1.05</v>
       </c>
       <c r="Y19">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z19">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="AA19">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="AB19">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AC19">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="AD19">
         <v>1.18</v>
       </c>
       <c r="AE19">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF19">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="AG19">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AK19">
-        <v>1.9</v>
+        <v>2.31</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,28 +3569,28 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="O20">
+        <v>3.74</v>
+      </c>
+      <c r="P20">
+        <v>3.35</v>
+      </c>
+      <c r="Q20">
+        <v>2.48</v>
+      </c>
+      <c r="R20">
+        <v>2.31</v>
+      </c>
+      <c r="S20">
+        <v>1.23</v>
+      </c>
+      <c r="T20">
         <v>3.7</v>
       </c>
-      <c r="P20">
-        <v>3.5</v>
-      </c>
-      <c r="Q20">
-        <v>2.3</v>
-      </c>
-      <c r="R20">
-        <v>2.4</v>
-      </c>
-      <c r="S20">
-        <v>1.2</v>
-      </c>
-      <c r="T20">
-        <v>3.42</v>
-      </c>
       <c r="U20">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="V20">
         <v>1.6</v>
@@ -3602,31 +3602,31 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z20">
-        <v>4.85</v>
+        <v>5.5</v>
       </c>
       <c r="AA20">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AB20">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AC20">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AD20">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AE20">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF20">
         <v>1.47</v>
       </c>
       <c r="AG20">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="O21">
         <v>3.5</v>
@@ -3741,7 +3741,7 @@
         <v>2.42</v>
       </c>
       <c r="Q21">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="R21">
         <v>2.25</v>
@@ -3762,25 +3762,25 @@
         <v>1.13</v>
       </c>
       <c r="X21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
         <v>1.11</v>
       </c>
       <c r="Z21">
-        <v>4.8</v>
+        <v>5.26</v>
       </c>
       <c r="AA21">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AB21">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="AC21">
         <v>2.31</v>
       </c>
       <c r="AD21">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE21">
         <v>1.2</v>
@@ -3789,7 +3789,7 @@
         <v>1.4</v>
       </c>
       <c r="AG21">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK21">
         <v>1.44</v>
@@ -3895,25 +3895,25 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="O22">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P22">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="Q22">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="R22">
-        <v>2.28</v>
+        <v>2.43</v>
       </c>
       <c r="S22">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T22">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="U22">
         <v>2.39</v>
@@ -3928,22 +3928,22 @@
         <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z22">
-        <v>4.33</v>
+        <v>4.47</v>
       </c>
       <c r="AA22">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB22">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AC22">
         <v>2.54</v>
       </c>
       <c r="AD22">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE22">
         <v>1.12</v>
@@ -3952,7 +3952,7 @@
         <v>1.54</v>
       </c>
       <c r="AG22">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.25</v>
       </c>
       <c r="AK22">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="O23">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="P23">
-        <v>4.86</v>
+        <v>4.33</v>
       </c>
       <c r="Q23">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="R23">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U23">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="V23">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z23">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AA23">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="AB23">
-        <v>2.23</v>
+        <v>2.52</v>
       </c>
       <c r="AC23">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="AD23">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="AE23">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AF23">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AG23">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK23">
-        <v>1.92</v>
+        <v>2.21</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4547,34 +4547,34 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="O26">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P26">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q26">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="R26">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S26">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="T26">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="U26">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="V26">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W26">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
         <v>1.01</v>
@@ -4586,25 +4586,25 @@
         <v>3.14</v>
       </c>
       <c r="AA26">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AB26">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AC26">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD26">
         <v>1.26</v>
       </c>
       <c r="AE26">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF26">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AG26">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AK26">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="O27">
         <v>3.5</v>
@@ -4719,55 +4719,55 @@
         <v>2.62</v>
       </c>
       <c r="Q27">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R27">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S27">
         <v>1.34</v>
       </c>
       <c r="T27">
-        <v>2.99</v>
+        <v>3.13</v>
       </c>
       <c r="U27">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="V27">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z27">
-        <v>3.62</v>
+        <v>3.54</v>
       </c>
       <c r="AA27">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AB27">
         <v>2</v>
       </c>
       <c r="AC27">
-        <v>2.89</v>
+        <v>3.09</v>
       </c>
       <c r="AD27">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE27">
         <v>1.08</v>
       </c>
       <c r="AF27">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG27">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.3</v>
       </c>
       <c r="AK27">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4882,16 +4882,16 @@
         <v>3.6</v>
       </c>
       <c r="Q28">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="R28">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="S28">
         <v>1.38</v>
       </c>
       <c r="T28">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="U28">
         <v>2.82</v>
@@ -4903,7 +4903,7 @@
         <v>1.03</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y28">
         <v>1.26</v>
@@ -4927,10 +4927,10 @@
         <v>1.05</v>
       </c>
       <c r="AF28">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AG28">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="O30">
+        <v>3.3</v>
+      </c>
+      <c r="P30">
+        <v>3.9</v>
+      </c>
+      <c r="Q30">
+        <v>2.36</v>
+      </c>
+      <c r="R30">
+        <v>2.1</v>
+      </c>
+      <c r="S30">
+        <v>1.33</v>
+      </c>
+      <c r="T30">
+        <v>3</v>
+      </c>
+      <c r="U30">
+        <v>2.7</v>
+      </c>
+      <c r="V30">
+        <v>1.38</v>
+      </c>
+      <c r="W30">
+        <v>1.08</v>
+      </c>
+      <c r="X30">
+        <v>1.01</v>
+      </c>
+      <c r="Y30">
+        <v>1.24</v>
+      </c>
+      <c r="Z30">
         <v>3.59</v>
       </c>
-      <c r="P30">
-        <v>4</v>
-      </c>
-      <c r="Q30">
-        <v>0</v>
-      </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="T30">
-        <v>0</v>
-      </c>
-      <c r="U30">
-        <v>0</v>
-      </c>
-      <c r="V30">
-        <v>0</v>
-      </c>
-      <c r="W30">
-        <v>0</v>
-      </c>
-      <c r="X30">
-        <v>0</v>
-      </c>
-      <c r="Y30">
-        <v>0</v>
-      </c>
-      <c r="Z30">
-        <v>0</v>
-      </c>
       <c r="AA30">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="O31">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="P31">
-        <v>3.3</v>
+        <v>3.56</v>
       </c>
       <c r="Q31">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="R31">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="S31">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="T31">
-        <v>3.03</v>
+        <v>2.89</v>
       </c>
       <c r="U31">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="V31">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W31">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X31">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
         <v>1.3</v>
       </c>
       <c r="Z31">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AA31">
         <v>1.85</v>
       </c>
       <c r="AB31">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AC31">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AD31">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE31">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF31">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG31">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK31">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O32">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="P32">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="Q32">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="R32">
+        <v>1.83</v>
+      </c>
+      <c r="S32">
+        <v>1.52</v>
+      </c>
+      <c r="T32">
+        <v>2.63</v>
+      </c>
+      <c r="U32">
+        <v>3.32</v>
+      </c>
+      <c r="V32">
+        <v>1.26</v>
+      </c>
+      <c r="W32">
+        <v>1.03</v>
+      </c>
+      <c r="X32">
+        <v>1.04</v>
+      </c>
+      <c r="Y32">
+        <v>1.38</v>
+      </c>
+      <c r="Z32">
+        <v>2.62</v>
+      </c>
+      <c r="AA32">
+        <v>2.29</v>
+      </c>
+      <c r="AB32">
+        <v>1.48</v>
+      </c>
+      <c r="AC32">
+        <v>4.2</v>
+      </c>
+      <c r="AD32">
+        <v>1.15</v>
+      </c>
+      <c r="AE32">
+        <v>1.01</v>
+      </c>
+      <c r="AF32">
         <v>2</v>
       </c>
-      <c r="S32">
-        <v>1.5</v>
-      </c>
-      <c r="T32">
-        <v>2.5</v>
-      </c>
-      <c r="U32">
-        <v>3.42</v>
-      </c>
-      <c r="V32">
-        <v>1.23</v>
-      </c>
-      <c r="W32">
-        <v>1.04</v>
-      </c>
-      <c r="X32">
-        <v>1.05</v>
-      </c>
-      <c r="Y32">
-        <v>1.41</v>
-      </c>
-      <c r="Z32">
-        <v>2.52</v>
-      </c>
-      <c r="AA32">
-        <v>2.39</v>
-      </c>
-      <c r="AB32">
-        <v>1.51</v>
-      </c>
-      <c r="AC32">
-        <v>4.45</v>
-      </c>
-      <c r="AD32">
-        <v>1.18</v>
-      </c>
-      <c r="AE32">
-        <v>1.03</v>
-      </c>
-      <c r="AF32">
-        <v>2.1</v>
-      </c>
       <c r="AG32">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AK32">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="O33">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="P33">
         <v>3.1</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,19 +5851,19 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="O34">
         <v>3.2</v>
       </c>
       <c r="P34">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="Q34">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="R34">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="S34">
         <v>1.43</v>
@@ -5887,7 +5887,7 @@
         <v>1.31</v>
       </c>
       <c r="Z34">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="AA34">
         <v>2.05</v>
@@ -5899,7 +5899,7 @@
         <v>3.74</v>
       </c>
       <c r="AD34">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE34">
         <v>1.02</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL41">
         <v>0</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU49"/>
+  <dimension ref="A1:AU50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Doqarah</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AK9">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-09-03 13:15:00</t>
+          <t>2026-09-03 13:00:00</t>
         </is>
       </c>
     </row>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q10">
+        <v>4.46</v>
+      </c>
+      <c r="R10">
+        <v>2.36</v>
+      </c>
+      <c r="S10">
+        <v>1.25</v>
+      </c>
+      <c r="T10">
+        <v>3.48</v>
+      </c>
+      <c r="U10">
+        <v>2.18</v>
+      </c>
+      <c r="V10">
+        <v>1.6</v>
+      </c>
+      <c r="W10">
+        <v>1.12</v>
+      </c>
+      <c r="X10">
+        <v>1.02</v>
+      </c>
+      <c r="Y10">
+        <v>1.1</v>
+      </c>
+      <c r="Z10">
+        <v>5.4</v>
+      </c>
+      <c r="AA10">
+        <v>1.44</v>
+      </c>
+      <c r="AB10">
         <v>2.42</v>
       </c>
-      <c r="R10">
-        <v>2.16</v>
-      </c>
-      <c r="S10">
-        <v>1.3</v>
-      </c>
-      <c r="T10">
-        <v>2.96</v>
-      </c>
-      <c r="U10">
-        <v>2.56</v>
-      </c>
-      <c r="V10">
-        <v>1.42</v>
-      </c>
-      <c r="W10">
-        <v>1.06</v>
-      </c>
-      <c r="X10">
-        <v>1</v>
-      </c>
-      <c r="Y10">
+      <c r="AC10">
+        <v>2.17</v>
+      </c>
+      <c r="AD10">
+        <v>1.62</v>
+      </c>
+      <c r="AE10">
         <v>1.25</v>
       </c>
-      <c r="Z10">
-        <v>3.74</v>
-      </c>
-      <c r="AA10">
-        <v>1.79</v>
-      </c>
-      <c r="AB10">
-        <v>1.98</v>
-      </c>
-      <c r="AC10">
-        <v>2.88</v>
-      </c>
-      <c r="AD10">
-        <v>1.32</v>
-      </c>
-      <c r="AE10">
-        <v>1.09</v>
-      </c>
       <c r="AF10">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="AG10">
-        <v>2.07</v>
+        <v>2.45</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.26</v>
+        <v>2.05</v>
       </c>
       <c r="AK10">
-        <v>1.79</v>
+        <v>1.17</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-09-03 13:30:00</t>
+          <t>2026-09-03 13:15:00</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.97</v>
+        <v>2.42</v>
       </c>
       <c r="R11">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="S11">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T11">
-        <v>2.59</v>
+        <v>2.96</v>
       </c>
       <c r="U11">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="V11">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W11">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
         <v>1</v>
       </c>
       <c r="Y11">
+        <v>1.25</v>
+      </c>
+      <c r="Z11">
+        <v>3.74</v>
+      </c>
+      <c r="AA11">
+        <v>1.79</v>
+      </c>
+      <c r="AB11">
+        <v>1.98</v>
+      </c>
+      <c r="AC11">
+        <v>2.88</v>
+      </c>
+      <c r="AD11">
         <v>1.32</v>
       </c>
-      <c r="Z11">
-        <v>3.24</v>
-      </c>
-      <c r="AA11">
-        <v>1.98</v>
-      </c>
-      <c r="AB11">
-        <v>1.74</v>
-      </c>
-      <c r="AC11">
-        <v>3.42</v>
-      </c>
-      <c r="AD11">
-        <v>1.23</v>
-      </c>
       <c r="AE11">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF11">
-        <v>2.15</v>
+        <v>1.66</v>
       </c>
       <c r="AG11">
-        <v>1.59</v>
+        <v>2.07</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AK11">
-        <v>2.7</v>
+        <v>1.79</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-09-03 14:00:00</t>
+          <t>2026-09-03 13:30:00</t>
         </is>
       </c>
     </row>
@@ -2223,22 +2223,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="O12">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P12">
-        <v>2.63</v>
+        <v>6.5</v>
       </c>
       <c r="Q12">
-        <v>3.1</v>
+        <v>1.97</v>
       </c>
       <c r="R12">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="S12">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T12">
-        <v>2.94</v>
+        <v>2.59</v>
       </c>
       <c r="U12">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="V12">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W12">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X12">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="Z12">
-        <v>3.75</v>
+        <v>3.24</v>
       </c>
       <c r="AA12">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AB12">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AC12">
-        <v>2.85</v>
+        <v>3.42</v>
       </c>
       <c r="AD12">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AE12">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF12">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AG12">
-        <v>2.15</v>
+        <v>1.59</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AK12">
-        <v>1.53</v>
+        <v>2.7</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2386,22 +2386,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,31 +2428,31 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q13">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="R13">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S13">
+        <v>1.35</v>
+      </c>
+      <c r="T13">
+        <v>2.94</v>
+      </c>
+      <c r="U13">
+        <v>2.62</v>
+      </c>
+      <c r="V13">
         <v>1.43</v>
-      </c>
-      <c r="T13">
-        <v>2.53</v>
-      </c>
-      <c r="U13">
-        <v>2.91</v>
-      </c>
-      <c r="V13">
-        <v>1.35</v>
       </c>
       <c r="W13">
         <v>1.05</v>
@@ -2461,31 +2461,31 @@
         <v>1.04</v>
       </c>
       <c r="Y13">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="AA13">
-        <v>2.09</v>
+        <v>1.75</v>
       </c>
       <c r="AB13">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AC13">
-        <v>3.57</v>
+        <v>2.85</v>
       </c>
       <c r="AD13">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AE13">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF13">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AG13">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1.3</v>
       </c>
       <c r="AK13">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>1.9</v>
+        <v>3.44</v>
       </c>
       <c r="R14">
-        <v>2.39</v>
+        <v>2.14</v>
       </c>
       <c r="S14">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="T14">
-        <v>3.5</v>
+        <v>2.53</v>
       </c>
       <c r="U14">
-        <v>2.33</v>
+        <v>2.91</v>
       </c>
       <c r="V14">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="W14">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="Z14">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA14">
-        <v>1.59</v>
+        <v>2.09</v>
       </c>
       <c r="AB14">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="AC14">
-        <v>2.43</v>
+        <v>3.57</v>
       </c>
       <c r="AD14">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="AE14">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AF14">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG14">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AK14">
-        <v>2.6</v>
+        <v>1.36</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-09-03 14:30:00</t>
+          <t>2026-09-03 14:00:00</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.8</v>
+        <v>3.95</v>
       </c>
       <c r="O17">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P17">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="Q17">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="R17">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="S17">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T17">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="U17">
-        <v>2.41</v>
+        <v>2.31</v>
       </c>
       <c r="V17">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W17">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z17">
-        <v>3.94</v>
+        <v>4.64</v>
       </c>
       <c r="AA17">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AB17">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="AC17">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AD17">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AE17">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AF17">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG17">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK17">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-09-03 15:00:00</t>
+          <t>2026-09-03 14:30:00</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="T19">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="V19">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X19">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y19">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z19">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA19">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AB19">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC19">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD19">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE19">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF19">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG19">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK19">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,80 +3569,80 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="O20">
-        <v>3.74</v>
+        <v>3.2</v>
       </c>
       <c r="P20">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="Q20">
-        <v>2.48</v>
+        <v>2.13</v>
       </c>
       <c r="R20">
+        <v>1.93</v>
+      </c>
+      <c r="S20">
+        <v>1.52</v>
+      </c>
+      <c r="T20">
+        <v>2.29</v>
+      </c>
+      <c r="U20">
+        <v>3.18</v>
+      </c>
+      <c r="V20">
+        <v>1.28</v>
+      </c>
+      <c r="W20">
+        <v>1.07</v>
+      </c>
+      <c r="X20">
+        <v>1.05</v>
+      </c>
+      <c r="Y20">
+        <v>1.37</v>
+      </c>
+      <c r="Z20">
+        <v>2.66</v>
+      </c>
+      <c r="AA20">
+        <v>2.21</v>
+      </c>
+      <c r="AB20">
+        <v>1.59</v>
+      </c>
+      <c r="AC20">
+        <v>3.9</v>
+      </c>
+      <c r="AD20">
+        <v>1.18</v>
+      </c>
+      <c r="AE20">
+        <v>1.02</v>
+      </c>
+      <c r="AF20">
+        <v>2.32</v>
+      </c>
+      <c r="AG20">
+        <v>1.53</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>1.29</v>
+      </c>
+      <c r="AK20">
         <v>2.31</v>
-      </c>
-      <c r="S20">
-        <v>1.23</v>
-      </c>
-      <c r="T20">
-        <v>3.7</v>
-      </c>
-      <c r="U20">
-        <v>2.18</v>
-      </c>
-      <c r="V20">
-        <v>1.6</v>
-      </c>
-      <c r="W20">
-        <v>1.15</v>
-      </c>
-      <c r="X20">
-        <v>1.01</v>
-      </c>
-      <c r="Y20">
-        <v>1.13</v>
-      </c>
-      <c r="Z20">
-        <v>5.5</v>
-      </c>
-      <c r="AA20">
-        <v>1.57</v>
-      </c>
-      <c r="AB20">
-        <v>2.35</v>
-      </c>
-      <c r="AC20">
-        <v>2.33</v>
-      </c>
-      <c r="AD20">
-        <v>1.55</v>
-      </c>
-      <c r="AE20">
-        <v>1.2</v>
-      </c>
-      <c r="AF20">
-        <v>1.47</v>
-      </c>
-      <c r="AG20">
-        <v>2.55</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.25</v>
-      </c>
-      <c r="AK20">
-        <v>1.77</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="O21">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="P21">
-        <v>2.42</v>
+        <v>3.35</v>
       </c>
       <c r="Q21">
-        <v>3.17</v>
+        <v>2.48</v>
       </c>
       <c r="R21">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="S21">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="T21">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="U21">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="V21">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W21">
+        <v>1.15</v>
+      </c>
+      <c r="X21">
+        <v>1.01</v>
+      </c>
+      <c r="Y21">
         <v>1.13</v>
       </c>
-      <c r="X21">
-        <v>1.02</v>
-      </c>
-      <c r="Y21">
-        <v>1.11</v>
-      </c>
       <c r="Z21">
-        <v>5.26</v>
+        <v>5.5</v>
       </c>
       <c r="AA21">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AB21">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="AC21">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AD21">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AE21">
         <v>1.2</v>
       </c>
       <c r="AF21">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AG21">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2026-09-03 15:30:00</t>
+          <t>2026-09-03 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,80 +3895,80 @@
         </is>
       </c>
       <c r="N22">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="O22">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P22">
-        <v>3.1</v>
+        <v>2.42</v>
       </c>
       <c r="Q22">
-        <v>2.55</v>
+        <v>3.17</v>
       </c>
       <c r="R22">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="S22">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T22">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="U22">
-        <v>2.39</v>
+        <v>2.21</v>
       </c>
       <c r="V22">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="W22">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X22">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
+        <v>1.11</v>
+      </c>
+      <c r="Z22">
+        <v>5.26</v>
+      </c>
+      <c r="AA22">
+        <v>1.5</v>
+      </c>
+      <c r="AB22">
+        <v>2.48</v>
+      </c>
+      <c r="AC22">
+        <v>2.31</v>
+      </c>
+      <c r="AD22">
+        <v>1.62</v>
+      </c>
+      <c r="AE22">
         <v>1.2</v>
       </c>
-      <c r="Z22">
-        <v>4.47</v>
-      </c>
-      <c r="AA22">
-        <v>1.67</v>
-      </c>
-      <c r="AB22">
-        <v>2.23</v>
-      </c>
-      <c r="AC22">
-        <v>2.54</v>
-      </c>
-      <c r="AD22">
+      <c r="AF22">
+        <v>1.4</v>
+      </c>
+      <c r="AG22">
+        <v>2.7</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>1.22</v>
+      </c>
+      <c r="AK22">
         <v>1.44</v>
-      </c>
-      <c r="AE22">
-        <v>1.12</v>
-      </c>
-      <c r="AF22">
-        <v>1.54</v>
-      </c>
-      <c r="AG22">
-        <v>2.3</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>1.25</v>
-      </c>
-      <c r="AK22">
-        <v>1.73</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="O23">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="P23">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="Q23">
-        <v>2.09</v>
+        <v>2.55</v>
       </c>
       <c r="R23">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="S23">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T23">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="U23">
-        <v>2.16</v>
+        <v>2.39</v>
       </c>
       <c r="V23">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="W23">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
+        <v>1.2</v>
+      </c>
+      <c r="Z23">
+        <v>4.47</v>
+      </c>
+      <c r="AA23">
+        <v>1.67</v>
+      </c>
+      <c r="AB23">
+        <v>2.23</v>
+      </c>
+      <c r="AC23">
+        <v>2.54</v>
+      </c>
+      <c r="AD23">
+        <v>1.44</v>
+      </c>
+      <c r="AE23">
         <v>1.12</v>
       </c>
-      <c r="Z23">
-        <v>5.4</v>
-      </c>
-      <c r="AA23">
-        <v>1.41</v>
-      </c>
-      <c r="AB23">
-        <v>2.52</v>
-      </c>
-      <c r="AC23">
-        <v>2.16</v>
-      </c>
-      <c r="AD23">
-        <v>1.66</v>
-      </c>
-      <c r="AE23">
-        <v>1.22</v>
-      </c>
       <c r="AF23">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AG23">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK23">
-        <v>2.21</v>
+        <v>1.73</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="O24">
         <v>4</v>
       </c>
       <c r="P24">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="O25">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P25">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4500,12 +4500,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.45</v>
+        <v>1.62</v>
       </c>
       <c r="O26">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="P26">
-        <v>2.15</v>
+        <v>5.5</v>
       </c>
       <c r="Q26">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S26">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U26">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="V26">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W26">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y26">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z26">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA26">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB26">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC26">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD26">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE26">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF26">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG26">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK26">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-09-03 15:45:00</t>
+          <t>2026-09-03 15:30:00</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,80 +4710,80 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.5</v>
+        <v>3.45</v>
       </c>
       <c r="O27">
+        <v>3.35</v>
+      </c>
+      <c r="P27">
+        <v>2.15</v>
+      </c>
+      <c r="Q27">
+        <v>4.1</v>
+      </c>
+      <c r="R27">
+        <v>2.07</v>
+      </c>
+      <c r="S27">
+        <v>1.41</v>
+      </c>
+      <c r="T27">
+        <v>2.9</v>
+      </c>
+      <c r="U27">
+        <v>3.05</v>
+      </c>
+      <c r="V27">
+        <v>1.38</v>
+      </c>
+      <c r="W27">
+        <v>1.05</v>
+      </c>
+      <c r="X27">
+        <v>1.01</v>
+      </c>
+      <c r="Y27">
+        <v>1.3</v>
+      </c>
+      <c r="Z27">
+        <v>3.14</v>
+      </c>
+      <c r="AA27">
+        <v>2.07</v>
+      </c>
+      <c r="AB27">
+        <v>1.86</v>
+      </c>
+      <c r="AC27">
         <v>3.5</v>
       </c>
-      <c r="P27">
-        <v>2.62</v>
-      </c>
-      <c r="Q27">
-        <v>3.1</v>
-      </c>
-      <c r="R27">
-        <v>2.28</v>
-      </c>
-      <c r="S27">
+      <c r="AD27">
+        <v>1.26</v>
+      </c>
+      <c r="AE27">
+        <v>1.09</v>
+      </c>
+      <c r="AF27">
+        <v>1.79</v>
+      </c>
+      <c r="AG27">
+        <v>1.94</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>1.35</v>
+      </c>
+      <c r="AK27">
         <v>1.34</v>
-      </c>
-      <c r="T27">
-        <v>3.13</v>
-      </c>
-      <c r="U27">
-        <v>2.69</v>
-      </c>
-      <c r="V27">
-        <v>1.41</v>
-      </c>
-      <c r="W27">
-        <v>1.08</v>
-      </c>
-      <c r="X27">
-        <v>1.02</v>
-      </c>
-      <c r="Y27">
-        <v>1.26</v>
-      </c>
-      <c r="Z27">
-        <v>3.54</v>
-      </c>
-      <c r="AA27">
-        <v>1.87</v>
-      </c>
-      <c r="AB27">
-        <v>2</v>
-      </c>
-      <c r="AC27">
-        <v>3.09</v>
-      </c>
-      <c r="AD27">
-        <v>1.33</v>
-      </c>
-      <c r="AE27">
-        <v>1.08</v>
-      </c>
-      <c r="AF27">
-        <v>1.63</v>
-      </c>
-      <c r="AG27">
-        <v>2.14</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.3</v>
-      </c>
-      <c r="AK27">
-        <v>1.52</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.94</v>
+        <v>2.5</v>
       </c>
       <c r="O28">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
-        <v>3.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q28">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="R28">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="S28">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="T28">
-        <v>2.88</v>
+        <v>3.13</v>
       </c>
       <c r="U28">
-        <v>2.82</v>
+        <v>2.69</v>
       </c>
       <c r="V28">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="W28">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X28">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
         <v>1.26</v>
       </c>
       <c r="Z28">
-        <v>3.2</v>
+        <v>3.54</v>
       </c>
       <c r="AA28">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AB28">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AC28">
-        <v>3.28</v>
+        <v>3.09</v>
       </c>
       <c r="AD28">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE28">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF28">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AG28">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK28">
-        <v>1.83</v>
+        <v>1.52</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G29">
@@ -5032,68 +5032,68 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-09-03 16:00:00</t>
+          <t>2026-09-03 15:45:00</t>
         </is>
       </c>
     </row>
@@ -5157,22 +5157,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="G30">
@@ -5195,68 +5195,68 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N30">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O30">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P30">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q30">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="R30">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S30">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U30">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V30">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W30">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y30">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z30">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="AA30">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB30">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC30">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD30">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE30">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG30">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK30">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5320,22 +5320,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="O31">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="P31">
-        <v>3.56</v>
+        <v>3.9</v>
       </c>
       <c r="Q31">
-        <v>2.49</v>
+        <v>2.36</v>
       </c>
       <c r="R31">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S31">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="T31">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="U31">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="V31">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W31">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X31">
         <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z31">
+        <v>3.59</v>
+      </c>
+      <c r="AA31">
+        <v>2.05</v>
+      </c>
+      <c r="AB31">
+        <v>1.75</v>
+      </c>
+      <c r="AC31">
         <v>3.1</v>
       </c>
-      <c r="AA31">
-        <v>1.85</v>
-      </c>
-      <c r="AB31">
-        <v>1.82</v>
-      </c>
-      <c r="AC31">
-        <v>3</v>
-      </c>
       <c r="AD31">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE31">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF31">
         <v>1.73</v>
       </c>
       <c r="AG31">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="O32">
-        <v>2.9</v>
+        <v>3.46</v>
       </c>
       <c r="P32">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="Q32">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="R32">
-        <v>1.83</v>
+        <v>2.11</v>
       </c>
       <c r="S32">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="T32">
-        <v>2.63</v>
+        <v>2.89</v>
       </c>
       <c r="U32">
-        <v>3.32</v>
+        <v>2.85</v>
       </c>
       <c r="V32">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="W32">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="Z32">
-        <v>2.62</v>
+        <v>3.48</v>
       </c>
       <c r="AA32">
-        <v>2.29</v>
+        <v>1.85</v>
       </c>
       <c r="AB32">
-        <v>1.48</v>
+        <v>1.82</v>
       </c>
       <c r="AC32">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="AD32">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AE32">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF32">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AG32">
-        <v>1.68</v>
+        <v>2.05</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AK32">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-09-03 17:00:00</t>
+          <t>2026-09-03 16:00:00</t>
         </is>
       </c>
     </row>
@@ -5641,27 +5641,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O33">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P33">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Q33">
-        <v>3.04</v>
+        <v>2.7</v>
       </c>
       <c r="R33">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="S33">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="T33">
-        <v>2.32</v>
+        <v>2.63</v>
       </c>
       <c r="U33">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="V33">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W33">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X33">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="Z33">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="AA33">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="AB33">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AC33">
-        <v>4.54</v>
+        <v>4.2</v>
       </c>
       <c r="AD33">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE33">
         <v>1.01</v>
       </c>
       <c r="AF33">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG33">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AK33">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-09-03 18:30:00</t>
+          <t>2026-09-03 17:00:00</t>
         </is>
       </c>
     </row>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,65 +5851,65 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="O34">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P34">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q34">
-        <v>2.55</v>
+        <v>3.04</v>
       </c>
       <c r="R34">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="S34">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="T34">
-        <v>2.74</v>
+        <v>2.32</v>
       </c>
       <c r="U34">
-        <v>3.16</v>
+        <v>3.34</v>
       </c>
       <c r="V34">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="W34">
         <v>1.02</v>
       </c>
       <c r="X34">
+        <v>1.05</v>
+      </c>
+      <c r="Y34">
+        <v>1.44</v>
+      </c>
+      <c r="Z34">
+        <v>2.49</v>
+      </c>
+      <c r="AA34">
+        <v>2.35</v>
+      </c>
+      <c r="AB34">
+        <v>1.57</v>
+      </c>
+      <c r="AC34">
+        <v>4.54</v>
+      </c>
+      <c r="AD34">
+        <v>1.14</v>
+      </c>
+      <c r="AE34">
         <v>1.01</v>
       </c>
-      <c r="Y34">
-        <v>1.31</v>
-      </c>
-      <c r="Z34">
-        <v>3.15</v>
-      </c>
-      <c r="AA34">
-        <v>2.05</v>
-      </c>
-      <c r="AB34">
+      <c r="AF34">
+        <v>2.01</v>
+      </c>
+      <c r="AG34">
         <v>1.7</v>
       </c>
-      <c r="AC34">
-        <v>3.74</v>
-      </c>
-      <c r="AD34">
-        <v>1.19</v>
-      </c>
-      <c r="AE34">
-        <v>1.02</v>
-      </c>
-      <c r="AF34">
-        <v>1.88</v>
-      </c>
-      <c r="AG34">
-        <v>1.82</v>
-      </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK34">
-        <v>1.83</v>
+        <v>1.54</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-09-03 20:00:00</t>
+          <t>2026-09-03 18:30:00</t>
         </is>
       </c>
     </row>
@@ -5967,27 +5967,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-09-03 21:00:00</t>
+          <t>2026-09-03 20:00:00</t>
         </is>
       </c>
     </row>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Safa</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Safa</t>
         </is>
       </c>
       <c r="G40">
@@ -6950,22 +6950,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P41">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R41">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="S41">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="T41">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="U41">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="V41">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W41">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X41">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y41">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z41">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AA41">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AB41">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC41">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="AD41">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE41">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF41">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG41">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK41">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7113,22 +7113,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G46">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G47">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,141 +8264,304 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
+          <t>Métlaoui</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Hammam-Sousse</t>
+        </is>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0</v>
+      </c>
+      <c r="X49">
+        <v>0</v>
+      </c>
+      <c r="Y49">
+        <v>0</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+      <c r="AA49">
+        <v>0</v>
+      </c>
+      <c r="AB49">
+        <v>0</v>
+      </c>
+      <c r="AC49">
+        <v>0</v>
+      </c>
+      <c r="AD49">
+        <v>0</v>
+      </c>
+      <c r="AE49">
+        <v>0</v>
+      </c>
+      <c r="AF49">
+        <v>0</v>
+      </c>
+      <c r="AG49">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>0</v>
+      </c>
+      <c r="AK49">
+        <v>0</v>
+      </c>
+      <c r="AL49">
+        <v>0</v>
+      </c>
+      <c r="AM49">
+        <v>-1</v>
+      </c>
+      <c r="AN49">
+        <v>-1</v>
+      </c>
+      <c r="AO49">
+        <v>-1</v>
+      </c>
+      <c r="AP49">
+        <v>-1</v>
+      </c>
+      <c r="AQ49">
+        <v>0</v>
+      </c>
+      <c r="AR49">
+        <v>0</v>
+      </c>
+      <c r="AS49">
+        <v>0</v>
+      </c>
+      <c r="AT49">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>2026-09-03 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Tunisia Ligue 1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>Ben Guerdane</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>CS Sfaxien</t>
         </is>
       </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>0</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49" t="inlineStr">
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
-      <c r="O49">
-        <v>0</v>
-      </c>
-      <c r="P49">
-        <v>0</v>
-      </c>
-      <c r="Q49">
-        <v>0</v>
-      </c>
-      <c r="R49">
-        <v>0</v>
-      </c>
-      <c r="S49">
-        <v>0</v>
-      </c>
-      <c r="T49">
-        <v>0</v>
-      </c>
-      <c r="U49">
-        <v>0</v>
-      </c>
-      <c r="V49">
-        <v>0</v>
-      </c>
-      <c r="W49">
-        <v>0</v>
-      </c>
-      <c r="X49">
-        <v>0</v>
-      </c>
-      <c r="Y49">
-        <v>0</v>
-      </c>
-      <c r="Z49">
-        <v>0</v>
-      </c>
-      <c r="AA49">
-        <v>0</v>
-      </c>
-      <c r="AB49">
-        <v>0</v>
-      </c>
-      <c r="AC49">
-        <v>0</v>
-      </c>
-      <c r="AD49">
-        <v>0</v>
-      </c>
-      <c r="AE49">
-        <v>0</v>
-      </c>
-      <c r="AF49">
-        <v>0</v>
-      </c>
-      <c r="AG49">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>0</v>
-      </c>
-      <c r="AK49">
-        <v>0</v>
-      </c>
-      <c r="AL49">
-        <v>0</v>
-      </c>
-      <c r="AM49">
-        <v>-1</v>
-      </c>
-      <c r="AN49">
-        <v>-1</v>
-      </c>
-      <c r="AO49">
-        <v>-1</v>
-      </c>
-      <c r="AP49">
-        <v>-1</v>
-      </c>
-      <c r="AQ49">
-        <v>0</v>
-      </c>
-      <c r="AR49">
-        <v>0</v>
-      </c>
-      <c r="AS49">
-        <v>0</v>
-      </c>
-      <c r="AT49">
-        <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0</v>
+      </c>
+      <c r="X50">
+        <v>0</v>
+      </c>
+      <c r="Y50">
+        <v>0</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+      <c r="AA50">
+        <v>0</v>
+      </c>
+      <c r="AB50">
+        <v>0</v>
+      </c>
+      <c r="AC50">
+        <v>0</v>
+      </c>
+      <c r="AD50">
+        <v>0</v>
+      </c>
+      <c r="AE50">
+        <v>0</v>
+      </c>
+      <c r="AF50">
+        <v>0</v>
+      </c>
+      <c r="AG50">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>0</v>
+      </c>
+      <c r="AK50">
+        <v>0</v>
+      </c>
+      <c r="AL50">
+        <v>0</v>
+      </c>
+      <c r="AM50">
+        <v>-1</v>
+      </c>
+      <c r="AN50">
+        <v>-1</v>
+      </c>
+      <c r="AO50">
+        <v>-1</v>
+      </c>
+      <c r="AP50">
+        <v>-1</v>
+      </c>
+      <c r="AQ50">
+        <v>0</v>
+      </c>
+      <c r="AR50">
+        <v>0</v>
+      </c>
+      <c r="AS50">
+        <v>0</v>
+      </c>
+      <c r="AT50">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
         <is>
           <t>2026-09-03 21:00:00</t>
         </is>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="O3">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P3">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q3">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="R3">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="S3">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T3">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="U3">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V3">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z3">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA3">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB3">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC3">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="AD3">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE3">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF3">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG3">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -970,34 +970,34 @@
         <v>2.75</v>
       </c>
       <c r="Q4">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="R4">
-        <v>2.22</v>
+        <v>2.46</v>
       </c>
       <c r="S4">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="T4">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="U4">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="V4">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W4">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
         <v>1.13</v>
       </c>
       <c r="Z4">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA4">
         <v>1.54</v>
@@ -1006,19 +1006,19 @@
         <v>2.32</v>
       </c>
       <c r="AC4">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AD4">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AE4">
         <v>1.22</v>
       </c>
       <c r="AF4">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG4">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AK4">
         <v>1.53</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1939,34 +1939,34 @@
         </is>
       </c>
       <c r="N10">
+        <v>4.3</v>
+      </c>
+      <c r="O10">
         <v>4.05</v>
       </c>
-      <c r="O10">
-        <v>3.95</v>
-      </c>
       <c r="P10">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="Q10">
-        <v>4.46</v>
+        <v>4.5</v>
       </c>
       <c r="R10">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="S10">
         <v>1.25</v>
       </c>
       <c r="T10">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="U10">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V10">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W10">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X10">
         <v>1.02</v>
@@ -1975,16 +1975,16 @@
         <v>1.1</v>
       </c>
       <c r="Z10">
-        <v>5.4</v>
+        <v>5.22</v>
       </c>
       <c r="AA10">
         <v>1.44</v>
       </c>
       <c r="AB10">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="AC10">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AD10">
         <v>1.62</v>
@@ -1993,10 +1993,10 @@
         <v>1.25</v>
       </c>
       <c r="AF10">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AG10">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>2.05</v>
+        <v>1.25</v>
       </c>
       <c r="AK10">
         <v>1.17</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="O13">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P13">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -2443,49 +2443,49 @@
         <v>2.25</v>
       </c>
       <c r="S13">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="T13">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="U13">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="V13">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="W13">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X13">
         <v>1.04</v>
       </c>
       <c r="Y13">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z13">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="AA13">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AB13">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC13">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="AD13">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AE13">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF13">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG13">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
+        <v>1.83</v>
+      </c>
+      <c r="AK13">
         <v>1.3</v>
-      </c>
-      <c r="AK13">
-        <v>1.53</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2600,55 +2600,55 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="R14">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="S14">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T14">
-        <v>2.53</v>
+        <v>2.87</v>
       </c>
       <c r="U14">
-        <v>2.91</v>
+        <v>2.5</v>
       </c>
       <c r="V14">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z14">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AA14">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="AB14">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC14">
-        <v>3.57</v>
+        <v>3.43</v>
       </c>
       <c r="AD14">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE14">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF14">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AG14">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK14">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.38</v>
+        <v>1.76</v>
       </c>
       <c r="O15">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="P15">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Q15">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="R15">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="S15">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T15">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U15">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="V15">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W15">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z15">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AA15">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AB15">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AC15">
-        <v>2.43</v>
+        <v>2.59</v>
       </c>
       <c r="AD15">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AE15">
         <v>1.15</v>
       </c>
       <c r="AF15">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AG15">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AK15">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3243,16 +3243,16 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O18">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q18">
-        <v>3.7</v>
+        <v>3.37</v>
       </c>
       <c r="R18">
         <v>2.24</v>
@@ -3261,40 +3261,40 @@
         <v>1.3</v>
       </c>
       <c r="T18">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="U18">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="V18">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W18">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z18">
-        <v>3.94</v>
+        <v>4.09</v>
       </c>
       <c r="AA18">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AB18">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AC18">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AD18">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE18">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF18">
         <v>1.56</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK18">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3732,22 +3732,22 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O21">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="P21">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="Q21">
+        <v>2.5</v>
+      </c>
+      <c r="R21">
         <v>2.48</v>
       </c>
-      <c r="R21">
-        <v>2.31</v>
-      </c>
       <c r="S21">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T21">
         <v>3.7</v>
@@ -3756,37 +3756,37 @@
         <v>2.18</v>
       </c>
       <c r="V21">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W21">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z21">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA21">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AB21">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AC21">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AD21">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AE21">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF21">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AG21">
         <v>2.55</v>
@@ -3805,7 +3805,7 @@
         <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="O25">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P25">
-        <v>5</v>
+        <v>5.03</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4423,10 +4423,10 @@
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC25">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="O26">
-        <v>3.9</v>
+        <v>4.48</v>
       </c>
       <c r="P26">
-        <v>5.5</v>
+        <v>5.85</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -4876,61 +4876,61 @@
         <v>2.5</v>
       </c>
       <c r="O28">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="Q28">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R28">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S28">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T28">
-        <v>3.13</v>
+        <v>2.95</v>
       </c>
       <c r="U28">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="V28">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W28">
         <v>1.08</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z28">
         <v>3.54</v>
       </c>
       <c r="AA28">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AB28">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC28">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="AD28">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE28">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF28">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AG28">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.3</v>
       </c>
       <c r="AK28">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5045,16 +5045,16 @@
         <v>3.6</v>
       </c>
       <c r="Q29">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="R29">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="S29">
         <v>1.38</v>
       </c>
       <c r="T29">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="U29">
         <v>2.82</v>
@@ -5066,19 +5066,19 @@
         <v>1.03</v>
       </c>
       <c r="X29">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z29">
-        <v>3.2</v>
+        <v>3.37</v>
       </c>
       <c r="AA29">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AB29">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC29">
         <v>3.28</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK29">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5365,61 +5365,61 @@
         <v>1.8</v>
       </c>
       <c r="O31">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P31">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q31">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="R31">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S31">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="U31">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="V31">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W31">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
         <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z31">
-        <v>3.59</v>
+        <v>3.7</v>
       </c>
       <c r="AA31">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AB31">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AC31">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="AD31">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE31">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF31">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG31">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK31">
         <v>1.9</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="O32">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="P32">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="Q32">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="R32">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="S32">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T32">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="U32">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="V32">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W32">
         <v>1.06</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y32">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z32">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="AA32">
         <v>1.85</v>
       </c>
       <c r="AB32">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="AC32">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AD32">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE32">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF32">
         <v>1.73</v>
       </c>
       <c r="AG32">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK32">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5851,31 +5851,31 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="O34">
+        <v>2.9</v>
+      </c>
+      <c r="P34">
         <v>3</v>
       </c>
-      <c r="P34">
-        <v>3.1</v>
-      </c>
       <c r="Q34">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="R34">
         <v>1.85</v>
       </c>
       <c r="S34">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="T34">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="U34">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="V34">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W34">
         <v>1.02</v>
@@ -5884,31 +5884,31 @@
         <v>1.05</v>
       </c>
       <c r="Y34">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z34">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="AA34">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="AB34">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AC34">
-        <v>4.54</v>
+        <v>4</v>
       </c>
       <c r="AD34">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AE34">
         <v>1.01</v>
       </c>
       <c r="AF34">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG34">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK34">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6017,19 +6017,19 @@
         <v>1.93</v>
       </c>
       <c r="O35">
-        <v>3.2</v>
+        <v>3.03</v>
       </c>
       <c r="P35">
         <v>3.9</v>
       </c>
       <c r="Q35">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="R35">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="S35">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T35">
         <v>2.74</v>
@@ -6041,37 +6041,37 @@
         <v>1.33</v>
       </c>
       <c r="W35">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y35">
         <v>1.31</v>
       </c>
       <c r="Z35">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="AA35">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AB35">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC35">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="AD35">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE35">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF35">
         <v>1.88</v>
       </c>
       <c r="AG35">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK35">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>2.62</v>
       </c>
       <c r="O42">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P42">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q42">
         <v>3.46</v>
@@ -7170,19 +7170,19 @@
         <v>1.92</v>
       </c>
       <c r="S42">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="T42">
-        <v>2.41</v>
+        <v>2.52</v>
       </c>
       <c r="U42">
         <v>3.32</v>
       </c>
       <c r="V42">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W42">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X42">
         <v>1.04</v>
@@ -7191,19 +7191,19 @@
         <v>1.41</v>
       </c>
       <c r="Z42">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="AA42">
         <v>2.34</v>
       </c>
       <c r="AB42">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AC42">
-        <v>4.38</v>
+        <v>4.35</v>
       </c>
       <c r="AD42">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE42">
         <v>1.01</v>
@@ -7212,7 +7212,7 @@
         <v>1.95</v>
       </c>
       <c r="AG42">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>1.33</v>
       </c>
       <c r="AK42">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AL42">
         <v>0</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -1293,7 +1293,7 @@
         <v>3.15</v>
       </c>
       <c r="P6">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="Q6">
         <v>3.16</v>
@@ -1305,40 +1305,40 @@
         <v>1.41</v>
       </c>
       <c r="T6">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U6">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="V6">
         <v>1.28</v>
       </c>
       <c r="W6">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X6">
         <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z6">
         <v>2.83</v>
       </c>
       <c r="AA6">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB6">
         <v>1.68</v>
       </c>
       <c r="AC6">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="AD6">
         <v>1.21</v>
       </c>
       <c r="AE6">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF6">
         <v>1.83</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AK6">
         <v>1.45</v>
@@ -1459,10 +1459,10 @@
         <v>4.33</v>
       </c>
       <c r="Q7">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R7">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="S7">
         <v>1.3</v>
@@ -1498,13 +1498,13 @@
         <v>2.75</v>
       </c>
       <c r="AD7">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE7">
         <v>1.1</v>
       </c>
       <c r="AF7">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AG7">
         <v>1.96</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AK7">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="O8">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P8">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="Q8">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="R8">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="S8">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T8">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="U8">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="V8">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W8">
         <v>1.06</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z8">
-        <v>3.58</v>
+        <v>3.89</v>
       </c>
       <c r="AA8">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AB8">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AC8">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="AD8">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE8">
         <v>1.09</v>
       </c>
       <c r="AF8">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AG8">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2111,13 +2111,13 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="R11">
         <v>2.16</v>
       </c>
       <c r="S11">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T11">
         <v>2.96</v>
@@ -2129,7 +2129,7 @@
         <v>1.42</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
         <v>1</v>
@@ -2138,28 +2138,28 @@
         <v>1.25</v>
       </c>
       <c r="Z11">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="AA11">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AB11">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="AC11">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="AD11">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE11">
         <v>1.09</v>
       </c>
       <c r="AF11">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG11">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>1.4</v>
       </c>
       <c r="O12">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P12">
         <v>6.5</v>
@@ -2283,46 +2283,46 @@
         <v>1.4</v>
       </c>
       <c r="T12">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="U12">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="V12">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W12">
         <v>1.02</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z12">
-        <v>3.24</v>
+        <v>3.08</v>
       </c>
       <c r="AA12">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AB12">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AC12">
-        <v>3.42</v>
+        <v>3.51</v>
       </c>
       <c r="AD12">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE12">
         <v>1.06</v>
       </c>
       <c r="AF12">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AG12">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AK12">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3080,65 +3080,65 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="O17">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P17">
         <v>1.78</v>
       </c>
       <c r="Q17">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="R17">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="S17">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T17">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="U17">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="V17">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="W17">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X17">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z17">
-        <v>4.64</v>
+        <v>5.06</v>
       </c>
       <c r="AA17">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB17">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="AC17">
+        <v>2.2</v>
+      </c>
+      <c r="AD17">
+        <v>1.56</v>
+      </c>
+      <c r="AE17">
+        <v>1.2</v>
+      </c>
+      <c r="AF17">
+        <v>1.48</v>
+      </c>
+      <c r="AG17">
         <v>2.5</v>
       </c>
-      <c r="AD17">
-        <v>1.51</v>
-      </c>
-      <c r="AE17">
-        <v>1.22</v>
-      </c>
-      <c r="AF17">
-        <v>1.57</v>
-      </c>
-      <c r="AG17">
-        <v>2.25</v>
-      </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK17">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3578,10 +3578,10 @@
         <v>4.8</v>
       </c>
       <c r="Q20">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="R20">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="S20">
         <v>1.52</v>
@@ -3596,7 +3596,7 @@
         <v>1.28</v>
       </c>
       <c r="W20">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X20">
         <v>1.05</v>
@@ -3605,7 +3605,7 @@
         <v>1.37</v>
       </c>
       <c r="Z20">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="AA20">
         <v>2.21</v>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK20">
         <v>2.31</v>
@@ -3895,25 +3895,25 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O22">
         <v>3.5</v>
       </c>
       <c r="P22">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="Q22">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="R22">
-        <v>2.25</v>
+        <v>2.51</v>
       </c>
       <c r="S22">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="T22">
-        <v>3.34</v>
+        <v>4</v>
       </c>
       <c r="U22">
         <v>2.21</v>
@@ -3928,31 +3928,31 @@
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z22">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="AA22">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AB22">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AC22">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="AD22">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AE22">
         <v>1.2</v>
       </c>
       <c r="AF22">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AG22">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK22">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4064,55 +4064,55 @@
         <v>3.4</v>
       </c>
       <c r="P23">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Q23">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="R23">
-        <v>2.43</v>
+        <v>2.28</v>
       </c>
       <c r="S23">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T23">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U23">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="V23">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W23">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X23">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z23">
-        <v>4.47</v>
+        <v>4.25</v>
       </c>
       <c r="AA23">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB23">
-        <v>2.23</v>
+        <v>2.09</v>
       </c>
       <c r="AC23">
         <v>2.54</v>
       </c>
       <c r="AD23">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE23">
         <v>1.12</v>
       </c>
       <c r="AF23">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG23">
         <v>2.3</v>
@@ -4131,7 +4131,7 @@
         <v>1.25</v>
       </c>
       <c r="AK23">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4224,55 +4224,55 @@
         <v>1.57</v>
       </c>
       <c r="O24">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="P24">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="Q24">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="R24">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="S24">
         <v>1.22</v>
       </c>
       <c r="T24">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U24">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="V24">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W24">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X24">
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z24">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AA24">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AB24">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="AC24">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AD24">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AE24">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AF24">
         <v>1.49</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK24">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4710,34 +4710,34 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O27">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P27">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q27">
-        <v>4.1</v>
+        <v>4.23</v>
       </c>
       <c r="R27">
-        <v>2.07</v>
+        <v>2.23</v>
       </c>
       <c r="S27">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T27">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="U27">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="V27">
         <v>1.38</v>
       </c>
       <c r="W27">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
         <v>1.01</v>
@@ -4749,25 +4749,25 @@
         <v>3.14</v>
       </c>
       <c r="AA27">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="AB27">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AC27">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="AD27">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE27">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF27">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG27">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5401,10 +5401,10 @@
         <v>3.7</v>
       </c>
       <c r="AA31">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB31">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC31">
         <v>3.13</v>
@@ -5697,16 +5697,16 @@
         <v>3.25</v>
       </c>
       <c r="Q33">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="R33">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="S33">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="T33">
-        <v>2.63</v>
+        <v>2.27</v>
       </c>
       <c r="U33">
         <v>3.32</v>
@@ -5718,7 +5718,7 @@
         <v>1.03</v>
       </c>
       <c r="X33">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y33">
         <v>1.38</v>
@@ -5730,7 +5730,7 @@
         <v>2.29</v>
       </c>
       <c r="AB33">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AC33">
         <v>4.2</v>
@@ -5745,7 +5745,7 @@
         <v>2</v>
       </c>
       <c r="AG33">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.32</v>
       </c>
       <c r="AK33">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5884,10 +5884,10 @@
         <v>1.05</v>
       </c>
       <c r="Y34">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="Z34">
-        <v>2.55</v>
+        <v>2.66</v>
       </c>
       <c r="AA34">
         <v>2.39</v>
@@ -6017,19 +6017,19 @@
         <v>1.93</v>
       </c>
       <c r="O35">
-        <v>3.03</v>
+        <v>3.2</v>
       </c>
       <c r="P35">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="Q35">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="R35">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S35">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T35">
         <v>2.74</v>
@@ -6044,22 +6044,22 @@
         <v>1.04</v>
       </c>
       <c r="X35">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
         <v>1.31</v>
       </c>
       <c r="Z35">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AA35">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="AB35">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AC35">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AD35">
         <v>1.25</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK35">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -7185,13 +7185,13 @@
         <v>1.04</v>
       </c>
       <c r="X42">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="Y42">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="Z42">
-        <v>2.59</v>
+        <v>2.71</v>
       </c>
       <c r="AA42">
         <v>2.34</v>
@@ -7203,7 +7203,7 @@
         <v>4.35</v>
       </c>
       <c r="AD42">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AE42">
         <v>1.01</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK42">
         <v>1.41</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -3596,7 +3596,7 @@
         <v>1.28</v>
       </c>
       <c r="W20">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X20">
         <v>1.05</v>
@@ -3605,13 +3605,13 @@
         <v>1.37</v>
       </c>
       <c r="Z20">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="AA20">
-        <v>2.21</v>
+        <v>2.37</v>
       </c>
       <c r="AB20">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AC20">
         <v>3.9</v>
@@ -5703,16 +5703,16 @@
         <v>2.01</v>
       </c>
       <c r="S33">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="T33">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="U33">
         <v>3.32</v>
       </c>
       <c r="V33">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W33">
         <v>1.03</v>
@@ -5727,10 +5727,10 @@
         <v>2.62</v>
       </c>
       <c r="AA33">
-        <v>2.29</v>
+        <v>2.37</v>
       </c>
       <c r="AB33">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC33">
         <v>4.2</v>
@@ -5745,7 +5745,7 @@
         <v>2</v>
       </c>
       <c r="AG33">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.32</v>
       </c>
       <c r="AK33">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL33">
         <v>0</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -801,16 +801,16 @@
         <v>1.91</v>
       </c>
       <c r="O3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P3">
         <v>3.2</v>
       </c>
       <c r="Q3">
-        <v>2.63</v>
+        <v>2.46</v>
       </c>
       <c r="R3">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="S3">
         <v>1.34</v>
@@ -828,7 +828,7 @@
         <v>1.06</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y3">
         <v>1.22</v>
@@ -837,10 +837,10 @@
         <v>3.5</v>
       </c>
       <c r="AA3">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB3">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC3">
         <v>2.92</v>
@@ -871,7 +871,7 @@
         <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="O4">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P4">
         <v>2.75</v>
@@ -979,31 +979,31 @@
         <v>1.22</v>
       </c>
       <c r="T4">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U4">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V4">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W4">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z4">
-        <v>4.5</v>
+        <v>4.95</v>
       </c>
       <c r="AA4">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AB4">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="AC4">
         <v>2.35</v>
@@ -1012,26 +1012,26 @@
         <v>1.5</v>
       </c>
       <c r="AE4">
+        <v>1.17</v>
+      </c>
+      <c r="AF4">
+        <v>1.45</v>
+      </c>
+      <c r="AG4">
+        <v>2.55</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
         <v>1.22</v>
-      </c>
-      <c r="AF4">
-        <v>1.44</v>
-      </c>
-      <c r="AG4">
-        <v>2.48</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.4</v>
       </c>
       <c r="AK4">
         <v>1.53</v>
@@ -1287,28 +1287,28 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="O6">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="P6">
-        <v>2.71</v>
+        <v>2.61</v>
       </c>
       <c r="Q6">
-        <v>3.16</v>
+        <v>3.26</v>
       </c>
       <c r="R6">
         <v>1.98</v>
       </c>
       <c r="S6">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="T6">
         <v>2.53</v>
       </c>
       <c r="U6">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="V6">
         <v>1.28</v>
@@ -1317,19 +1317,19 @@
         <v>1.03</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y6">
         <v>1.35</v>
       </c>
       <c r="Z6">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AA6">
         <v>2.15</v>
       </c>
       <c r="AB6">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC6">
         <v>3.85</v>
@@ -1338,7 +1338,7 @@
         <v>1.21</v>
       </c>
       <c r="AE6">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF6">
         <v>1.83</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AK6">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1939,22 +1939,22 @@
         </is>
       </c>
       <c r="N10">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O10">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="P10">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q10">
-        <v>4.5</v>
+        <v>4.72</v>
       </c>
       <c r="R10">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S10">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T10">
         <v>3.5</v>
@@ -1963,19 +1963,19 @@
         <v>2.2</v>
       </c>
       <c r="V10">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="W10">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X10">
         <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z10">
-        <v>5.22</v>
+        <v>5.05</v>
       </c>
       <c r="AA10">
         <v>1.44</v>
@@ -1987,16 +1987,16 @@
         <v>2.2</v>
       </c>
       <c r="AD10">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE10">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF10">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG10">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK10">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2111,7 +2111,7 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R11">
         <v>2.16</v>
@@ -2135,22 +2135,22 @@
         <v>1</v>
       </c>
       <c r="Y11">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z11">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="AA11">
         <v>1.82</v>
       </c>
       <c r="AB11">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="AC11">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="AD11">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE11">
         <v>1.09</v>
@@ -2175,7 +2175,7 @@
         <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="O12">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P12">
         <v>6.5</v>
@@ -2286,43 +2286,43 @@
         <v>2.62</v>
       </c>
       <c r="U12">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="V12">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W12">
         <v>1.02</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z12">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AA12">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AB12">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AC12">
-        <v>3.51</v>
+        <v>3.6</v>
       </c>
       <c r="AD12">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE12">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF12">
         <v>2.21</v>
       </c>
       <c r="AG12">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.16</v>
       </c>
       <c r="AK12">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2600,25 +2600,25 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R14">
         <v>1.95</v>
       </c>
       <c r="S14">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T14">
-        <v>2.87</v>
+        <v>2.56</v>
       </c>
       <c r="U14">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="V14">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W14">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
         <v>1.02</v>
@@ -2627,13 +2627,13 @@
         <v>1.28</v>
       </c>
       <c r="Z14">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="AA14">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB14">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC14">
         <v>3.43</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AK14">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2760,25 +2760,25 @@
         <v>2.5</v>
       </c>
       <c r="P15">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R15">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S15">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T15">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="U15">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="V15">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="W15">
         <v>1.08</v>
@@ -2787,31 +2787,31 @@
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z15">
-        <v>4</v>
+        <v>4.01</v>
       </c>
       <c r="AA15">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB15">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AC15">
-        <v>2.59</v>
+        <v>2.74</v>
       </c>
       <c r="AD15">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AE15">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF15">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG15">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AK15">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3080,34 +3080,34 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="O17">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P17">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q17">
-        <v>4</v>
+        <v>4.24</v>
       </c>
       <c r="R17">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="S17">
         <v>1.25</v>
       </c>
       <c r="T17">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="U17">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="V17">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W17">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X17">
         <v>1.02</v>
@@ -3122,13 +3122,13 @@
         <v>1.53</v>
       </c>
       <c r="AB17">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AC17">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="AD17">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AE17">
         <v>1.2</v>
@@ -3153,7 +3153,7 @@
         <v>1.2</v>
       </c>
       <c r="AK17">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O18">
         <v>3.4</v>
       </c>
       <c r="P18">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Q18">
-        <v>3.37</v>
+        <v>3.14</v>
       </c>
       <c r="R18">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="S18">
         <v>1.3</v>
       </c>
       <c r="T18">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U18">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="V18">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W18">
         <v>1.08</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y18">
         <v>1.18</v>
       </c>
       <c r="Z18">
-        <v>4.09</v>
+        <v>4.1</v>
       </c>
       <c r="AA18">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AB18">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC18">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="AD18">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE18">
         <v>1.12</v>
       </c>
       <c r="AF18">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG18">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.26</v>
       </c>
       <c r="AK18">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3578,10 +3578,10 @@
         <v>4.8</v>
       </c>
       <c r="Q20">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="R20">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="S20">
         <v>1.52</v>
@@ -3596,7 +3596,7 @@
         <v>1.28</v>
       </c>
       <c r="W20">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X20">
         <v>1.05</v>
@@ -3732,65 +3732,65 @@
         </is>
       </c>
       <c r="N21">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O21">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="P21">
-        <v>3.31</v>
+        <v>3.18</v>
       </c>
       <c r="Q21">
         <v>2.5</v>
       </c>
       <c r="R21">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="S21">
         <v>1.2</v>
       </c>
       <c r="T21">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="U21">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="V21">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="W21">
         <v>1.12</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z21">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AA21">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AB21">
+        <v>2.5</v>
+      </c>
+      <c r="AC21">
+        <v>2.19</v>
+      </c>
+      <c r="AD21">
+        <v>1.7</v>
+      </c>
+      <c r="AE21">
+        <v>1.22</v>
+      </c>
+      <c r="AF21">
+        <v>1.42</v>
+      </c>
+      <c r="AG21">
         <v>2.7</v>
       </c>
-      <c r="AC21">
-        <v>2.31</v>
-      </c>
-      <c r="AD21">
-        <v>1.59</v>
-      </c>
-      <c r="AE21">
-        <v>1.25</v>
-      </c>
-      <c r="AF21">
-        <v>1.46</v>
-      </c>
-      <c r="AG21">
-        <v>2.55</v>
-      </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK21">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="O25">
-        <v>4.1</v>
+        <v>4.04</v>
       </c>
       <c r="P25">
-        <v>5.03</v>
+        <v>5.37</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>1.51</v>
       </c>
       <c r="O26">
-        <v>4.48</v>
+        <v>4.4</v>
       </c>
       <c r="P26">
-        <v>5.85</v>
+        <v>5.5</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB26">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="O28">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="P28">
         <v>2.7</v>
       </c>
       <c r="Q28">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R28">
         <v>2.2</v>
       </c>
       <c r="S28">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T28">
-        <v>2.95</v>
+        <v>3.14</v>
       </c>
       <c r="U28">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="V28">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W28">
         <v>1.08</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z28">
         <v>3.54</v>
       </c>
       <c r="AA28">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB28">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC28">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="AD28">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE28">
         <v>1.07</v>
       </c>
       <c r="AF28">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG28">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>3.6</v>
       </c>
       <c r="Q29">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="R29">
         <v>2.03</v>
@@ -5054,13 +5054,13 @@
         <v>1.38</v>
       </c>
       <c r="T29">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="U29">
-        <v>2.82</v>
+        <v>2.93</v>
       </c>
       <c r="V29">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W29">
         <v>1.03</v>
@@ -5075,7 +5075,7 @@
         <v>3.37</v>
       </c>
       <c r="AA29">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AB29">
         <v>1.79</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK29">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5525,25 +5525,25 @@
         </is>
       </c>
       <c r="N32">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O32">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P32">
         <v>3.6</v>
       </c>
       <c r="Q32">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="R32">
         <v>2.12</v>
       </c>
       <c r="S32">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T32">
-        <v>2.93</v>
+        <v>3.01</v>
       </c>
       <c r="U32">
         <v>2.81</v>
@@ -5555,31 +5555,31 @@
         <v>1.06</v>
       </c>
       <c r="X32">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z32">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="AA32">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB32">
         <v>1.98</v>
       </c>
       <c r="AC32">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AD32">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE32">
         <v>1.07</v>
       </c>
       <c r="AF32">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AG32">
         <v>2.04</v>
@@ -5697,10 +5697,10 @@
         <v>3.25</v>
       </c>
       <c r="Q33">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="R33">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="S33">
         <v>1.52</v>
@@ -5712,7 +5712,7 @@
         <v>3.32</v>
       </c>
       <c r="V33">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="W33">
         <v>1.03</v>
@@ -5727,7 +5727,7 @@
         <v>2.62</v>
       </c>
       <c r="AA33">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AB33">
         <v>1.53</v>
@@ -5742,7 +5742,7 @@
         <v>1.01</v>
       </c>
       <c r="AF33">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG33">
         <v>1.73</v>
@@ -6014,61 +6014,61 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="O35">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P35">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q35">
-        <v>2.57</v>
+        <v>2.66</v>
       </c>
       <c r="R35">
         <v>2</v>
       </c>
       <c r="S35">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T35">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="U35">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="V35">
         <v>1.33</v>
       </c>
       <c r="W35">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z35">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA35">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AB35">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AC35">
         <v>3.75</v>
       </c>
       <c r="AD35">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE35">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF35">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AG35">
         <v>1.87</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -1462,7 +1462,7 @@
         <v>2.16</v>
       </c>
       <c r="R7">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="S7">
         <v>1.3</v>
@@ -1471,7 +1471,7 @@
         <v>3.04</v>
       </c>
       <c r="U7">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V7">
         <v>1.43</v>
@@ -1483,7 +1483,7 @@
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z7">
         <v>3.58</v>
@@ -1495,7 +1495,7 @@
         <v>1.94</v>
       </c>
       <c r="AC7">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="AD7">
         <v>1.35</v>
@@ -1504,10 +1504,10 @@
         <v>1.1</v>
       </c>
       <c r="AF7">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG7">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.18</v>
       </c>
       <c r="AK7">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P8">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q8">
         <v>2.72</v>
@@ -1646,10 +1646,10 @@
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z8">
-        <v>3.89</v>
+        <v>3.5</v>
       </c>
       <c r="AA8">
         <v>1.81</v>
@@ -1658,7 +1658,7 @@
         <v>1.95</v>
       </c>
       <c r="AC8">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AD8">
         <v>1.32</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="O13">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P13">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="Q13">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="R13">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="S13">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="T13">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="U13">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="V13">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="W13">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X13">
         <v>1.04</v>
       </c>
       <c r="Y13">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z13">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA13">
         <v>1.57</v>
       </c>
       <c r="AB13">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC13">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="AD13">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AE13">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF13">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG13">
-        <v>2.37</v>
+        <v>2.16</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AK13">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O22">
         <v>3.5</v>
       </c>
       <c r="P22">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q22">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="R22">
-        <v>2.51</v>
+        <v>2.31</v>
       </c>
       <c r="S22">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T22">
-        <v>4</v>
+        <v>3.42</v>
       </c>
       <c r="U22">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="V22">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W22">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X22">
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z22">
         <v>5</v>
       </c>
       <c r="AA22">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AB22">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC22">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="AD22">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="AE22">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF22">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AG22">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK22">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,34 +4058,34 @@
         </is>
       </c>
       <c r="N23">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="O23">
         <v>3.4</v>
       </c>
       <c r="P23">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q23">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="R23">
         <v>2.28</v>
       </c>
       <c r="S23">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T23">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U23">
-        <v>2.31</v>
+        <v>2.46</v>
       </c>
       <c r="V23">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W23">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X23">
         <v>1.04</v>
@@ -4097,22 +4097,22 @@
         <v>4.25</v>
       </c>
       <c r="AA23">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB23">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AC23">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="AD23">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AE23">
         <v>1.12</v>
       </c>
       <c r="AF23">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG23">
         <v>2.3</v>
@@ -4131,7 +4131,7 @@
         <v>1.25</v>
       </c>
       <c r="AK23">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4224,13 +4224,13 @@
         <v>1.57</v>
       </c>
       <c r="O24">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="P24">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="Q24">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="R24">
         <v>2.41</v>
@@ -4242,37 +4242,37 @@
         <v>3.6</v>
       </c>
       <c r="U24">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="V24">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="W24">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X24">
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z24">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AA24">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AB24">
         <v>2.6</v>
       </c>
       <c r="AC24">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AD24">
         <v>1.68</v>
       </c>
       <c r="AE24">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AF24">
         <v>1.49</v>
@@ -4294,7 +4294,7 @@
         <v>1.19</v>
       </c>
       <c r="AK24">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4716,19 +4716,19 @@
         <v>3.4</v>
       </c>
       <c r="P27">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q27">
-        <v>4.23</v>
+        <v>4.15</v>
       </c>
       <c r="R27">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="S27">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T27">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="U27">
         <v>3.02</v>
@@ -4737,10 +4737,10 @@
         <v>1.38</v>
       </c>
       <c r="W27">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y27">
         <v>1.3</v>
@@ -4749,25 +4749,25 @@
         <v>3.14</v>
       </c>
       <c r="AA27">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AB27">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC27">
-        <v>3.48</v>
+        <v>3.66</v>
       </c>
       <c r="AD27">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE27">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG27">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK27">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5374,13 +5374,13 @@
         <v>2.3</v>
       </c>
       <c r="R31">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="S31">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T31">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="U31">
         <v>2.74</v>
@@ -5413,7 +5413,7 @@
         <v>1.32</v>
       </c>
       <c r="AE31">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF31">
         <v>1.74</v>
@@ -5863,13 +5863,13 @@
         <v>2.96</v>
       </c>
       <c r="R34">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="S34">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="T34">
-        <v>2.29</v>
+        <v>2.48</v>
       </c>
       <c r="U34">
         <v>3.38</v>
@@ -5878,10 +5878,10 @@
         <v>1.25</v>
       </c>
       <c r="W34">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X34">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y34">
         <v>1.46</v>
@@ -5890,10 +5890,10 @@
         <v>2.66</v>
       </c>
       <c r="AA34">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AB34">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AC34">
         <v>4</v>
@@ -7194,13 +7194,13 @@
         <v>2.71</v>
       </c>
       <c r="AA42">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AB42">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC42">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="AD42">
         <v>1.16</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -3581,7 +3581,7 @@
         <v>2.15</v>
       </c>
       <c r="R20">
-        <v>1.93</v>
+        <v>2.22</v>
       </c>
       <c r="S20">
         <v>1.52</v>
@@ -3605,7 +3605,7 @@
         <v>1.37</v>
       </c>
       <c r="Z20">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="AA20">
         <v>2.37</v>
@@ -5697,10 +5697,10 @@
         <v>3.25</v>
       </c>
       <c r="Q33">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="R33">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="S33">
         <v>1.52</v>
@@ -5718,7 +5718,7 @@
         <v>1.03</v>
       </c>
       <c r="X33">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
         <v>1.38</v>
@@ -5727,10 +5727,10 @@
         <v>2.62</v>
       </c>
       <c r="AA33">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AB33">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AC33">
         <v>4.2</v>
@@ -5761,7 +5761,7 @@
         <v>1.32</v>
       </c>
       <c r="AK33">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL33">
         <v>0</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -798,25 +798,25 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.91</v>
+        <v>2.62</v>
       </c>
       <c r="O3">
         <v>3.4</v>
       </c>
       <c r="P3">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q3">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="R3">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S3">
         <v>1.34</v>
       </c>
       <c r="T3">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="U3">
         <v>2.62</v>
@@ -825,10 +825,10 @@
         <v>1.4</v>
       </c>
       <c r="W3">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
         <v>1.22</v>
@@ -837,10 +837,10 @@
         <v>3.5</v>
       </c>
       <c r="AA3">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB3">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC3">
         <v>2.92</v>
@@ -849,29 +849,29 @@
         <v>1.31</v>
       </c>
       <c r="AE3">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF3">
+        <v>1.66</v>
+      </c>
+      <c r="AG3">
+        <v>2.07</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3">
+        <v>1.24</v>
+      </c>
+      <c r="AK3">
         <v>1.65</v>
-      </c>
-      <c r="AG3">
-        <v>2.08</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3">
-        <v>1.25</v>
-      </c>
-      <c r="AK3">
-        <v>1.63</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,22 +961,22 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="O4">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q4">
         <v>2.77</v>
       </c>
       <c r="R4">
-        <v>2.46</v>
+        <v>2.22</v>
       </c>
       <c r="S4">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="T4">
         <v>3.2</v>
@@ -997,16 +997,16 @@
         <v>1.16</v>
       </c>
       <c r="Z4">
-        <v>4.95</v>
+        <v>4.6</v>
       </c>
       <c r="AA4">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AB4">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="AC4">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AD4">
         <v>1.5</v>
@@ -1018,7 +1018,7 @@
         <v>1.45</v>
       </c>
       <c r="AG4">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="O5">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="P5">
-        <v>4.13</v>
+        <v>4.66</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1459,19 +1459,19 @@
         <v>4.33</v>
       </c>
       <c r="Q7">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="R7">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S7">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T7">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="U7">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V7">
         <v>1.43</v>
@@ -1495,10 +1495,10 @@
         <v>1.94</v>
       </c>
       <c r="AC7">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="AD7">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE7">
         <v>1.1</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK7">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>4.1</v>
+        <v>4.35</v>
       </c>
       <c r="O10">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="P10">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="Q10">
-        <v>4.72</v>
+        <v>4.88</v>
       </c>
       <c r="R10">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="S10">
         <v>1.22</v>
@@ -1960,43 +1960,43 @@
         <v>3.5</v>
       </c>
       <c r="U10">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V10">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W10">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X10">
         <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z10">
-        <v>5.05</v>
+        <v>5.15</v>
       </c>
       <c r="AA10">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AB10">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AC10">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AD10">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AE10">
         <v>1.22</v>
       </c>
       <c r="AF10">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG10">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.16</v>
       </c>
       <c r="AK10">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="O12">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="P12">
         <v>6.5</v>
       </c>
       <c r="Q12">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="R12">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S12">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T12">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="U12">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V12">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z12">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA12">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AB12">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AC12">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AD12">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE12">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF12">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AG12">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.16</v>
       </c>
       <c r="AK12">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2600,7 +2600,7 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R14">
         <v>1.95</v>
@@ -2627,41 +2627,41 @@
         <v>1.28</v>
       </c>
       <c r="Z14">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="AA14">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AB14">
         <v>1.75</v>
       </c>
       <c r="AC14">
-        <v>3.43</v>
+        <v>3.34</v>
       </c>
       <c r="AD14">
+        <v>1.24</v>
+      </c>
+      <c r="AE14">
+        <v>1.05</v>
+      </c>
+      <c r="AF14">
+        <v>1.73</v>
+      </c>
+      <c r="AG14">
+        <v>1.97</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
         <v>1.29</v>
-      </c>
-      <c r="AE14">
-        <v>1.06</v>
-      </c>
-      <c r="AF14">
-        <v>1.74</v>
-      </c>
-      <c r="AG14">
-        <v>1.96</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>1.44</v>
       </c>
       <c r="AK14">
         <v>1.38</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="O15">
+        <v>4.2</v>
+      </c>
+      <c r="P15">
+        <v>5.5</v>
+      </c>
+      <c r="Q15">
+        <v>1.93</v>
+      </c>
+      <c r="R15">
         <v>2.5</v>
       </c>
-      <c r="P15">
-        <v>6</v>
-      </c>
-      <c r="Q15">
-        <v>1.86</v>
-      </c>
-      <c r="R15">
-        <v>2.38</v>
-      </c>
       <c r="S15">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T15">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="U15">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V15">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z15">
-        <v>4.01</v>
+        <v>3.88</v>
       </c>
       <c r="AA15">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB15">
         <v>2.1</v>
       </c>
       <c r="AC15">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="AD15">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE15">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF15">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AG15">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK15">
-        <v>2.72</v>
+        <v>2.53</v>
       </c>
       <c r="AL15">
         <v>0</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="O6">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="P6">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="Q6">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="R6">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S6">
         <v>1.43</v>
@@ -1308,31 +1308,31 @@
         <v>2.53</v>
       </c>
       <c r="U6">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="V6">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="W6">
         <v>1.03</v>
       </c>
       <c r="X6">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z6">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AA6">
         <v>2.15</v>
       </c>
       <c r="AB6">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC6">
-        <v>3.85</v>
+        <v>3.58</v>
       </c>
       <c r="AD6">
         <v>1.21</v>
@@ -1341,10 +1341,10 @@
         <v>1.04</v>
       </c>
       <c r="AF6">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG6">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1622,31 +1622,31 @@
         <v>2.9</v>
       </c>
       <c r="Q8">
-        <v>2.72</v>
+        <v>2.54</v>
       </c>
       <c r="R8">
         <v>2.11</v>
       </c>
       <c r="S8">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T8">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="U8">
         <v>2.62</v>
       </c>
       <c r="V8">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z8">
         <v>3.5</v>
@@ -1658,7 +1658,7 @@
         <v>1.95</v>
       </c>
       <c r="AC8">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD8">
         <v>1.32</v>
@@ -1667,7 +1667,7 @@
         <v>1.09</v>
       </c>
       <c r="AF8">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG8">
         <v>2.13</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK8">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2111,16 +2111,16 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R11">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="S11">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T11">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="U11">
         <v>2.56</v>
@@ -2129,7 +2129,7 @@
         <v>1.42</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
         <v>1</v>
@@ -2138,13 +2138,13 @@
         <v>1.21</v>
       </c>
       <c r="Z11">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="AA11">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AB11">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC11">
         <v>2.88</v>
@@ -2159,7 +2159,7 @@
         <v>1.67</v>
       </c>
       <c r="AG11">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O13">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P13">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="Q13">
         <v>4</v>
       </c>
       <c r="R13">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="S13">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T13">
-        <v>2.94</v>
+        <v>3.34</v>
       </c>
       <c r="U13">
         <v>2.43</v>
       </c>
       <c r="V13">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="W13">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X13">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z13">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA13">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB13">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AC13">
-        <v>2.54</v>
+        <v>2.39</v>
       </c>
       <c r="AD13">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AE13">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF13">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AG13">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.91</v>
+        <v>1.23</v>
       </c>
       <c r="AK13">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="O17">
         <v>3.6</v>
@@ -3089,16 +3089,16 @@
         <v>1.8</v>
       </c>
       <c r="Q17">
-        <v>4.24</v>
+        <v>4.36</v>
       </c>
       <c r="R17">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="S17">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T17">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U17">
         <v>2.22</v>
@@ -3113,19 +3113,19 @@
         <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z17">
-        <v>5.06</v>
+        <v>4.65</v>
       </c>
       <c r="AA17">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AB17">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="AC17">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AD17">
         <v>1.57</v>
@@ -3137,7 +3137,7 @@
         <v>1.48</v>
       </c>
       <c r="AG17">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.2</v>
       </c>
       <c r="AK17">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O18">
         <v>3.4</v>
       </c>
       <c r="P18">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Q18">
-        <v>3.14</v>
+        <v>3.21</v>
       </c>
       <c r="R18">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="S18">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T18">
         <v>3.1</v>
       </c>
       <c r="U18">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="V18">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W18">
         <v>1.08</v>
       </c>
       <c r="X18">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y18">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z18">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA18">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AB18">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AC18">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AD18">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE18">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF18">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG18">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.26</v>
       </c>
       <c r="AK18">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3581,7 +3581,7 @@
         <v>2.15</v>
       </c>
       <c r="R20">
-        <v>2.22</v>
+        <v>1.93</v>
       </c>
       <c r="S20">
         <v>1.52</v>
@@ -3605,13 +3605,13 @@
         <v>1.37</v>
       </c>
       <c r="Z20">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="AA20">
-        <v>2.37</v>
+        <v>2.21</v>
       </c>
       <c r="AB20">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AC20">
         <v>3.9</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O21">
         <v>3.6</v>
       </c>
       <c r="P21">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="Q21">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="R21">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="S21">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T21">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U21">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V21">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W21">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X21">
         <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z21">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AA21">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AB21">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AC21">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="AD21">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AE21">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF21">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AG21">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK21">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3898,16 +3898,16 @@
         <v>2.4</v>
       </c>
       <c r="O22">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P22">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q22">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="R22">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="S22">
         <v>1.25</v>
@@ -3916,10 +3916,10 @@
         <v>3.42</v>
       </c>
       <c r="U22">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="V22">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W22">
         <v>1.14</v>
@@ -3928,13 +3928,13 @@
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z22">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA22">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AB22">
         <v>2.4</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="O23">
-        <v>3.4</v>
+        <v>3.66</v>
       </c>
       <c r="P23">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="Q23">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="R23">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="S23">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T23">
         <v>3.3</v>
       </c>
       <c r="U23">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="V23">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W23">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z23">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="AA23">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AB23">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AC23">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD23">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AE23">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF23">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AG23">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK23">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4233,7 +4233,7 @@
         <v>2.09</v>
       </c>
       <c r="R24">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="S24">
         <v>1.22</v>
@@ -4248,7 +4248,7 @@
         <v>1.64</v>
       </c>
       <c r="W24">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X24">
         <v>1.02</v>
@@ -4260,16 +4260,16 @@
         <v>5.4</v>
       </c>
       <c r="AA24">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AB24">
         <v>2.6</v>
       </c>
       <c r="AC24">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="AD24">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AE24">
         <v>1.22</v>
@@ -4294,7 +4294,7 @@
         <v>1.19</v>
       </c>
       <c r="AK24">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="O25">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="P25">
-        <v>5.37</v>
+        <v>5</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4423,10 +4423,10 @@
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB25">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC25">
         <v>0</v>
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="O26">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="P26">
         <v>5.5</v>
@@ -4725,10 +4725,10 @@
         <v>2.07</v>
       </c>
       <c r="S27">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T27">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="U27">
         <v>3.02</v>
@@ -4740,7 +4740,7 @@
         <v>1.05</v>
       </c>
       <c r="X27">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y27">
         <v>1.3</v>
@@ -4749,25 +4749,25 @@
         <v>3.14</v>
       </c>
       <c r="AA27">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AB27">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AC27">
-        <v>3.66</v>
+        <v>3.4</v>
       </c>
       <c r="AD27">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE27">
         <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG27">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="O28">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
+        <v>2.65</v>
+      </c>
+      <c r="Q28">
+        <v>3.08</v>
+      </c>
+      <c r="R28">
+        <v>2.1</v>
+      </c>
+      <c r="S28">
+        <v>1.36</v>
+      </c>
+      <c r="T28">
+        <v>2.89</v>
+      </c>
+      <c r="U28">
         <v>2.7</v>
-      </c>
-      <c r="Q28">
-        <v>3.1</v>
-      </c>
-      <c r="R28">
-        <v>2.2</v>
-      </c>
-      <c r="S28">
-        <v>1.34</v>
-      </c>
-      <c r="T28">
-        <v>3.14</v>
-      </c>
-      <c r="U28">
-        <v>2.69</v>
       </c>
       <c r="V28">
         <v>1.41</v>
       </c>
       <c r="W28">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y28">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z28">
         <v>3.54</v>
       </c>
       <c r="AA28">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB28">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC28">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AD28">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE28">
         <v>1.07</v>
       </c>
       <c r="AF28">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG28">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.94</v>
+        <v>2.55</v>
       </c>
       <c r="O29">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P29">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="Q29">
         <v>2.54</v>
@@ -5054,7 +5054,7 @@
         <v>1.38</v>
       </c>
       <c r="T29">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="U29">
         <v>2.93</v>
@@ -5069,10 +5069,10 @@
         <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z29">
-        <v>3.37</v>
+        <v>3.2</v>
       </c>
       <c r="AA29">
         <v>1.92</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5525,25 +5525,25 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="O32">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P32">
-        <v>3.6</v>
+        <v>3.76</v>
       </c>
       <c r="Q32">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="R32">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S32">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T32">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="U32">
         <v>2.81</v>
@@ -5564,13 +5564,13 @@
         <v>3.48</v>
       </c>
       <c r="AA32">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AB32">
         <v>1.98</v>
       </c>
       <c r="AC32">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AD32">
         <v>1.31</v>
@@ -5579,10 +5579,10 @@
         <v>1.07</v>
       </c>
       <c r="AF32">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AG32">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK32">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6020,25 +6020,25 @@
         <v>3.1</v>
       </c>
       <c r="P35">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q35">
         <v>2.66</v>
       </c>
       <c r="R35">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S35">
         <v>1.44</v>
       </c>
       <c r="T35">
-        <v>2.73</v>
+        <v>2.56</v>
       </c>
       <c r="U35">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="V35">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W35">
         <v>1.02</v>
@@ -6056,7 +6056,7 @@
         <v>2.12</v>
       </c>
       <c r="AB35">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AC35">
         <v>3.75</v>
@@ -6071,7 +6071,7 @@
         <v>1.87</v>
       </c>
       <c r="AG35">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="AK35">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL35">
         <v>0</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -1299,7 +1299,7 @@
         <v>3.2</v>
       </c>
       <c r="R6">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S6">
         <v>1.43</v>
@@ -1326,10 +1326,10 @@
         <v>2.83</v>
       </c>
       <c r="AA6">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AB6">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AC6">
         <v>3.58</v>
@@ -2132,7 +2132,7 @@
         <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
         <v>1.21</v>
@@ -2141,16 +2141,16 @@
         <v>3.58</v>
       </c>
       <c r="AA11">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AB11">
         <v>1.95</v>
       </c>
       <c r="AC11">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="AD11">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE11">
         <v>1.09</v>
@@ -2431,16 +2431,16 @@
         <v>3.6</v>
       </c>
       <c r="O13">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="P13">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q13">
-        <v>4</v>
+        <v>3.59</v>
       </c>
       <c r="R13">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="S13">
         <v>1.28</v>
@@ -2449,7 +2449,7 @@
         <v>3.34</v>
       </c>
       <c r="U13">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="V13">
         <v>1.53</v>
@@ -2464,13 +2464,13 @@
         <v>1.15</v>
       </c>
       <c r="Z13">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA13">
         <v>1.61</v>
       </c>
       <c r="AB13">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AC13">
         <v>2.39</v>
@@ -3409,61 +3409,61 @@
         <v>5.65</v>
       </c>
       <c r="O19">
-        <v>4.46</v>
+        <v>4.56</v>
       </c>
       <c r="P19">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="O22">
         <v>3.4</v>
@@ -3931,10 +3931,10 @@
         <v>1.11</v>
       </c>
       <c r="Z22">
-        <v>5.25</v>
+        <v>4.95</v>
       </c>
       <c r="AA22">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AB22">
         <v>2.4</v>
@@ -4061,13 +4061,13 @@
         <v>2.02</v>
       </c>
       <c r="O23">
-        <v>3.66</v>
+        <v>3.4</v>
       </c>
       <c r="P23">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="Q23">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="R23">
         <v>2.26</v>
@@ -4097,13 +4097,13 @@
         <v>4.15</v>
       </c>
       <c r="AA23">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB23">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AC23">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="AD23">
         <v>1.39</v>
@@ -4112,10 +4112,10 @@
         <v>1.11</v>
       </c>
       <c r="AF23">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG23">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.26</v>
       </c>
       <c r="AK23">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -5365,13 +5365,13 @@
         <v>1.8</v>
       </c>
       <c r="O31">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P31">
         <v>3.8</v>
       </c>
       <c r="Q31">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R31">
         <v>2.05</v>
@@ -5383,7 +5383,7 @@
         <v>2.74</v>
       </c>
       <c r="U31">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="V31">
         <v>1.37</v>
@@ -5395,22 +5395,22 @@
         <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z31">
-        <v>3.7</v>
+        <v>3.48</v>
       </c>
       <c r="AA31">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AB31">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC31">
         <v>3.13</v>
       </c>
       <c r="AD31">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE31">
         <v>1.07</v>
@@ -5419,7 +5419,7 @@
         <v>1.74</v>
       </c>
       <c r="AG31">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="O32">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="P32">
         <v>3.76</v>
@@ -5570,7 +5570,7 @@
         <v>1.98</v>
       </c>
       <c r="AC32">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AD32">
         <v>1.31</v>
@@ -5582,7 +5582,7 @@
         <v>1.72</v>
       </c>
       <c r="AG32">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5851,25 +5851,25 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O34">
         <v>2.9</v>
       </c>
       <c r="P34">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q34">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="R34">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="S34">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="T34">
-        <v>2.48</v>
+        <v>2.29</v>
       </c>
       <c r="U34">
         <v>3.38</v>
@@ -5878,16 +5878,16 @@
         <v>1.25</v>
       </c>
       <c r="W34">
+        <v>1.02</v>
+      </c>
+      <c r="X34">
         <v>1.05</v>
       </c>
-      <c r="X34">
-        <v>1.08</v>
-      </c>
       <c r="Y34">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="Z34">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="AA34">
         <v>2.4</v>
@@ -5896,19 +5896,19 @@
         <v>1.53</v>
       </c>
       <c r="AC34">
-        <v>4</v>
+        <v>4.49</v>
       </c>
       <c r="AD34">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE34">
         <v>1.01</v>
       </c>
       <c r="AF34">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AG34">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AK34">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O35">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P35">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="Q35">
         <v>2.66</v>
@@ -6053,13 +6053,13 @@
         <v>2.88</v>
       </c>
       <c r="AA35">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AB35">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AC35">
-        <v>3.75</v>
+        <v>3.89</v>
       </c>
       <c r="AD35">
         <v>1.19</v>
@@ -7155,25 +7155,25 @@
         </is>
       </c>
       <c r="N42">
+        <v>2.45</v>
+      </c>
+      <c r="O42">
+        <v>3</v>
+      </c>
+      <c r="P42">
         <v>2.62</v>
       </c>
-      <c r="O42">
-        <v>2.95</v>
-      </c>
-      <c r="P42">
-        <v>2.52</v>
-      </c>
       <c r="Q42">
-        <v>3.46</v>
+        <v>3.15</v>
       </c>
       <c r="R42">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="S42">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="T42">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="U42">
         <v>3.32</v>
@@ -7182,16 +7182,16 @@
         <v>1.29</v>
       </c>
       <c r="W42">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X42">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Y42">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="Z42">
-        <v>2.71</v>
+        <v>2.59</v>
       </c>
       <c r="AA42">
         <v>2.35</v>
@@ -7200,10 +7200,10 @@
         <v>1.57</v>
       </c>
       <c r="AC42">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="AD42">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE42">
         <v>1.01</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK42">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AL42">
         <v>0</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -5401,10 +5401,10 @@
         <v>3.48</v>
       </c>
       <c r="AA31">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB31">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC31">
         <v>3.13</v>
@@ -5860,16 +5860,16 @@
         <v>3.1</v>
       </c>
       <c r="Q34">
-        <v>2.93</v>
+        <v>2.86</v>
       </c>
       <c r="R34">
         <v>1.86</v>
       </c>
       <c r="S34">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="T34">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="U34">
         <v>3.38</v>
@@ -5884,10 +5884,10 @@
         <v>1.05</v>
       </c>
       <c r="Y34">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z34">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="AA34">
         <v>2.4</v>
@@ -5896,7 +5896,7 @@
         <v>1.53</v>
       </c>
       <c r="AC34">
-        <v>4.49</v>
+        <v>4.39</v>
       </c>
       <c r="AD34">
         <v>1.15</v>
@@ -5905,10 +5905,10 @@
         <v>1.01</v>
       </c>
       <c r="AF34">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG34">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>1.34</v>
       </c>
       <c r="AK34">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>2.01</v>
       </c>
       <c r="O35">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P35">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q35">
         <v>2.66</v>
@@ -6053,10 +6053,10 @@
         <v>2.88</v>
       </c>
       <c r="AA35">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AB35">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AC35">
         <v>3.89</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="O42">
         <v>3</v>
       </c>
       <c r="P42">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="Q42">
         <v>3.15</v>
@@ -7191,7 +7191,7 @@
         <v>1.41</v>
       </c>
       <c r="Z42">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="AA42">
         <v>2.35</v>
@@ -7200,7 +7200,7 @@
         <v>1.57</v>
       </c>
       <c r="AC42">
-        <v>4.53</v>
+        <v>4.52</v>
       </c>
       <c r="AD42">
         <v>1.18</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK42">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AL42">
         <v>0</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P4">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="Q4">
         <v>2.77</v>
@@ -991,7 +991,7 @@
         <v>1.1</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
         <v>1.16</v>
@@ -1000,25 +1000,25 @@
         <v>4.6</v>
       </c>
       <c r="AA4">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AB4">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="AC4">
         <v>2.28</v>
       </c>
       <c r="AD4">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AE4">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF4">
         <v>1.45</v>
       </c>
       <c r="AG4">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="O5">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="P5">
-        <v>4.66</v>
+        <v>4.82</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>4.35</v>
+        <v>4.01</v>
       </c>
       <c r="O10">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="P10">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="Q10">
         <v>4.88</v>
@@ -1960,7 +1960,7 @@
         <v>3.5</v>
       </c>
       <c r="U10">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V10">
         <v>1.62</v>
@@ -1978,13 +1978,13 @@
         <v>5.15</v>
       </c>
       <c r="AA10">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AB10">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AC10">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AD10">
         <v>1.63</v>
@@ -1996,7 +1996,7 @@
         <v>1.51</v>
       </c>
       <c r="AG10">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2265,37 +2265,37 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="O12">
-        <v>4.15</v>
+        <v>3.85</v>
       </c>
       <c r="P12">
-        <v>6.5</v>
+        <v>6.62</v>
       </c>
       <c r="Q12">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="R12">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="S12">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T12">
-        <v>2.66</v>
+        <v>2.91</v>
       </c>
       <c r="U12">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="V12">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W12">
         <v>1.03</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
         <v>1.27</v>
@@ -2304,7 +2304,7 @@
         <v>3.14</v>
       </c>
       <c r="AA12">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB12">
         <v>1.76</v>
@@ -2313,13 +2313,13 @@
         <v>3.34</v>
       </c>
       <c r="AD12">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE12">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF12">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AG12">
         <v>1.57</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK12">
-        <v>2.72</v>
+        <v>2.55</v>
       </c>
       <c r="AL12">
         <v>0</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.62</v>
+        <v>2.04</v>
       </c>
       <c r="O3">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="P3">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -819,28 +819,28 @@
         <v>2.88</v>
       </c>
       <c r="U3">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="V3">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W3">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z3">
         <v>3.5</v>
       </c>
       <c r="AA3">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB3">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC3">
         <v>2.92</v>
@@ -855,7 +855,7 @@
         <v>1.66</v>
       </c>
       <c r="AG3">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK3">
         <v>1.65</v>
@@ -1299,7 +1299,7 @@
         <v>3.2</v>
       </c>
       <c r="R6">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S6">
         <v>1.43</v>
@@ -1326,13 +1326,13 @@
         <v>2.83</v>
       </c>
       <c r="AA6">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AB6">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AC6">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="AD6">
         <v>1.21</v>
@@ -1613,49 +1613,49 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O8">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P8">
+        <v>3.15</v>
+      </c>
+      <c r="Q8">
+        <v>2.71</v>
+      </c>
+      <c r="R8">
+        <v>2.2</v>
+      </c>
+      <c r="S8">
+        <v>1.35</v>
+      </c>
+      <c r="T8">
         <v>2.9</v>
-      </c>
-      <c r="Q8">
-        <v>2.54</v>
-      </c>
-      <c r="R8">
-        <v>2.11</v>
-      </c>
-      <c r="S8">
-        <v>1.33</v>
-      </c>
-      <c r="T8">
-        <v>3.16</v>
       </c>
       <c r="U8">
         <v>2.62</v>
       </c>
       <c r="V8">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W8">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z8">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA8">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB8">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AC8">
         <v>2.88</v>
@@ -1667,7 +1667,7 @@
         <v>1.09</v>
       </c>
       <c r="AF8">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AG8">
         <v>2.13</v>
@@ -2111,31 +2111,31 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="R11">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S11">
         <v>1.31</v>
       </c>
       <c r="T11">
-        <v>3.02</v>
+        <v>3.15</v>
       </c>
       <c r="U11">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="V11">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W11">
         <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y11">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z11">
         <v>3.58</v>
@@ -2147,19 +2147,19 @@
         <v>1.95</v>
       </c>
       <c r="AC11">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="AD11">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE11">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF11">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG11">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK11">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2600,10 +2600,10 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="R14">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="S14">
         <v>1.42</v>
@@ -2624,31 +2624,31 @@
         <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z14">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AA14">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB14">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC14">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AD14">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE14">
         <v>1.05</v>
       </c>
       <c r="AF14">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG14">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>1.29</v>
       </c>
       <c r="AK14">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="O15">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="P15">
-        <v>5.5</v>
+        <v>5.33</v>
       </c>
       <c r="Q15">
         <v>1.93</v>
@@ -2787,28 +2787,28 @@
         <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z15">
-        <v>3.88</v>
+        <v>4.1</v>
       </c>
       <c r="AA15">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AB15">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC15">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="AD15">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AE15">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF15">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AG15">
         <v>1.86</v>
@@ -3080,19 +3080,19 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="O17">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P17">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q17">
-        <v>4.36</v>
+        <v>4</v>
       </c>
       <c r="R17">
-        <v>2.27</v>
+        <v>2.43</v>
       </c>
       <c r="S17">
         <v>1.26</v>
@@ -3101,43 +3101,43 @@
         <v>3.2</v>
       </c>
       <c r="U17">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="V17">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="W17">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X17">
         <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z17">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="AA17">
         <v>1.48</v>
       </c>
       <c r="AB17">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AC17">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AD17">
         <v>1.57</v>
       </c>
       <c r="AE17">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF17">
         <v>1.48</v>
       </c>
       <c r="AG17">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK17">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,25 +3243,25 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P18">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="Q18">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="R18">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="S18">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="T18">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="U18">
         <v>2.5</v>
@@ -3282,19 +3282,19 @@
         <v>3.8</v>
       </c>
       <c r="AA18">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB18">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AC18">
         <v>2.66</v>
       </c>
       <c r="AD18">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE18">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF18">
         <v>1.58</v>
@@ -3406,25 +3406,25 @@
         </is>
       </c>
       <c r="N19">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="O19">
-        <v>4.56</v>
+        <v>4.6</v>
       </c>
       <c r="P19">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q19">
-        <v>5.2</v>
+        <v>4.75</v>
       </c>
       <c r="R19">
         <v>2.51</v>
       </c>
       <c r="S19">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T19">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U19">
         <v>2.13</v>
@@ -3442,7 +3442,7 @@
         <v>1.11</v>
       </c>
       <c r="Z19">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="AA19">
         <v>1.5</v>
@@ -3451,19 +3451,19 @@
         <v>2.5</v>
       </c>
       <c r="AC19">
+        <v>2.07</v>
+      </c>
+      <c r="AD19">
+        <v>1.62</v>
+      </c>
+      <c r="AE19">
+        <v>1.21</v>
+      </c>
+      <c r="AF19">
+        <v>1.59</v>
+      </c>
+      <c r="AG19">
         <v>2.19</v>
-      </c>
-      <c r="AD19">
-        <v>1.63</v>
-      </c>
-      <c r="AE19">
-        <v>1.22</v>
-      </c>
-      <c r="AF19">
-        <v>1.45</v>
-      </c>
-      <c r="AG19">
-        <v>2.5</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3569,31 +3569,31 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="O20">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="Q20">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="R20">
-        <v>1.93</v>
+        <v>2.22</v>
       </c>
       <c r="S20">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="T20">
-        <v>2.29</v>
+        <v>2.63</v>
       </c>
       <c r="U20">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="V20">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="W20">
         <v>1.05</v>
@@ -3602,10 +3602,10 @@
         <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z20">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="AA20">
         <v>2.21</v>
@@ -3614,19 +3614,19 @@
         <v>1.59</v>
       </c>
       <c r="AC20">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="AD20">
         <v>1.18</v>
       </c>
       <c r="AE20">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF20">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AG20">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="AK20">
-        <v>2.31</v>
+        <v>1.9</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,25 +3732,25 @@
         </is>
       </c>
       <c r="N21">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="O21">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P21">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q21">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="R21">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="S21">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T21">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U21">
         <v>2.14</v>
@@ -3759,37 +3759,37 @@
         <v>1.66</v>
       </c>
       <c r="W21">
+        <v>1.17</v>
+      </c>
+      <c r="X21">
+        <v>1.01</v>
+      </c>
+      <c r="Y21">
         <v>1.14</v>
       </c>
-      <c r="X21">
-        <v>1.02</v>
-      </c>
-      <c r="Y21">
-        <v>1.09</v>
-      </c>
       <c r="Z21">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AA21">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AB21">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="AC21">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AD21">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AE21">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AF21">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AG21">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AK21">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.65</v>
+        <v>2.44</v>
       </c>
       <c r="O22">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="P22">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="Q22">
         <v>2.9</v>
@@ -3916,10 +3916,10 @@
         <v>3.42</v>
       </c>
       <c r="U22">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V22">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="W22">
         <v>1.14</v>
@@ -3934,25 +3934,25 @@
         <v>4.95</v>
       </c>
       <c r="AA22">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB22">
         <v>2.4</v>
       </c>
       <c r="AC22">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AD22">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AE22">
         <v>1.22</v>
       </c>
       <c r="AF22">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG22">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4058,16 +4058,16 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="O23">
-        <v>3.4</v>
+        <v>3.66</v>
       </c>
       <c r="P23">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="Q23">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="R23">
         <v>2.26</v>
@@ -4088,7 +4088,7 @@
         <v>1.08</v>
       </c>
       <c r="X23">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
         <v>1.16</v>
@@ -4097,10 +4097,10 @@
         <v>4.15</v>
       </c>
       <c r="AA23">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB23">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AC23">
         <v>2.61</v>
@@ -4131,7 +4131,7 @@
         <v>1.26</v>
       </c>
       <c r="AK23">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4224,28 +4224,28 @@
         <v>1.57</v>
       </c>
       <c r="O24">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P24">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="Q24">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="R24">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="S24">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T24">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="U24">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V24">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W24">
         <v>1.13</v>
@@ -4269,16 +4269,16 @@
         <v>2.16</v>
       </c>
       <c r="AD24">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AE24">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF24">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG24">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AK24">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="O25">
         <v>4</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="O26">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="P26">
-        <v>5.5</v>
+        <v>6.19</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4710,25 +4710,25 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O27">
         <v>3.4</v>
       </c>
       <c r="P27">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q27">
-        <v>4.15</v>
+        <v>3.66</v>
       </c>
       <c r="R27">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="S27">
         <v>1.44</v>
       </c>
       <c r="T27">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="U27">
         <v>3.02</v>
@@ -4740,7 +4740,7 @@
         <v>1.05</v>
       </c>
       <c r="X27">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
         <v>1.3</v>
@@ -4752,22 +4752,22 @@
         <v>2.06</v>
       </c>
       <c r="AB27">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AC27">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AD27">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE27">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF27">
         <v>1.79</v>
       </c>
       <c r="AG27">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.35</v>
       </c>
       <c r="AK27">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O28">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P28">
         <v>2.65</v>
       </c>
       <c r="Q28">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="R28">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="S28">
         <v>1.36</v>
@@ -4894,7 +4894,7 @@
         <v>2.89</v>
       </c>
       <c r="U28">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="V28">
         <v>1.41</v>
@@ -4903,7 +4903,7 @@
         <v>1.04</v>
       </c>
       <c r="X28">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
         <v>1.22</v>
@@ -4912,25 +4912,25 @@
         <v>3.54</v>
       </c>
       <c r="AA28">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AB28">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC28">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="AD28">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE28">
         <v>1.07</v>
       </c>
       <c r="AF28">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AG28">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5036,16 +5036,16 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.55</v>
+        <v>1.94</v>
       </c>
       <c r="O29">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P29">
-        <v>3.35</v>
+        <v>3.64</v>
       </c>
       <c r="Q29">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="R29">
         <v>2.03</v>
@@ -5057,10 +5057,10 @@
         <v>2.7</v>
       </c>
       <c r="U29">
-        <v>2.93</v>
+        <v>2.82</v>
       </c>
       <c r="V29">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W29">
         <v>1.03</v>
@@ -5081,10 +5081,10 @@
         <v>1.79</v>
       </c>
       <c r="AC29">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="AD29">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE29">
         <v>1.05</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="O32">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="P32">
-        <v>3.76</v>
+        <v>3.8</v>
       </c>
       <c r="Q32">
         <v>2.57</v>
@@ -5540,22 +5540,22 @@
         <v>2.14</v>
       </c>
       <c r="S32">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T32">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="U32">
-        <v>2.81</v>
+        <v>2.61</v>
       </c>
       <c r="V32">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W32">
         <v>1.06</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
         <v>1.25</v>
@@ -5564,13 +5564,13 @@
         <v>3.48</v>
       </c>
       <c r="AA32">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AB32">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AC32">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="AD32">
         <v>1.31</v>
@@ -5582,7 +5582,7 @@
         <v>1.72</v>
       </c>
       <c r="AG32">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5688,40 +5688,40 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O33">
         <v>2.9</v>
       </c>
       <c r="P33">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q33">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="R33">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="S33">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="T33">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="U33">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="V33">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W33">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X33">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y33">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="Z33">
         <v>2.62</v>
@@ -5733,16 +5733,16 @@
         <v>1.55</v>
       </c>
       <c r="AC33">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AD33">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE33">
         <v>1.01</v>
       </c>
       <c r="AF33">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG33">
         <v>1.73</v>
@@ -5761,7 +5761,7 @@
         <v>1.32</v>
       </c>
       <c r="AK33">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6014,19 +6014,19 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="O35">
         <v>3.2</v>
       </c>
       <c r="P35">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="Q35">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="R35">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S35">
         <v>1.44</v>
@@ -6035,7 +6035,7 @@
         <v>2.56</v>
       </c>
       <c r="U35">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="V35">
         <v>1.32</v>
@@ -6047,28 +6047,28 @@
         <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z35">
         <v>2.88</v>
       </c>
       <c r="AA35">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AB35">
         <v>1.68</v>
       </c>
       <c r="AC35">
-        <v>3.89</v>
+        <v>3.75</v>
       </c>
       <c r="AD35">
         <v>1.19</v>
       </c>
       <c r="AE35">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF35">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG35">
         <v>1.83</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AK35">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6186,55 +6186,55 @@
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6349,55 +6349,55 @@
         <v>0</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL37">
         <v>0</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU50"/>
+  <dimension ref="A1:AU39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1130,7 +1130,7 @@
         <v>2.5</v>
       </c>
       <c r="P5">
-        <v>4.82</v>
+        <v>4.8</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="O7">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P7">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="Q7">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="R7">
-        <v>2.23</v>
+        <v>1.88</v>
       </c>
       <c r="S7">
+        <v>1.46</v>
+      </c>
+      <c r="T7">
+        <v>2.41</v>
+      </c>
+      <c r="U7">
+        <v>2.79</v>
+      </c>
+      <c r="V7">
+        <v>1.35</v>
+      </c>
+      <c r="W7">
+        <v>1.06</v>
+      </c>
+      <c r="X7">
+        <v>1.04</v>
+      </c>
+      <c r="Y7">
+        <v>1.29</v>
+      </c>
+      <c r="Z7">
+        <v>3.04</v>
+      </c>
+      <c r="AA7">
+        <v>1.85</v>
+      </c>
+      <c r="AB7">
+        <v>1.95</v>
+      </c>
+      <c r="AC7">
+        <v>3.14</v>
+      </c>
+      <c r="AD7">
+        <v>1.27</v>
+      </c>
+      <c r="AE7">
+        <v>1.07</v>
+      </c>
+      <c r="AF7">
+        <v>1.78</v>
+      </c>
+      <c r="AG7">
+        <v>1.89</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
         <v>1.31</v>
       </c>
-      <c r="T7">
-        <v>2.97</v>
-      </c>
-      <c r="U7">
-        <v>2.5</v>
-      </c>
-      <c r="V7">
-        <v>1.43</v>
-      </c>
-      <c r="W7">
-        <v>1.1</v>
-      </c>
-      <c r="X7">
-        <v>1.01</v>
-      </c>
-      <c r="Y7">
-        <v>1.21</v>
-      </c>
-      <c r="Z7">
-        <v>3.58</v>
-      </c>
-      <c r="AA7">
-        <v>1.75</v>
-      </c>
-      <c r="AB7">
-        <v>1.94</v>
-      </c>
-      <c r="AC7">
-        <v>2.75</v>
-      </c>
-      <c r="AD7">
-        <v>1.34</v>
-      </c>
-      <c r="AE7">
-        <v>1.1</v>
-      </c>
-      <c r="AF7">
-        <v>1.73</v>
-      </c>
-      <c r="AG7">
-        <v>1.95</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.19</v>
-      </c>
       <c r="AK7">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
+        <v>4.1</v>
+      </c>
+      <c r="O13">
         <v>3.6</v>
       </c>
-      <c r="O13">
-        <v>3.84</v>
-      </c>
       <c r="P13">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="Q13">
-        <v>3.59</v>
+        <v>4</v>
       </c>
       <c r="R13">
+        <v>2.43</v>
+      </c>
+      <c r="S13">
+        <v>1.22</v>
+      </c>
+      <c r="T13">
+        <v>3.3</v>
+      </c>
+      <c r="U13">
         <v>2.42</v>
-      </c>
-      <c r="S13">
-        <v>1.28</v>
-      </c>
-      <c r="T13">
-        <v>3.34</v>
-      </c>
-      <c r="U13">
-        <v>2.33</v>
       </c>
       <c r="V13">
         <v>1.53</v>
       </c>
       <c r="W13">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y13">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="AA13">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB13">
         <v>2.3</v>
       </c>
       <c r="AC13">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="AD13">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AE13">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF13">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG13">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-09-03 14:00:00</t>
+          <t>2026-09-03 14:30:00</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
+        <v>2.5</v>
+      </c>
+      <c r="O17">
+        <v>3.5</v>
+      </c>
+      <c r="P17">
+        <v>2.4</v>
+      </c>
+      <c r="Q17">
+        <v>3.1</v>
+      </c>
+      <c r="R17">
+        <v>2.22</v>
+      </c>
+      <c r="S17">
+        <v>1.34</v>
+      </c>
+      <c r="T17">
+        <v>2.91</v>
+      </c>
+      <c r="U17">
+        <v>2.5</v>
+      </c>
+      <c r="V17">
+        <v>1.46</v>
+      </c>
+      <c r="W17">
+        <v>1.08</v>
+      </c>
+      <c r="X17">
+        <v>1</v>
+      </c>
+      <c r="Y17">
+        <v>1.19</v>
+      </c>
+      <c r="Z17">
         <v>3.8</v>
       </c>
-      <c r="O17">
-        <v>3.7</v>
-      </c>
-      <c r="P17">
-        <v>1.75</v>
-      </c>
-      <c r="Q17">
-        <v>4</v>
-      </c>
-      <c r="R17">
-        <v>2.43</v>
-      </c>
-      <c r="S17">
+      <c r="AA17">
+        <v>1.72</v>
+      </c>
+      <c r="AB17">
+        <v>2</v>
+      </c>
+      <c r="AC17">
+        <v>2.66</v>
+      </c>
+      <c r="AD17">
+        <v>1.37</v>
+      </c>
+      <c r="AE17">
+        <v>1.12</v>
+      </c>
+      <c r="AF17">
+        <v>1.58</v>
+      </c>
+      <c r="AG17">
+        <v>2.23</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
         <v>1.26</v>
       </c>
-      <c r="T17">
-        <v>3.2</v>
-      </c>
-      <c r="U17">
-        <v>2.12</v>
-      </c>
-      <c r="V17">
-        <v>1.61</v>
-      </c>
-      <c r="W17">
-        <v>1.14</v>
-      </c>
-      <c r="X17">
-        <v>1.02</v>
-      </c>
-      <c r="Y17">
-        <v>1.13</v>
-      </c>
-      <c r="Z17">
-        <v>4.8</v>
-      </c>
-      <c r="AA17">
-        <v>1.48</v>
-      </c>
-      <c r="AB17">
-        <v>2.4</v>
-      </c>
-      <c r="AC17">
-        <v>2.2</v>
-      </c>
-      <c r="AD17">
-        <v>1.57</v>
-      </c>
-      <c r="AE17">
-        <v>1.22</v>
-      </c>
-      <c r="AF17">
-        <v>1.48</v>
-      </c>
-      <c r="AG17">
-        <v>2.4</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.24</v>
-      </c>
       <c r="AK17">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.55</v>
+        <v>5.5</v>
       </c>
       <c r="O18">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="P18">
-        <v>2.47</v>
+        <v>1.5</v>
       </c>
       <c r="Q18">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="R18">
-        <v>2.22</v>
+        <v>2.51</v>
       </c>
       <c r="S18">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="T18">
-        <v>2.91</v>
+        <v>3.5</v>
       </c>
       <c r="U18">
+        <v>2.13</v>
+      </c>
+      <c r="V18">
+        <v>1.63</v>
+      </c>
+      <c r="W18">
+        <v>1.14</v>
+      </c>
+      <c r="X18">
+        <v>1.02</v>
+      </c>
+      <c r="Y18">
+        <v>1.11</v>
+      </c>
+      <c r="Z18">
+        <v>4.85</v>
+      </c>
+      <c r="AA18">
+        <v>1.5</v>
+      </c>
+      <c r="AB18">
         <v>2.5</v>
       </c>
-      <c r="V18">
-        <v>1.46</v>
-      </c>
-      <c r="W18">
-        <v>1.08</v>
-      </c>
-      <c r="X18">
-        <v>1</v>
-      </c>
-      <c r="Y18">
-        <v>1.19</v>
-      </c>
-      <c r="Z18">
-        <v>3.8</v>
-      </c>
-      <c r="AA18">
-        <v>1.8</v>
-      </c>
-      <c r="AB18">
-        <v>2</v>
-      </c>
       <c r="AC18">
-        <v>2.66</v>
+        <v>2.07</v>
       </c>
       <c r="AD18">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="AE18">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AF18">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AG18">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK18">
-        <v>1.43</v>
+        <v>1.11</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-09-03 14:30:00</t>
+          <t>2026-09-03 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>5.5</v>
+        <v>1.49</v>
       </c>
       <c r="O19">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q19">
-        <v>4.75</v>
+        <v>2</v>
       </c>
       <c r="R19">
-        <v>2.51</v>
+        <v>2.22</v>
       </c>
       <c r="S19">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="T19">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="U19">
-        <v>2.13</v>
+        <v>3.12</v>
       </c>
       <c r="V19">
-        <v>1.63</v>
+        <v>1.32</v>
       </c>
       <c r="W19">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y19">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="Z19">
-        <v>4.85</v>
+        <v>2.75</v>
       </c>
       <c r="AA19">
-        <v>1.5</v>
+        <v>2.21</v>
       </c>
       <c r="AB19">
-        <v>2.5</v>
+        <v>1.59</v>
       </c>
       <c r="AC19">
-        <v>2.07</v>
+        <v>3.88</v>
       </c>
       <c r="AD19">
-        <v>1.62</v>
+        <v>1.18</v>
       </c>
       <c r="AE19">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="AF19">
-        <v>1.59</v>
+        <v>2.25</v>
       </c>
       <c r="AG19">
-        <v>2.19</v>
+        <v>1.57</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AK19">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.49</v>
+        <v>2.05</v>
       </c>
       <c r="O20">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="P20">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="Q20">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="R20">
-        <v>2.22</v>
+        <v>2.45</v>
       </c>
       <c r="S20">
+        <v>1.22</v>
+      </c>
+      <c r="T20">
+        <v>3.8</v>
+      </c>
+      <c r="U20">
+        <v>2.14</v>
+      </c>
+      <c r="V20">
+        <v>1.66</v>
+      </c>
+      <c r="W20">
+        <v>1.17</v>
+      </c>
+      <c r="X20">
+        <v>1.01</v>
+      </c>
+      <c r="Y20">
+        <v>1.14</v>
+      </c>
+      <c r="Z20">
+        <v>5.25</v>
+      </c>
+      <c r="AA20">
+        <v>1.47</v>
+      </c>
+      <c r="AB20">
+        <v>2.66</v>
+      </c>
+      <c r="AC20">
+        <v>2.2</v>
+      </c>
+      <c r="AD20">
+        <v>1.69</v>
+      </c>
+      <c r="AE20">
+        <v>1.28</v>
+      </c>
+      <c r="AF20">
         <v>1.44</v>
       </c>
-      <c r="T20">
-        <v>2.63</v>
-      </c>
-      <c r="U20">
-        <v>3.12</v>
-      </c>
-      <c r="V20">
-        <v>1.32</v>
-      </c>
-      <c r="W20">
-        <v>1.05</v>
-      </c>
-      <c r="X20">
-        <v>1.05</v>
-      </c>
-      <c r="Y20">
-        <v>1.33</v>
-      </c>
-      <c r="Z20">
-        <v>2.75</v>
-      </c>
-      <c r="AA20">
-        <v>2.21</v>
-      </c>
-      <c r="AB20">
-        <v>1.59</v>
-      </c>
-      <c r="AC20">
-        <v>3.88</v>
-      </c>
-      <c r="AD20">
-        <v>1.18</v>
-      </c>
-      <c r="AE20">
-        <v>1.06</v>
-      </c>
-      <c r="AF20">
-        <v>2.25</v>
-      </c>
       <c r="AG20">
-        <v>1.57</v>
+        <v>2.7</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.08</v>
+        <v>1.34</v>
       </c>
       <c r="AK20">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R21">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V21">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W21">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AC21">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD21">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AE21">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AF21">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG21">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK21">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.44</v>
+        <v>1.98</v>
       </c>
       <c r="O22">
-        <v>3.52</v>
+        <v>3.66</v>
       </c>
       <c r="P22">
-        <v>2.64</v>
+        <v>3.34</v>
       </c>
       <c r="Q22">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="R22">
         <v>2.26</v>
       </c>
       <c r="S22">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T22">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="U22">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="V22">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="W22">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y22">
+        <v>1.16</v>
+      </c>
+      <c r="Z22">
+        <v>4.15</v>
+      </c>
+      <c r="AA22">
+        <v>1.68</v>
+      </c>
+      <c r="AB22">
+        <v>2.14</v>
+      </c>
+      <c r="AC22">
+        <v>2.61</v>
+      </c>
+      <c r="AD22">
+        <v>1.39</v>
+      </c>
+      <c r="AE22">
         <v>1.11</v>
       </c>
-      <c r="Z22">
-        <v>4.95</v>
-      </c>
-      <c r="AA22">
-        <v>1.5</v>
-      </c>
-      <c r="AB22">
-        <v>2.4</v>
-      </c>
-      <c r="AC22">
-        <v>2.25</v>
-      </c>
-      <c r="AD22">
+      <c r="AF22">
         <v>1.57</v>
       </c>
-      <c r="AE22">
-        <v>1.22</v>
-      </c>
-      <c r="AF22">
-        <v>1.4</v>
-      </c>
       <c r="AG22">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK22">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.98</v>
+        <v>2.44</v>
       </c>
       <c r="O23">
-        <v>3.66</v>
+        <v>3.52</v>
       </c>
       <c r="P23">
-        <v>3.34</v>
+        <v>2.64</v>
       </c>
       <c r="Q23">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="R23">
         <v>2.26</v>
       </c>
       <c r="S23">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T23">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="U23">
-        <v>2.41</v>
+        <v>2.2</v>
       </c>
       <c r="V23">
+        <v>1.6</v>
+      </c>
+      <c r="W23">
+        <v>1.14</v>
+      </c>
+      <c r="X23">
+        <v>1.02</v>
+      </c>
+      <c r="Y23">
+        <v>1.11</v>
+      </c>
+      <c r="Z23">
+        <v>4.95</v>
+      </c>
+      <c r="AA23">
         <v>1.5</v>
       </c>
-      <c r="W23">
-        <v>1.08</v>
-      </c>
-      <c r="X23">
-        <v>1.04</v>
-      </c>
-      <c r="Y23">
-        <v>1.16</v>
-      </c>
-      <c r="Z23">
-        <v>4.15</v>
-      </c>
-      <c r="AA23">
-        <v>1.68</v>
-      </c>
       <c r="AB23">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="AC23">
-        <v>2.61</v>
+        <v>2.25</v>
       </c>
       <c r="AD23">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="AE23">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AF23">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AG23">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK23">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="O25">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P25">
         <v>5</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="O26">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P26">
-        <v>6.19</v>
+        <v>6</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4710,19 +4710,19 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O27">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P27">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q27">
-        <v>3.66</v>
+        <v>4.05</v>
       </c>
       <c r="R27">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="S27">
         <v>1.44</v>
@@ -4764,7 +4764,7 @@
         <v>1.05</v>
       </c>
       <c r="AF27">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG27">
         <v>1.95</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="O31">
         <v>3.3</v>
@@ -5371,10 +5371,10 @@
         <v>3.8</v>
       </c>
       <c r="Q31">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="R31">
-        <v>2.05</v>
+        <v>2.32</v>
       </c>
       <c r="S31">
         <v>1.37</v>
@@ -5383,19 +5383,19 @@
         <v>2.74</v>
       </c>
       <c r="U31">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="V31">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W31">
         <v>1.07</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y31">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z31">
         <v>3.48</v>
@@ -5404,13 +5404,13 @@
         <v>1.9</v>
       </c>
       <c r="AB31">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC31">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="AD31">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE31">
         <v>1.07</v>
@@ -5419,7 +5419,7 @@
         <v>1.74</v>
       </c>
       <c r="AG31">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.27</v>
       </c>
       <c r="AK31">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O34">
         <v>2.9</v>
@@ -5863,7 +5863,7 @@
         <v>2.86</v>
       </c>
       <c r="R34">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="S34">
         <v>1.51</v>
@@ -5884,22 +5884,22 @@
         <v>1.05</v>
       </c>
       <c r="Y34">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="Z34">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="AA34">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AB34">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AC34">
-        <v>4.39</v>
+        <v>4.35</v>
       </c>
       <c r="AD34">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE34">
         <v>1.01</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AK34">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6135,22 +6135,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q36">
-        <v>2.98</v>
+        <v>3.27</v>
       </c>
       <c r="R36">
-        <v>1.88</v>
+        <v>2.01</v>
       </c>
       <c r="S36">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T36">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="U36">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="V36">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W36">
+        <v>1.05</v>
+      </c>
+      <c r="X36">
+        <v>1.04</v>
+      </c>
+      <c r="Y36">
+        <v>1.4</v>
+      </c>
+      <c r="Z36">
+        <v>2.88</v>
+      </c>
+      <c r="AA36">
+        <v>2.38</v>
+      </c>
+      <c r="AB36">
+        <v>1.56</v>
+      </c>
+      <c r="AC36">
+        <v>4.33</v>
+      </c>
+      <c r="AD36">
+        <v>1.14</v>
+      </c>
+      <c r="AE36">
         <v>1.02</v>
       </c>
-      <c r="X36">
-        <v>1.05</v>
-      </c>
-      <c r="Y36">
-        <v>1.38</v>
-      </c>
-      <c r="Z36">
-        <v>2.62</v>
-      </c>
-      <c r="AA36">
-        <v>2.23</v>
-      </c>
-      <c r="AB36">
-        <v>1.57</v>
-      </c>
-      <c r="AC36">
-        <v>3.92</v>
-      </c>
-      <c r="AD36">
-        <v>1.18</v>
-      </c>
-      <c r="AE36">
-        <v>1.03</v>
-      </c>
       <c r="AF36">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AG36">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK36">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G37">
@@ -6349,55 +6349,55 @@
         <v>0</v>
       </c>
       <c r="Q37">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S37">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T37">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U37">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="V37">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X37">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y37">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z37">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA37">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AB37">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC37">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD37">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF37">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AG37">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK37">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G38">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N38">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G39">
@@ -6769,1799 +6769,6 @@
         <v>0</v>
       </c>
       <c r="AU39" t="inlineStr">
-        <is>
-          <t>2026-09-03 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Azerbaijan Premyer Liqası</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Neftçi</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Safa</t>
-        </is>
-      </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-      <c r="H40">
-        <v>0</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
-      <c r="K40">
-        <v>0</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
-      <c r="O40">
-        <v>0</v>
-      </c>
-      <c r="P40">
-        <v>0</v>
-      </c>
-      <c r="Q40">
-        <v>0</v>
-      </c>
-      <c r="R40">
-        <v>0</v>
-      </c>
-      <c r="S40">
-        <v>0</v>
-      </c>
-      <c r="T40">
-        <v>0</v>
-      </c>
-      <c r="U40">
-        <v>0</v>
-      </c>
-      <c r="V40">
-        <v>0</v>
-      </c>
-      <c r="W40">
-        <v>0</v>
-      </c>
-      <c r="X40">
-        <v>0</v>
-      </c>
-      <c r="Y40">
-        <v>0</v>
-      </c>
-      <c r="Z40">
-        <v>0</v>
-      </c>
-      <c r="AA40">
-        <v>0</v>
-      </c>
-      <c r="AB40">
-        <v>0</v>
-      </c>
-      <c r="AC40">
-        <v>0</v>
-      </c>
-      <c r="AD40">
-        <v>0</v>
-      </c>
-      <c r="AE40">
-        <v>0</v>
-      </c>
-      <c r="AF40">
-        <v>0</v>
-      </c>
-      <c r="AG40">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>0</v>
-      </c>
-      <c r="AK40">
-        <v>0</v>
-      </c>
-      <c r="AL40">
-        <v>0</v>
-      </c>
-      <c r="AM40">
-        <v>-1</v>
-      </c>
-      <c r="AN40">
-        <v>-1</v>
-      </c>
-      <c r="AO40">
-        <v>-1</v>
-      </c>
-      <c r="AP40">
-        <v>-1</v>
-      </c>
-      <c r="AQ40">
-        <v>0</v>
-      </c>
-      <c r="AR40">
-        <v>0</v>
-      </c>
-      <c r="AS40">
-        <v>0</v>
-      </c>
-      <c r="AT40">
-        <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>2026-09-03 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Azerbaijan Premyer Liqası</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Qarabağ</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Araz</t>
-        </is>
-      </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
-      <c r="H41">
-        <v>0</v>
-      </c>
-      <c r="I41">
-        <v>0</v>
-      </c>
-      <c r="J41">
-        <v>0</v>
-      </c>
-      <c r="K41">
-        <v>0</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41">
-        <v>0</v>
-      </c>
-      <c r="P41">
-        <v>0</v>
-      </c>
-      <c r="Q41">
-        <v>0</v>
-      </c>
-      <c r="R41">
-        <v>0</v>
-      </c>
-      <c r="S41">
-        <v>0</v>
-      </c>
-      <c r="T41">
-        <v>0</v>
-      </c>
-      <c r="U41">
-        <v>0</v>
-      </c>
-      <c r="V41">
-        <v>0</v>
-      </c>
-      <c r="W41">
-        <v>0</v>
-      </c>
-      <c r="X41">
-        <v>0</v>
-      </c>
-      <c r="Y41">
-        <v>0</v>
-      </c>
-      <c r="Z41">
-        <v>0</v>
-      </c>
-      <c r="AA41">
-        <v>0</v>
-      </c>
-      <c r="AB41">
-        <v>0</v>
-      </c>
-      <c r="AC41">
-        <v>0</v>
-      </c>
-      <c r="AD41">
-        <v>0</v>
-      </c>
-      <c r="AE41">
-        <v>0</v>
-      </c>
-      <c r="AF41">
-        <v>0</v>
-      </c>
-      <c r="AG41">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>0</v>
-      </c>
-      <c r="AK41">
-        <v>0</v>
-      </c>
-      <c r="AL41">
-        <v>0</v>
-      </c>
-      <c r="AM41">
-        <v>-1</v>
-      </c>
-      <c r="AN41">
-        <v>-1</v>
-      </c>
-      <c r="AO41">
-        <v>-1</v>
-      </c>
-      <c r="AP41">
-        <v>-1</v>
-      </c>
-      <c r="AQ41">
-        <v>0</v>
-      </c>
-      <c r="AR41">
-        <v>0</v>
-      </c>
-      <c r="AS41">
-        <v>0</v>
-      </c>
-      <c r="AT41">
-        <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>2026-09-03 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Libertad</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>CS Emelec</t>
-        </is>
-      </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
-      <c r="K42">
-        <v>0</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N42">
-        <v>2.25</v>
-      </c>
-      <c r="O42">
-        <v>3</v>
-      </c>
-      <c r="P42">
-        <v>2.9</v>
-      </c>
-      <c r="Q42">
-        <v>3.15</v>
-      </c>
-      <c r="R42">
-        <v>1.89</v>
-      </c>
-      <c r="S42">
-        <v>1.48</v>
-      </c>
-      <c r="T42">
-        <v>2.38</v>
-      </c>
-      <c r="U42">
-        <v>3.32</v>
-      </c>
-      <c r="V42">
-        <v>1.29</v>
-      </c>
-      <c r="W42">
-        <v>1.02</v>
-      </c>
-      <c r="X42">
-        <v>1.05</v>
-      </c>
-      <c r="Y42">
-        <v>1.41</v>
-      </c>
-      <c r="Z42">
-        <v>2.58</v>
-      </c>
-      <c r="AA42">
-        <v>2.35</v>
-      </c>
-      <c r="AB42">
-        <v>1.57</v>
-      </c>
-      <c r="AC42">
-        <v>4.52</v>
-      </c>
-      <c r="AD42">
-        <v>1.18</v>
-      </c>
-      <c r="AE42">
-        <v>1.01</v>
-      </c>
-      <c r="AF42">
-        <v>1.95</v>
-      </c>
-      <c r="AG42">
-        <v>1.74</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42">
-        <v>1.32</v>
-      </c>
-      <c r="AK42">
-        <v>1.52</v>
-      </c>
-      <c r="AL42">
-        <v>0</v>
-      </c>
-      <c r="AM42">
-        <v>-1</v>
-      </c>
-      <c r="AN42">
-        <v>-1</v>
-      </c>
-      <c r="AO42">
-        <v>-1</v>
-      </c>
-      <c r="AP42">
-        <v>-1</v>
-      </c>
-      <c r="AQ42">
-        <v>0</v>
-      </c>
-      <c r="AR42">
-        <v>0</v>
-      </c>
-      <c r="AS42">
-        <v>0</v>
-      </c>
-      <c r="AT42">
-        <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>2026-09-03 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Tunisia Ligue 1</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Zarzis</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Monastir</t>
-        </is>
-      </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
-      <c r="I43">
-        <v>0</v>
-      </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
-      <c r="K43">
-        <v>0</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
-      <c r="O43">
-        <v>0</v>
-      </c>
-      <c r="P43">
-        <v>0</v>
-      </c>
-      <c r="Q43">
-        <v>0</v>
-      </c>
-      <c r="R43">
-        <v>0</v>
-      </c>
-      <c r="S43">
-        <v>0</v>
-      </c>
-      <c r="T43">
-        <v>0</v>
-      </c>
-      <c r="U43">
-        <v>0</v>
-      </c>
-      <c r="V43">
-        <v>0</v>
-      </c>
-      <c r="W43">
-        <v>0</v>
-      </c>
-      <c r="X43">
-        <v>0</v>
-      </c>
-      <c r="Y43">
-        <v>0</v>
-      </c>
-      <c r="Z43">
-        <v>0</v>
-      </c>
-      <c r="AA43">
-        <v>0</v>
-      </c>
-      <c r="AB43">
-        <v>0</v>
-      </c>
-      <c r="AC43">
-        <v>0</v>
-      </c>
-      <c r="AD43">
-        <v>0</v>
-      </c>
-      <c r="AE43">
-        <v>0</v>
-      </c>
-      <c r="AF43">
-        <v>0</v>
-      </c>
-      <c r="AG43">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ43">
-        <v>0</v>
-      </c>
-      <c r="AK43">
-        <v>0</v>
-      </c>
-      <c r="AL43">
-        <v>0</v>
-      </c>
-      <c r="AM43">
-        <v>-1</v>
-      </c>
-      <c r="AN43">
-        <v>-1</v>
-      </c>
-      <c r="AO43">
-        <v>-1</v>
-      </c>
-      <c r="AP43">
-        <v>-1</v>
-      </c>
-      <c r="AQ43">
-        <v>0</v>
-      </c>
-      <c r="AR43">
-        <v>0</v>
-      </c>
-      <c r="AS43">
-        <v>0</v>
-      </c>
-      <c r="AT43">
-        <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>2026-09-03 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Tunisia Ligue 1</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Etoile du Sahel</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Jeunesse Sportive Omrane</t>
-        </is>
-      </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
-      <c r="I44">
-        <v>0</v>
-      </c>
-      <c r="J44">
-        <v>0</v>
-      </c>
-      <c r="K44">
-        <v>0</v>
-      </c>
-      <c r="L44">
-        <v>0</v>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N44">
-        <v>0</v>
-      </c>
-      <c r="O44">
-        <v>0</v>
-      </c>
-      <c r="P44">
-        <v>0</v>
-      </c>
-      <c r="Q44">
-        <v>0</v>
-      </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
-      <c r="S44">
-        <v>0</v>
-      </c>
-      <c r="T44">
-        <v>0</v>
-      </c>
-      <c r="U44">
-        <v>0</v>
-      </c>
-      <c r="V44">
-        <v>0</v>
-      </c>
-      <c r="W44">
-        <v>0</v>
-      </c>
-      <c r="X44">
-        <v>0</v>
-      </c>
-      <c r="Y44">
-        <v>0</v>
-      </c>
-      <c r="Z44">
-        <v>0</v>
-      </c>
-      <c r="AA44">
-        <v>0</v>
-      </c>
-      <c r="AB44">
-        <v>0</v>
-      </c>
-      <c r="AC44">
-        <v>0</v>
-      </c>
-      <c r="AD44">
-        <v>0</v>
-      </c>
-      <c r="AE44">
-        <v>0</v>
-      </c>
-      <c r="AF44">
-        <v>0</v>
-      </c>
-      <c r="AG44">
-        <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ44">
-        <v>0</v>
-      </c>
-      <c r="AK44">
-        <v>0</v>
-      </c>
-      <c r="AL44">
-        <v>0</v>
-      </c>
-      <c r="AM44">
-        <v>-1</v>
-      </c>
-      <c r="AN44">
-        <v>-1</v>
-      </c>
-      <c r="AO44">
-        <v>-1</v>
-      </c>
-      <c r="AP44">
-        <v>-1</v>
-      </c>
-      <c r="AQ44">
-        <v>0</v>
-      </c>
-      <c r="AR44">
-        <v>0</v>
-      </c>
-      <c r="AS44">
-        <v>0</v>
-      </c>
-      <c r="AT44">
-        <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>2026-09-03 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Tunisia Ligue 1</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Progrès Sakiet Eddaïer</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Hammam-Lif</t>
-        </is>
-      </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
-      <c r="I45">
-        <v>0</v>
-      </c>
-      <c r="J45">
-        <v>0</v>
-      </c>
-      <c r="K45">
-        <v>0</v>
-      </c>
-      <c r="L45">
-        <v>0</v>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
-      <c r="O45">
-        <v>0</v>
-      </c>
-      <c r="P45">
-        <v>0</v>
-      </c>
-      <c r="Q45">
-        <v>0</v>
-      </c>
-      <c r="R45">
-        <v>0</v>
-      </c>
-      <c r="S45">
-        <v>0</v>
-      </c>
-      <c r="T45">
-        <v>0</v>
-      </c>
-      <c r="U45">
-        <v>0</v>
-      </c>
-      <c r="V45">
-        <v>0</v>
-      </c>
-      <c r="W45">
-        <v>0</v>
-      </c>
-      <c r="X45">
-        <v>0</v>
-      </c>
-      <c r="Y45">
-        <v>0</v>
-      </c>
-      <c r="Z45">
-        <v>0</v>
-      </c>
-      <c r="AA45">
-        <v>0</v>
-      </c>
-      <c r="AB45">
-        <v>0</v>
-      </c>
-      <c r="AC45">
-        <v>0</v>
-      </c>
-      <c r="AD45">
-        <v>0</v>
-      </c>
-      <c r="AE45">
-        <v>0</v>
-      </c>
-      <c r="AF45">
-        <v>0</v>
-      </c>
-      <c r="AG45">
-        <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ45">
-        <v>0</v>
-      </c>
-      <c r="AK45">
-        <v>0</v>
-      </c>
-      <c r="AL45">
-        <v>0</v>
-      </c>
-      <c r="AM45">
-        <v>-1</v>
-      </c>
-      <c r="AN45">
-        <v>-1</v>
-      </c>
-      <c r="AO45">
-        <v>-1</v>
-      </c>
-      <c r="AP45">
-        <v>-1</v>
-      </c>
-      <c r="AQ45">
-        <v>0</v>
-      </c>
-      <c r="AR45">
-        <v>0</v>
-      </c>
-      <c r="AS45">
-        <v>0</v>
-      </c>
-      <c r="AT45">
-        <v>0</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>2026-09-03 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Tunisia Ligue 1</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>CA Bizertin</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Olympique Béja</t>
-        </is>
-      </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="K46">
-        <v>0</v>
-      </c>
-      <c r="L46">
-        <v>0</v>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N46">
-        <v>0</v>
-      </c>
-      <c r="O46">
-        <v>0</v>
-      </c>
-      <c r="P46">
-        <v>0</v>
-      </c>
-      <c r="Q46">
-        <v>0</v>
-      </c>
-      <c r="R46">
-        <v>0</v>
-      </c>
-      <c r="S46">
-        <v>0</v>
-      </c>
-      <c r="T46">
-        <v>0</v>
-      </c>
-      <c r="U46">
-        <v>0</v>
-      </c>
-      <c r="V46">
-        <v>0</v>
-      </c>
-      <c r="W46">
-        <v>0</v>
-      </c>
-      <c r="X46">
-        <v>0</v>
-      </c>
-      <c r="Y46">
-        <v>0</v>
-      </c>
-      <c r="Z46">
-        <v>0</v>
-      </c>
-      <c r="AA46">
-        <v>0</v>
-      </c>
-      <c r="AB46">
-        <v>0</v>
-      </c>
-      <c r="AC46">
-        <v>0</v>
-      </c>
-      <c r="AD46">
-        <v>0</v>
-      </c>
-      <c r="AE46">
-        <v>0</v>
-      </c>
-      <c r="AF46">
-        <v>0</v>
-      </c>
-      <c r="AG46">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46">
-        <v>0</v>
-      </c>
-      <c r="AK46">
-        <v>0</v>
-      </c>
-      <c r="AL46">
-        <v>0</v>
-      </c>
-      <c r="AM46">
-        <v>-1</v>
-      </c>
-      <c r="AN46">
-        <v>-1</v>
-      </c>
-      <c r="AO46">
-        <v>-1</v>
-      </c>
-      <c r="AP46">
-        <v>-1</v>
-      </c>
-      <c r="AQ46">
-        <v>0</v>
-      </c>
-      <c r="AR46">
-        <v>0</v>
-      </c>
-      <c r="AS46">
-        <v>0</v>
-      </c>
-      <c r="AT46">
-        <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>2026-09-03 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Tunisia Ligue 1</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Stade Tunisien</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Club Africain</t>
-        </is>
-      </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-      <c r="H47">
-        <v>0</v>
-      </c>
-      <c r="I47">
-        <v>0</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47">
-        <v>0</v>
-      </c>
-      <c r="L47">
-        <v>0</v>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="N47">
-        <v>0</v>
-      </c>
-      <c r="O47">
-        <v>0</v>
-      </c>
-      <c r="P47">
-        <v>0</v>
-      </c>
-      <c r="Q47">
-        <v>0</v>
-      </c>
-      <c r="R47">
-        <v>0</v>
-      </c>
-      <c r="S47">
-        <v>0</v>
-      </c>
-      <c r="T47">
-        <v>0</v>
-      </c>
-      <c r="U47">
-        <v>0</v>
-      </c>
-      <c r="V47">
-        <v>0</v>
-      </c>
-      <c r="W47">
-        <v>0</v>
-      </c>
-      <c r="X47">
-        <v>0</v>
-      </c>
-      <c r="Y47">
-        <v>0</v>
-      </c>
-      <c r="Z47">
-        <v>0</v>
-      </c>
-      <c r="AA47">
-        <v>0</v>
-      </c>
-      <c r="AB47">
-        <v>0</v>
-      </c>
-      <c r="AC47">
-        <v>0</v>
-      </c>
-      <c r="AD47">
-        <v>0</v>
-      </c>
-      <c r="AE47">
-        <v>0</v>
-      </c>
-      <c r="AF47">
-        <v>0</v>
-      </c>
-      <c r="AG47">
-        <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47">
-        <v>0</v>
-      </c>
-      <c r="AK47">
-        <v>0</v>
-      </c>
-      <c r="AL47">
-        <v>0</v>
-      </c>
-      <c r="AM47">
-        <v>-1</v>
-      </c>
-      <c r="AN47">
-        <v>-1</v>
-      </c>
-      <c r="AO47">
-        <v>-1</v>
-      </c>
-      <c r="AP47">
-        <v>-1</v>
-      </c>
-      <c r="AQ47">
-        <v>0</v>
-      </c>
-      <c r="AR47">
-        <v>0</v>
-      </c>
-      <c r="AS47">
-        <v>0</v>
-      </c>
-      <c r="AT47">
-        <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>2026-09-03 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Tunisia Ligue 1</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>ES Tunis</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Marsa</t>
-        </is>
-      </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48">
-        <v>0</v>
-      </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
-      <c r="O48">
-        <v>0</v>
-      </c>
-      <c r="P48">
-        <v>0</v>
-      </c>
-      <c r="Q48">
-        <v>0</v>
-      </c>
-      <c r="R48">
-        <v>0</v>
-      </c>
-      <c r="S48">
-        <v>0</v>
-      </c>
-      <c r="T48">
-        <v>0</v>
-      </c>
-      <c r="U48">
-        <v>0</v>
-      </c>
-      <c r="V48">
-        <v>0</v>
-      </c>
-      <c r="W48">
-        <v>0</v>
-      </c>
-      <c r="X48">
-        <v>0</v>
-      </c>
-      <c r="Y48">
-        <v>0</v>
-      </c>
-      <c r="Z48">
-        <v>0</v>
-      </c>
-      <c r="AA48">
-        <v>0</v>
-      </c>
-      <c r="AB48">
-        <v>0</v>
-      </c>
-      <c r="AC48">
-        <v>0</v>
-      </c>
-      <c r="AD48">
-        <v>0</v>
-      </c>
-      <c r="AE48">
-        <v>0</v>
-      </c>
-      <c r="AF48">
-        <v>0</v>
-      </c>
-      <c r="AG48">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>0</v>
-      </c>
-      <c r="AK48">
-        <v>0</v>
-      </c>
-      <c r="AL48">
-        <v>0</v>
-      </c>
-      <c r="AM48">
-        <v>-1</v>
-      </c>
-      <c r="AN48">
-        <v>-1</v>
-      </c>
-      <c r="AO48">
-        <v>-1</v>
-      </c>
-      <c r="AP48">
-        <v>-1</v>
-      </c>
-      <c r="AQ48">
-        <v>0</v>
-      </c>
-      <c r="AR48">
-        <v>0</v>
-      </c>
-      <c r="AS48">
-        <v>0</v>
-      </c>
-      <c r="AT48">
-        <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>2026-09-03 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Tunisia Ligue 1</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Métlaoui</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Hammam-Sousse</t>
-        </is>
-      </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>0</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
-      <c r="O49">
-        <v>0</v>
-      </c>
-      <c r="P49">
-        <v>0</v>
-      </c>
-      <c r="Q49">
-        <v>0</v>
-      </c>
-      <c r="R49">
-        <v>0</v>
-      </c>
-      <c r="S49">
-        <v>0</v>
-      </c>
-      <c r="T49">
-        <v>0</v>
-      </c>
-      <c r="U49">
-        <v>0</v>
-      </c>
-      <c r="V49">
-        <v>0</v>
-      </c>
-      <c r="W49">
-        <v>0</v>
-      </c>
-      <c r="X49">
-        <v>0</v>
-      </c>
-      <c r="Y49">
-        <v>0</v>
-      </c>
-      <c r="Z49">
-        <v>0</v>
-      </c>
-      <c r="AA49">
-        <v>0</v>
-      </c>
-      <c r="AB49">
-        <v>0</v>
-      </c>
-      <c r="AC49">
-        <v>0</v>
-      </c>
-      <c r="AD49">
-        <v>0</v>
-      </c>
-      <c r="AE49">
-        <v>0</v>
-      </c>
-      <c r="AF49">
-        <v>0</v>
-      </c>
-      <c r="AG49">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>0</v>
-      </c>
-      <c r="AK49">
-        <v>0</v>
-      </c>
-      <c r="AL49">
-        <v>0</v>
-      </c>
-      <c r="AM49">
-        <v>-1</v>
-      </c>
-      <c r="AN49">
-        <v>-1</v>
-      </c>
-      <c r="AO49">
-        <v>-1</v>
-      </c>
-      <c r="AP49">
-        <v>-1</v>
-      </c>
-      <c r="AQ49">
-        <v>0</v>
-      </c>
-      <c r="AR49">
-        <v>0</v>
-      </c>
-      <c r="AS49">
-        <v>0</v>
-      </c>
-      <c r="AT49">
-        <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>2026-09-03 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Tunisia Ligue 1</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Ben Guerdane</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>CS Sfaxien</t>
-        </is>
-      </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
-      <c r="H50">
-        <v>0</v>
-      </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50">
-        <v>0</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N50">
-        <v>0</v>
-      </c>
-      <c r="O50">
-        <v>0</v>
-      </c>
-      <c r="P50">
-        <v>0</v>
-      </c>
-      <c r="Q50">
-        <v>0</v>
-      </c>
-      <c r="R50">
-        <v>0</v>
-      </c>
-      <c r="S50">
-        <v>0</v>
-      </c>
-      <c r="T50">
-        <v>0</v>
-      </c>
-      <c r="U50">
-        <v>0</v>
-      </c>
-      <c r="V50">
-        <v>0</v>
-      </c>
-      <c r="W50">
-        <v>0</v>
-      </c>
-      <c r="X50">
-        <v>0</v>
-      </c>
-      <c r="Y50">
-        <v>0</v>
-      </c>
-      <c r="Z50">
-        <v>0</v>
-      </c>
-      <c r="AA50">
-        <v>0</v>
-      </c>
-      <c r="AB50">
-        <v>0</v>
-      </c>
-      <c r="AC50">
-        <v>0</v>
-      </c>
-      <c r="AD50">
-        <v>0</v>
-      </c>
-      <c r="AE50">
-        <v>0</v>
-      </c>
-      <c r="AF50">
-        <v>0</v>
-      </c>
-      <c r="AG50">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>0</v>
-      </c>
-      <c r="AK50">
-        <v>0</v>
-      </c>
-      <c r="AL50">
-        <v>0</v>
-      </c>
-      <c r="AM50">
-        <v>-1</v>
-      </c>
-      <c r="AN50">
-        <v>-1</v>
-      </c>
-      <c r="AO50">
-        <v>-1</v>
-      </c>
-      <c r="AP50">
-        <v>-1</v>
-      </c>
-      <c r="AQ50">
-        <v>0</v>
-      </c>
-      <c r="AR50">
-        <v>0</v>
-      </c>
-      <c r="AS50">
-        <v>0</v>
-      </c>
-      <c r="AT50">
-        <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
         <is>
           <t>2026-09-03 21:00:00</t>
         </is>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.98</v>
+        <v>2.44</v>
       </c>
       <c r="O22">
-        <v>3.66</v>
+        <v>3.52</v>
       </c>
       <c r="P22">
-        <v>3.34</v>
+        <v>2.64</v>
       </c>
       <c r="Q22">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="R22">
         <v>2.26</v>
       </c>
       <c r="S22">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T22">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="U22">
-        <v>2.41</v>
+        <v>2.2</v>
       </c>
       <c r="V22">
+        <v>1.6</v>
+      </c>
+      <c r="W22">
+        <v>1.14</v>
+      </c>
+      <c r="X22">
+        <v>1.02</v>
+      </c>
+      <c r="Y22">
+        <v>1.11</v>
+      </c>
+      <c r="Z22">
+        <v>4.95</v>
+      </c>
+      <c r="AA22">
         <v>1.5</v>
       </c>
-      <c r="W22">
-        <v>1.08</v>
-      </c>
-      <c r="X22">
-        <v>1.04</v>
-      </c>
-      <c r="Y22">
-        <v>1.16</v>
-      </c>
-      <c r="Z22">
-        <v>4.15</v>
-      </c>
-      <c r="AA22">
-        <v>1.68</v>
-      </c>
       <c r="AB22">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="AC22">
-        <v>2.61</v>
+        <v>2.25</v>
       </c>
       <c r="AD22">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="AE22">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AF22">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AG22">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK22">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.44</v>
+        <v>1.98</v>
       </c>
       <c r="O23">
-        <v>3.52</v>
+        <v>3.66</v>
       </c>
       <c r="P23">
-        <v>2.64</v>
+        <v>3.34</v>
       </c>
       <c r="Q23">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="R23">
         <v>2.26</v>
       </c>
       <c r="S23">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T23">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="U23">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="V23">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="W23">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
+        <v>1.16</v>
+      </c>
+      <c r="Z23">
+        <v>4.15</v>
+      </c>
+      <c r="AA23">
+        <v>1.68</v>
+      </c>
+      <c r="AB23">
+        <v>2.14</v>
+      </c>
+      <c r="AC23">
+        <v>2.61</v>
+      </c>
+      <c r="AD23">
+        <v>1.39</v>
+      </c>
+      <c r="AE23">
         <v>1.11</v>
       </c>
-      <c r="Z23">
-        <v>4.95</v>
-      </c>
-      <c r="AA23">
-        <v>1.5</v>
-      </c>
-      <c r="AB23">
-        <v>2.4</v>
-      </c>
-      <c r="AC23">
-        <v>2.25</v>
-      </c>
-      <c r="AD23">
+      <c r="AF23">
         <v>1.57</v>
       </c>
-      <c r="AE23">
-        <v>1.22</v>
-      </c>
-      <c r="AF23">
-        <v>1.4</v>
-      </c>
       <c r="AG23">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK23">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="AL23">
         <v>0</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="O3">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="P3">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="Q3">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="R3">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="S3">
         <v>1.34</v>
@@ -822,25 +822,25 @@
         <v>2.75</v>
       </c>
       <c r="V3">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
         <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
         <v>1.25</v>
       </c>
       <c r="Z3">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA3">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB3">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC3">
         <v>2.92</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK3">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1130,43 +1130,43 @@
         <v>2.5</v>
       </c>
       <c r="P5">
-        <v>4.8</v>
+        <v>4.82</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W5">
         <v>0</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1178,10 +1178,10 @@
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2265,34 +2265,34 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="O12">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="P12">
-        <v>6.62</v>
+        <v>8.35</v>
       </c>
       <c r="Q12">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="R12">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="S12">
+        <v>1.39</v>
+      </c>
+      <c r="T12">
+        <v>2.93</v>
+      </c>
+      <c r="U12">
+        <v>2.9</v>
+      </c>
+      <c r="V12">
         <v>1.38</v>
       </c>
-      <c r="T12">
-        <v>2.91</v>
-      </c>
-      <c r="U12">
-        <v>2.75</v>
-      </c>
-      <c r="V12">
-        <v>1.37</v>
-      </c>
       <c r="W12">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X12">
         <v>1.03</v>
@@ -2313,16 +2313,16 @@
         <v>3.34</v>
       </c>
       <c r="AD12">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AE12">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF12">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AG12">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK12">
-        <v>2.55</v>
+        <v>2.72</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2603,7 +2603,7 @@
         <v>3.42</v>
       </c>
       <c r="R14">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S14">
         <v>1.42</v>
@@ -2664,7 +2664,7 @@
         <v>1.29</v>
       </c>
       <c r="AK14">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,25 +2754,25 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="O15">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="P15">
-        <v>5.33</v>
+        <v>5.75</v>
       </c>
       <c r="Q15">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="R15">
         <v>2.5</v>
       </c>
       <c r="S15">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T15">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="U15">
         <v>2.5</v>
@@ -2805,13 +2805,13 @@
         <v>1.45</v>
       </c>
       <c r="AE15">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF15">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG15">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>1.14</v>
       </c>
       <c r="AK15">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="AL15">
         <v>0</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -807,10 +807,10 @@
         <v>3.17</v>
       </c>
       <c r="Q3">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="R3">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="S3">
         <v>1.34</v>
@@ -840,7 +840,7 @@
         <v>1.8</v>
       </c>
       <c r="AB3">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC3">
         <v>2.92</v>
@@ -871,7 +871,7 @@
         <v>1.24</v>
       </c>
       <c r="AK3">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O4">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="Q4">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="R4">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="S4">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T4">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U4">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="V4">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W4">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
         <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z4">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AA4">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AB4">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="AC4">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="AD4">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE4">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AF4">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG4">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1287,25 +1287,25 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O6">
         <v>3.3</v>
       </c>
       <c r="P6">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q6">
         <v>3.2</v>
       </c>
       <c r="R6">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S6">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T6">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="U6">
         <v>2.96</v>
@@ -1320,10 +1320,10 @@
         <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z6">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="AA6">
         <v>2.1</v>
@@ -1332,7 +1332,7 @@
         <v>1.66</v>
       </c>
       <c r="AC6">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="AD6">
         <v>1.21</v>
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="N8">
+        <v>2.1</v>
+      </c>
+      <c r="O8">
+        <v>3.3</v>
+      </c>
+      <c r="P8">
+        <v>2.9</v>
+      </c>
+      <c r="Q8">
+        <v>2.54</v>
+      </c>
+      <c r="R8">
         <v>2.15</v>
-      </c>
-      <c r="O8">
-        <v>3.25</v>
-      </c>
-      <c r="P8">
-        <v>3.15</v>
-      </c>
-      <c r="Q8">
-        <v>2.71</v>
-      </c>
-      <c r="R8">
-        <v>2.2</v>
       </c>
       <c r="S8">
         <v>1.35</v>
@@ -1634,10 +1634,10 @@
         <v>2.9</v>
       </c>
       <c r="U8">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="V8">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W8">
         <v>1.06</v>
@@ -1646,7 +1646,7 @@
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z8">
         <v>3.58</v>
@@ -1667,7 +1667,7 @@
         <v>1.09</v>
       </c>
       <c r="AF8">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AG8">
         <v>2.13</v>
@@ -1686,7 +1686,7 @@
         <v>1.28</v>
       </c>
       <c r="AK8">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1815,10 +1815,10 @@
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>4.01</v>
+        <v>5.3</v>
       </c>
       <c r="O10">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="P10">
-        <v>1.63</v>
+        <v>1.46</v>
       </c>
       <c r="Q10">
-        <v>4.88</v>
+        <v>5.44</v>
       </c>
       <c r="R10">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="S10">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T10">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="U10">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="V10">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="W10">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X10">
         <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z10">
-        <v>5.15</v>
+        <v>5.63</v>
       </c>
       <c r="AA10">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AB10">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="AC10">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AD10">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AE10">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AF10">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG10">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AK10">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,16 +2102,16 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q11">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="R11">
         <v>2.2</v>
@@ -2120,7 +2120,7 @@
         <v>1.31</v>
       </c>
       <c r="T11">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="U11">
         <v>2.53</v>
@@ -2132,7 +2132,7 @@
         <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
         <v>1.2</v>
@@ -2141,10 +2141,10 @@
         <v>3.58</v>
       </c>
       <c r="AA11">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB11">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC11">
         <v>2.7</v>
@@ -2153,13 +2153,13 @@
         <v>1.33</v>
       </c>
       <c r="AE11">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AF11">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AG11">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>4.1</v>
       </c>
       <c r="P12">
-        <v>8.35</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q12">
         <v>1.94</v>
@@ -2283,16 +2283,16 @@
         <v>1.39</v>
       </c>
       <c r="T12">
-        <v>2.93</v>
+        <v>2.66</v>
       </c>
       <c r="U12">
         <v>2.9</v>
       </c>
       <c r="V12">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W12">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
         <v>1.03</v>
@@ -2307,7 +2307,7 @@
         <v>2</v>
       </c>
       <c r="AB12">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC12">
         <v>3.34</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q14">
-        <v>3.42</v>
+        <v>1.92</v>
       </c>
       <c r="R14">
-        <v>1.95</v>
+        <v>2.34</v>
       </c>
       <c r="S14">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="T14">
-        <v>2.56</v>
+        <v>3.12</v>
       </c>
       <c r="U14">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="V14">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="W14">
+        <v>1.07</v>
+      </c>
+      <c r="X14">
         <v>1.03</v>
       </c>
-      <c r="X14">
-        <v>1.02</v>
-      </c>
       <c r="Y14">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z14">
-        <v>3.2</v>
+        <v>3.88</v>
       </c>
       <c r="AA14">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AB14">
-        <v>1.72</v>
+        <v>2.04</v>
       </c>
       <c r="AC14">
-        <v>3.6</v>
+        <v>2.66</v>
       </c>
       <c r="AD14">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AE14">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AG14">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AK14">
-        <v>1.38</v>
+        <v>2.57</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.44</v>
+        <v>2.48</v>
       </c>
       <c r="O15">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="P15">
-        <v>5.75</v>
+        <v>2.45</v>
       </c>
       <c r="Q15">
-        <v>1.84</v>
+        <v>3.42</v>
       </c>
       <c r="R15">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="S15">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T15">
-        <v>3.08</v>
+        <v>2.56</v>
       </c>
       <c r="U15">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="V15">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="W15">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="Z15">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA15">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AB15">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="AC15">
-        <v>2.75</v>
+        <v>3.34</v>
       </c>
       <c r="AD15">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="AE15">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AF15">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AG15">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AK15">
-        <v>2.57</v>
+        <v>1.37</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2920,61 +2920,61 @@
         <v>3.8</v>
       </c>
       <c r="O16">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P16">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="Q16">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="R16">
-        <v>2.43</v>
+        <v>2.28</v>
       </c>
       <c r="S16">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T16">
         <v>3.2</v>
       </c>
       <c r="U16">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="V16">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="W16">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X16">
         <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z16">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="AA16">
         <v>1.48</v>
       </c>
       <c r="AB16">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AC16">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AD16">
         <v>1.57</v>
       </c>
       <c r="AE16">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF16">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AG16">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK16">
-        <v>1.37</v>
+        <v>1.16</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,16 +3080,16 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O17">
         <v>3.5</v>
       </c>
       <c r="P17">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Q17">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="R17">
         <v>2.22</v>
@@ -3116,13 +3116,13 @@
         <v>1.19</v>
       </c>
       <c r="Z17">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="AA17">
         <v>1.72</v>
       </c>
       <c r="AB17">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AC17">
         <v>2.66</v>
@@ -3131,7 +3131,7 @@
         <v>1.37</v>
       </c>
       <c r="AE17">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF17">
         <v>1.58</v>
@@ -3153,7 +3153,7 @@
         <v>1.26</v>
       </c>
       <c r="AK17">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="O18">
         <v>4.6</v>
@@ -3264,10 +3264,10 @@
         <v>3.5</v>
       </c>
       <c r="U18">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="V18">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W18">
         <v>1.14</v>
@@ -3282,16 +3282,16 @@
         <v>4.85</v>
       </c>
       <c r="AA18">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AB18">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="AC18">
         <v>2.07</v>
       </c>
       <c r="AD18">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE18">
         <v>1.21</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK18">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,31 +3406,31 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="O19">
         <v>3.4</v>
       </c>
       <c r="P19">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Q19">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="R19">
-        <v>2.22</v>
+        <v>1.93</v>
       </c>
       <c r="S19">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T19">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U19">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="V19">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="W19">
         <v>1.05</v>
@@ -3439,31 +3439,31 @@
         <v>1.05</v>
       </c>
       <c r="Y19">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z19">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="AA19">
-        <v>2.21</v>
+        <v>2.37</v>
       </c>
       <c r="AB19">
         <v>1.59</v>
       </c>
       <c r="AC19">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AD19">
         <v>1.18</v>
       </c>
       <c r="AE19">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF19">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AG19">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AK19">
-        <v>1.9</v>
+        <v>2.31</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,16 +3569,16 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="O20">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
         <v>3</v>
       </c>
       <c r="Q20">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="R20">
         <v>2.45</v>
@@ -3587,7 +3587,7 @@
         <v>1.22</v>
       </c>
       <c r="T20">
-        <v>3.8</v>
+        <v>3.66</v>
       </c>
       <c r="U20">
         <v>2.14</v>
@@ -3596,31 +3596,31 @@
         <v>1.66</v>
       </c>
       <c r="W20">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z20">
         <v>5.25</v>
       </c>
       <c r="AA20">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AB20">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="AC20">
         <v>2.2</v>
       </c>
       <c r="AD20">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AE20">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AF20">
         <v>1.44</v>
@@ -3642,7 +3642,7 @@
         <v>1.34</v>
       </c>
       <c r="AK20">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3771,10 +3771,10 @@
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC21">
         <v>0</v>
@@ -3937,13 +3937,13 @@
         <v>1.5</v>
       </c>
       <c r="AB22">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AC22">
         <v>2.25</v>
       </c>
       <c r="AD22">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AE22">
         <v>1.22</v>
@@ -3952,7 +3952,7 @@
         <v>1.4</v>
       </c>
       <c r="AG22">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4058,25 +4058,25 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="O23">
-        <v>3.66</v>
+        <v>3.4</v>
       </c>
       <c r="P23">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="Q23">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="R23">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="S23">
         <v>1.28</v>
       </c>
       <c r="T23">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="U23">
         <v>2.41</v>
@@ -4094,22 +4094,22 @@
         <v>1.16</v>
       </c>
       <c r="Z23">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA23">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB23">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AC23">
-        <v>2.61</v>
+        <v>2.71</v>
       </c>
       <c r="AD23">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE23">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF23">
         <v>1.57</v>
@@ -4131,7 +4131,7 @@
         <v>1.26</v>
       </c>
       <c r="AK23">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,31 +4221,31 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="O24">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P24">
-        <v>4.05</v>
+        <v>4.45</v>
       </c>
       <c r="Q24">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="R24">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="S24">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T24">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="U24">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V24">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W24">
         <v>1.13</v>
@@ -4257,25 +4257,25 @@
         <v>1.09</v>
       </c>
       <c r="Z24">
-        <v>5.4</v>
+        <v>5.35</v>
       </c>
       <c r="AA24">
         <v>1.47</v>
       </c>
       <c r="AB24">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="AC24">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="AD24">
         <v>1.65</v>
       </c>
       <c r="AE24">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF24">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG24">
         <v>2.45</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="O25">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P25">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4553,7 +4553,7 @@
         <v>4.5</v>
       </c>
       <c r="P26">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4710,25 +4710,25 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="O27">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P27">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q27">
         <v>4.05</v>
       </c>
       <c r="R27">
-        <v>2.07</v>
+        <v>2.24</v>
       </c>
       <c r="S27">
         <v>1.44</v>
       </c>
       <c r="T27">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="U27">
         <v>3.02</v>
@@ -4740,31 +4740,31 @@
         <v>1.05</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z27">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AA27">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AB27">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AC27">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="AD27">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE27">
         <v>1.05</v>
       </c>
       <c r="AF27">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG27">
         <v>1.95</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK27">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="O28">
         <v>3.35</v>
       </c>
       <c r="P28">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="Q28">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="R28">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="S28">
         <v>1.36</v>
@@ -4903,7 +4903,7 @@
         <v>1.04</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y28">
         <v>1.22</v>
@@ -4918,13 +4918,13 @@
         <v>1.9</v>
       </c>
       <c r="AC28">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AD28">
         <v>1.31</v>
       </c>
       <c r="AE28">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF28">
         <v>1.63</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="O29">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P29">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="Q29">
         <v>2.45</v>
@@ -5063,10 +5063,10 @@
         <v>1.35</v>
       </c>
       <c r="W29">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y29">
         <v>1.26</v>
@@ -5075,19 +5075,19 @@
         <v>3.2</v>
       </c>
       <c r="AA29">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AB29">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AC29">
         <v>3.25</v>
       </c>
       <c r="AD29">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE29">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF29">
         <v>1.76</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="O32">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="P32">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q32">
         <v>2.57</v>
       </c>
       <c r="R32">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="S32">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T32">
-        <v>2.7</v>
+        <v>2.93</v>
       </c>
       <c r="U32">
-        <v>2.61</v>
+        <v>2.85</v>
       </c>
       <c r="V32">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W32">
         <v>1.06</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z32">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="AA32">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AB32">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AC32">
-        <v>2.95</v>
+        <v>3.22</v>
       </c>
       <c r="AD32">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE32">
         <v>1.07</v>
       </c>
       <c r="AF32">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG32">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>1.32</v>
       </c>
       <c r="AK32">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5691,52 +5691,52 @@
         <v>2.05</v>
       </c>
       <c r="O33">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="P33">
         <v>3.5</v>
       </c>
       <c r="Q33">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="R33">
         <v>2</v>
       </c>
       <c r="S33">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="T33">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="U33">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="V33">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="W33">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X33">
         <v>1.07</v>
       </c>
       <c r="Y33">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z33">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AA33">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AB33">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC33">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AD33">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE33">
         <v>1.01</v>
@@ -5745,7 +5745,7 @@
         <v>2</v>
       </c>
       <c r="AG33">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK33">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="O35">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="P35">
-        <v>3.85</v>
+        <v>3.18</v>
       </c>
       <c r="Q35">
         <v>2.6</v>
@@ -6029,46 +6029,46 @@
         <v>2</v>
       </c>
       <c r="S35">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T35">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="U35">
         <v>3</v>
       </c>
       <c r="V35">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W35">
         <v>1.02</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z35">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="AA35">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB35">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AC35">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AD35">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE35">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF35">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG35">
         <v>1.83</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK35">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AL35">
         <v>0</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1145,10 +1145,10 @@
         <v>1.77</v>
       </c>
       <c r="U5">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="V5">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O6">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="P6">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q6">
         <v>3.2</v>
@@ -1302,13 +1302,13 @@
         <v>1.98</v>
       </c>
       <c r="S6">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="T6">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="U6">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="V6">
         <v>1.32</v>
@@ -1323,16 +1323,16 @@
         <v>1.36</v>
       </c>
       <c r="Z6">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AA6">
         <v>2.1</v>
       </c>
       <c r="AB6">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC6">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="AD6">
         <v>1.21</v>
@@ -1450,43 +1450,43 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="O7">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P7">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="Q7">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="R7">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="S7">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T7">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="U7">
-        <v>2.79</v>
+        <v>2.53</v>
       </c>
       <c r="V7">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X7">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z7">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="AA7">
         <v>1.85</v>
@@ -1495,35 +1495,35 @@
         <v>1.95</v>
       </c>
       <c r="AC7">
-        <v>3.14</v>
+        <v>2.71</v>
       </c>
       <c r="AD7">
+        <v>1.43</v>
+      </c>
+      <c r="AE7">
+        <v>1.11</v>
+      </c>
+      <c r="AF7">
+        <v>1.69</v>
+      </c>
+      <c r="AG7">
+        <v>2</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
         <v>1.27</v>
       </c>
-      <c r="AE7">
-        <v>1.07</v>
-      </c>
-      <c r="AF7">
-        <v>1.78</v>
-      </c>
-      <c r="AG7">
-        <v>1.89</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.31</v>
-      </c>
       <c r="AK7">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2102,16 +2102,16 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="O11">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P11">
-        <v>3.85</v>
+        <v>4.33</v>
       </c>
       <c r="Q11">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R11">
         <v>2.2</v>
@@ -2138,28 +2138,28 @@
         <v>1.2</v>
       </c>
       <c r="Z11">
-        <v>3.58</v>
+        <v>3.92</v>
       </c>
       <c r="AA11">
         <v>1.8</v>
       </c>
       <c r="AB11">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AC11">
         <v>2.7</v>
       </c>
       <c r="AD11">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AE11">
         <v>1.09</v>
       </c>
       <c r="AF11">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AG11">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>4.1</v>
       </c>
       <c r="P12">
-        <v>8.199999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="Q12">
         <v>1.94</v>
@@ -2286,13 +2286,13 @@
         <v>2.66</v>
       </c>
       <c r="U12">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V12">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W12">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X12">
         <v>1.03</v>
@@ -2307,7 +2307,7 @@
         <v>2</v>
       </c>
       <c r="AB12">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC12">
         <v>3.34</v>
@@ -2319,10 +2319,10 @@
         <v>1.05</v>
       </c>
       <c r="AF12">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AG12">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2428,43 +2428,43 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.1</v>
+        <v>3.93</v>
       </c>
       <c r="O13">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P13">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="Q13">
-        <v>4</v>
+        <v>4.36</v>
       </c>
       <c r="R13">
+        <v>2.36</v>
+      </c>
+      <c r="S13">
+        <v>1.26</v>
+      </c>
+      <c r="T13">
+        <v>3.34</v>
+      </c>
+      <c r="U13">
         <v>2.43</v>
       </c>
-      <c r="S13">
-        <v>1.22</v>
-      </c>
-      <c r="T13">
-        <v>3.3</v>
-      </c>
-      <c r="U13">
-        <v>2.42</v>
-      </c>
       <c r="V13">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W13">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X13">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z13">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="AA13">
         <v>1.6</v>
@@ -2473,19 +2473,19 @@
         <v>2.3</v>
       </c>
       <c r="AC13">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AD13">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AE13">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF13">
         <v>1.55</v>
       </c>
       <c r="AG13">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK13">
         <v>1.21</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="O18">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="P18">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="Q18">
         <v>4.75</v>
       </c>
       <c r="R18">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="S18">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T18">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U18">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="V18">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="W18">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z18">
-        <v>4.85</v>
+        <v>4.5</v>
       </c>
       <c r="AA18">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AB18">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="AC18">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="AD18">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AE18">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF18">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AG18">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.13</v>
       </c>
       <c r="AK18">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3569,31 +3569,31 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="O20">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P20">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="Q20">
         <v>2.35</v>
       </c>
       <c r="R20">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="S20">
         <v>1.22</v>
       </c>
       <c r="T20">
-        <v>3.66</v>
+        <v>4</v>
       </c>
       <c r="U20">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V20">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W20">
         <v>1.14</v>
@@ -3602,28 +3602,28 @@
         <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z20">
-        <v>5.25</v>
+        <v>5.15</v>
       </c>
       <c r="AA20">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AB20">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="AC20">
         <v>2.2</v>
       </c>
       <c r="AD20">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AE20">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF20">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AG20">
         <v>2.7</v>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AK20">
         <v>1.67</v>
@@ -3895,19 +3895,19 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="O22">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="P22">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="Q22">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="R22">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="S22">
         <v>1.25</v>
@@ -3916,10 +3916,10 @@
         <v>3.42</v>
       </c>
       <c r="U22">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V22">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="W22">
         <v>1.14</v>
@@ -3937,7 +3937,7 @@
         <v>1.5</v>
       </c>
       <c r="AB22">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AC22">
         <v>2.25</v>
@@ -4064,10 +4064,10 @@
         <v>3.4</v>
       </c>
       <c r="P23">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="Q23">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="R23">
         <v>2.27</v>
@@ -4115,7 +4115,7 @@
         <v>1.57</v>
       </c>
       <c r="AG23">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK23">
         <v>1.79</v>
@@ -4387,10 +4387,10 @@
         <v>1.59</v>
       </c>
       <c r="O25">
-        <v>3.75</v>
+        <v>4.12</v>
       </c>
       <c r="P25">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="O26">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="P26">
-        <v>5.6</v>
+        <v>6.18</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4873,16 +4873,16 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="O28">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="P28">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="Q28">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="R28">
         <v>2.08</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="O31">
         <v>3.3</v>
@@ -5377,46 +5377,46 @@
         <v>2.32</v>
       </c>
       <c r="S31">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T31">
-        <v>2.74</v>
+        <v>2.29</v>
       </c>
       <c r="U31">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="V31">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W31">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X31">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z31">
-        <v>3.48</v>
+        <v>3.41</v>
       </c>
       <c r="AA31">
         <v>1.9</v>
       </c>
       <c r="AB31">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC31">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="AD31">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE31">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF31">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AG31">
         <v>2</v>
@@ -5435,7 +5435,7 @@
         <v>1.27</v>
       </c>
       <c r="AK31">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5851,58 +5851,58 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="O34">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P34">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="Q34">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="R34">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="S34">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="T34">
-        <v>2.31</v>
+        <v>2.57</v>
       </c>
       <c r="U34">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="V34">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W34">
         <v>1.02</v>
       </c>
       <c r="X34">
+        <v>1.04</v>
+      </c>
+      <c r="Y34">
+        <v>1.43</v>
+      </c>
+      <c r="Z34">
+        <v>2.77</v>
+      </c>
+      <c r="AA34">
+        <v>2.4</v>
+      </c>
+      <c r="AB34">
+        <v>1.53</v>
+      </c>
+      <c r="AC34">
+        <v>4.24</v>
+      </c>
+      <c r="AD34">
+        <v>1.19</v>
+      </c>
+      <c r="AE34">
         <v>1.05</v>
-      </c>
-      <c r="Y34">
-        <v>1.45</v>
-      </c>
-      <c r="Z34">
-        <v>2.67</v>
-      </c>
-      <c r="AA34">
-        <v>2.36</v>
-      </c>
-      <c r="AB34">
-        <v>1.52</v>
-      </c>
-      <c r="AC34">
-        <v>4.35</v>
-      </c>
-      <c r="AD34">
-        <v>1.18</v>
-      </c>
-      <c r="AE34">
-        <v>1.01</v>
       </c>
       <c r="AF34">
         <v>2</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK34">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O36">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="P36">
-        <v>2.9</v>
+        <v>2.68</v>
       </c>
       <c r="Q36">
         <v>3.27</v>
@@ -6192,19 +6192,19 @@
         <v>2.01</v>
       </c>
       <c r="S36">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="T36">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="U36">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="V36">
         <v>1.26</v>
       </c>
       <c r="W36">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X36">
         <v>1.04</v>
@@ -6219,7 +6219,7 @@
         <v>2.38</v>
       </c>
       <c r="AB36">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC36">
         <v>4.33</v>
@@ -6234,7 +6234,7 @@
         <v>1.92</v>
       </c>
       <c r="AG36">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.32</v>
       </c>
       <c r="AK36">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AL36">
         <v>0</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="O31">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P31">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q31">
         <v>2.25</v>
@@ -5380,7 +5380,7 @@
         <v>1.38</v>
       </c>
       <c r="T31">
-        <v>2.29</v>
+        <v>2.7</v>
       </c>
       <c r="U31">
         <v>2.78</v>
@@ -5389,34 +5389,34 @@
         <v>1.38</v>
       </c>
       <c r="W31">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z31">
-        <v>3.41</v>
+        <v>2.7</v>
       </c>
       <c r="AA31">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB31">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AC31">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="AD31">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE31">
         <v>1.06</v>
       </c>
       <c r="AF31">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AG31">
         <v>2</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5854,16 +5854,16 @@
         <v>1.95</v>
       </c>
       <c r="O34">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P34">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q34">
         <v>2.7</v>
       </c>
       <c r="R34">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="S34">
         <v>1.49</v>
@@ -5884,25 +5884,25 @@
         <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Z34">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="AA34">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AB34">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC34">
         <v>4.24</v>
       </c>
       <c r="AD34">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE34">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF34">
         <v>2</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK34">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>1.95</v>
       </c>
       <c r="O35">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="P35">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="Q35">
         <v>2.6</v>
@@ -6038,34 +6038,34 @@
         <v>3</v>
       </c>
       <c r="V35">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W35">
         <v>1.02</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y35">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z35">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AA35">
         <v>2.1</v>
       </c>
       <c r="AB35">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC35">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD35">
         <v>1.22</v>
       </c>
       <c r="AE35">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF35">
         <v>1.83</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK35">
         <v>1.77</v>
@@ -6177,49 +6177,49 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="O36">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="P36">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="Q36">
-        <v>3.27</v>
+        <v>3.19</v>
       </c>
       <c r="R36">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="S36">
         <v>1.47</v>
       </c>
       <c r="T36">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="U36">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="V36">
         <v>1.26</v>
       </c>
       <c r="W36">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X36">
         <v>1.04</v>
       </c>
       <c r="Y36">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="Z36">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AA36">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AB36">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AC36">
         <v>4.33</v>
@@ -6228,13 +6228,13 @@
         <v>1.14</v>
       </c>
       <c r="AE36">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF36">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AG36">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.32</v>
       </c>
       <c r="AK36">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="AL36">
         <v>0</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="N3">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O3">
         <v>3.4</v>
       </c>
       <c r="P3">
-        <v>3.17</v>
+        <v>3.3</v>
       </c>
       <c r="Q3">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="R3">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S3">
         <v>1.34</v>
@@ -828,19 +828,19 @@
         <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y3">
         <v>1.25</v>
       </c>
       <c r="Z3">
-        <v>3.6</v>
+        <v>3.76</v>
       </c>
       <c r="AA3">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB3">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC3">
         <v>2.92</v>
@@ -855,7 +855,7 @@
         <v>1.66</v>
       </c>
       <c r="AG3">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK3">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="P4">
         <v>2.7</v>
@@ -982,10 +982,10 @@
         <v>3.28</v>
       </c>
       <c r="U4">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V4">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W4">
         <v>1.11</v>
@@ -994,22 +994,22 @@
         <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z4">
         <v>4.75</v>
       </c>
       <c r="AA4">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AB4">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="AC4">
         <v>2.27</v>
       </c>
       <c r="AD4">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AE4">
         <v>1.24</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="AK4">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,49 +1124,49 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="O5">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="P5">
-        <v>4.82</v>
+        <v>5.31</v>
       </c>
       <c r="Q5">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="R5">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="S5">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="T5">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="U5">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="V5">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="W5">
         <v>0</v>
       </c>
       <c r="X5">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Y5">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="Z5">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AA5">
-        <v>4.75</v>
+        <v>3.85</v>
       </c>
       <c r="AB5">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1178,10 +1178,10 @@
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="AG5">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK5">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,43 +1287,43 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.58</v>
+        <v>2.9</v>
       </c>
       <c r="O6">
         <v>3.05</v>
       </c>
       <c r="P6">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="Q6">
+        <v>3.52</v>
+      </c>
+      <c r="R6">
+        <v>2.05</v>
+      </c>
+      <c r="S6">
+        <v>1.44</v>
+      </c>
+      <c r="T6">
+        <v>2.52</v>
+      </c>
+      <c r="U6">
         <v>3.2</v>
       </c>
-      <c r="R6">
-        <v>1.98</v>
-      </c>
-      <c r="S6">
-        <v>1.43</v>
-      </c>
-      <c r="T6">
-        <v>2.53</v>
-      </c>
-      <c r="U6">
-        <v>3.1</v>
-      </c>
       <c r="V6">
+        <v>1.36</v>
+      </c>
+      <c r="W6">
+        <v>1.05</v>
+      </c>
+      <c r="X6">
+        <v>1.07</v>
+      </c>
+      <c r="Y6">
         <v>1.32</v>
       </c>
-      <c r="W6">
-        <v>1.03</v>
-      </c>
-      <c r="X6">
-        <v>1.03</v>
-      </c>
-      <c r="Y6">
-        <v>1.36</v>
-      </c>
       <c r="Z6">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AA6">
         <v>2.1</v>
@@ -1332,19 +1332,19 @@
         <v>1.7</v>
       </c>
       <c r="AC6">
-        <v>3.84</v>
+        <v>3.58</v>
       </c>
       <c r="AD6">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE6">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF6">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AG6">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AK6">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.34</v>
+        <v>3.25</v>
       </c>
       <c r="O9">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P9">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1815,10 +1815,10 @@
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB9">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -1939,34 +1939,34 @@
         </is>
       </c>
       <c r="N10">
-        <v>5.3</v>
+        <v>5.27</v>
       </c>
       <c r="O10">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="P10">
         <v>1.46</v>
       </c>
       <c r="Q10">
-        <v>5.44</v>
+        <v>5.5</v>
       </c>
       <c r="R10">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="S10">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T10">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="U10">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="V10">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="W10">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X10">
         <v>1.02</v>
@@ -1975,28 +1975,28 @@
         <v>1.13</v>
       </c>
       <c r="Z10">
-        <v>5.63</v>
+        <v>5.3</v>
       </c>
       <c r="AA10">
         <v>1.45</v>
       </c>
       <c r="AB10">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="AC10">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AD10">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AE10">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF10">
         <v>1.53</v>
       </c>
       <c r="AG10">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.13</v>
+        <v>2.5</v>
       </c>
       <c r="AK10">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="O11">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P11">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="Q11">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="R11">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S11">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T11">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="U11">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V11">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
         <v>1.2</v>
       </c>
       <c r="Z11">
-        <v>3.92</v>
+        <v>3.74</v>
       </c>
       <c r="AA11">
         <v>1.8</v>
       </c>
       <c r="AB11">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AC11">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AD11">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE11">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF11">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG11">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,37 +2265,37 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="O12">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P12">
-        <v>8.35</v>
+        <v>7.39</v>
       </c>
       <c r="Q12">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="R12">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S12">
         <v>1.39</v>
       </c>
       <c r="T12">
-        <v>2.66</v>
+        <v>2.96</v>
       </c>
       <c r="U12">
         <v>2.88</v>
       </c>
       <c r="V12">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W12">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y12">
         <v>1.27</v>
@@ -2307,22 +2307,22 @@
         <v>2</v>
       </c>
       <c r="AB12">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AC12">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AD12">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE12">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AG12">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK12">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="O14">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P14">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Q14">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="R14">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="S14">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T14">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="U14">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="V14">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W14">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
         <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z14">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AA14">
         <v>1.57</v>
       </c>
       <c r="AB14">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AC14">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AD14">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AE14">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF14">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AG14">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AK14">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="O15">
         <v>3.1</v>
@@ -2763,10 +2763,10 @@
         <v>2.45</v>
       </c>
       <c r="Q15">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="R15">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S15">
         <v>1.42</v>
@@ -2787,31 +2787,31 @@
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Z15">
         <v>3.05</v>
       </c>
       <c r="AA15">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB15">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AC15">
         <v>3.34</v>
       </c>
       <c r="AD15">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE15">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF15">
         <v>1.75</v>
       </c>
       <c r="AG15">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AK15">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3249,22 +3249,22 @@
         <v>4.5</v>
       </c>
       <c r="P18">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="Q18">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="R18">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S18">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T18">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="U18">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="V18">
         <v>1.58</v>
@@ -3276,28 +3276,28 @@
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z18">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA18">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AB18">
         <v>2.4</v>
       </c>
       <c r="AC18">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="AD18">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE18">
         <v>1.18</v>
       </c>
       <c r="AF18">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG18">
         <v>2.1</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AK18">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,25 +3406,25 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="O19">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P19">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="Q19">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="R19">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="S19">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T19">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U19">
         <v>3.18</v>
@@ -3433,22 +3433,22 @@
         <v>1.28</v>
       </c>
       <c r="W19">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y19">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z19">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AA19">
         <v>2.37</v>
       </c>
       <c r="AB19">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AC19">
         <v>3.9</v>
@@ -3460,7 +3460,7 @@
         <v>1.02</v>
       </c>
       <c r="AF19">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="AG19">
         <v>1.53</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AK19">
         <v>2.31</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="O20">
+        <v>3.95</v>
+      </c>
+      <c r="P20">
+        <v>3.05</v>
+      </c>
+      <c r="Q20">
+        <v>2.53</v>
+      </c>
+      <c r="R20">
+        <v>2.42</v>
+      </c>
+      <c r="S20">
+        <v>1.21</v>
+      </c>
+      <c r="T20">
         <v>3.75</v>
       </c>
-      <c r="P20">
-        <v>2.88</v>
-      </c>
-      <c r="Q20">
-        <v>2.35</v>
-      </c>
-      <c r="R20">
-        <v>2.33</v>
-      </c>
-      <c r="S20">
-        <v>1.22</v>
-      </c>
-      <c r="T20">
-        <v>4</v>
-      </c>
       <c r="U20">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V20">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="W20">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X20">
         <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z20">
-        <v>5.15</v>
+        <v>5.6</v>
       </c>
       <c r="AA20">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AB20">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="AC20">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD20">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AE20">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF20">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AG20">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="O21">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P21">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA21">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="AB21">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="O25">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="P25">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4423,10 +4423,10 @@
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB25">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC25">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>1.4</v>
       </c>
       <c r="O26">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="P26">
-        <v>6.18</v>
+        <v>6</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -5691,13 +5691,13 @@
         <v>2.05</v>
       </c>
       <c r="O33">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="P33">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q33">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="R33">
         <v>2</v>
@@ -5706,7 +5706,7 @@
         <v>1.52</v>
       </c>
       <c r="T33">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="U33">
         <v>3.32</v>
@@ -5718,34 +5718,34 @@
         <v>1.03</v>
       </c>
       <c r="X33">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="Z33">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AA33">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AB33">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC33">
         <v>4.2</v>
       </c>
       <c r="AD33">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE33">
         <v>1.01</v>
       </c>
       <c r="AF33">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG33">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK33">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AL33">
         <v>0</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -635,31 +635,31 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O2">
-        <v>4.11</v>
+        <v>3.9</v>
       </c>
       <c r="P2">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="Q2">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R2">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="S2">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T2">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="U2">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="V2">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W2">
         <v>1.11</v>
@@ -668,47 +668,47 @@
         <v>1.02</v>
       </c>
       <c r="Y2">
+        <v>1.18</v>
+      </c>
+      <c r="Z2">
+        <v>4.1</v>
+      </c>
+      <c r="AA2">
+        <v>1.7</v>
+      </c>
+      <c r="AB2">
+        <v>2.12</v>
+      </c>
+      <c r="AC2">
+        <v>2.8</v>
+      </c>
+      <c r="AD2">
+        <v>1.4</v>
+      </c>
+      <c r="AE2">
+        <v>1.11</v>
+      </c>
+      <c r="AF2">
+        <v>1.7</v>
+      </c>
+      <c r="AG2">
+        <v>1.99</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2">
         <v>1.17</v>
       </c>
-      <c r="Z2">
-        <v>4.24</v>
-      </c>
-      <c r="AA2">
-        <v>1.66</v>
-      </c>
-      <c r="AB2">
-        <v>2.13</v>
-      </c>
-      <c r="AC2">
-        <v>2.62</v>
-      </c>
-      <c r="AD2">
-        <v>1.41</v>
-      </c>
-      <c r="AE2">
-        <v>1.12</v>
-      </c>
-      <c r="AF2">
-        <v>1.68</v>
-      </c>
-      <c r="AG2">
-        <v>2.02</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2">
-        <v>1.2</v>
-      </c>
       <c r="AK2">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1450,37 +1450,37 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O7">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q7">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R7">
-        <v>1.98</v>
+        <v>2.31</v>
       </c>
       <c r="S7">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="T7">
-        <v>2.6</v>
+        <v>3.04</v>
       </c>
       <c r="U7">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="V7">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W7">
         <v>1.09</v>
       </c>
       <c r="X7">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
         <v>1.3</v>
@@ -1489,22 +1489,22 @@
         <v>3.34</v>
       </c>
       <c r="AA7">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AB7">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC7">
         <v>2.71</v>
       </c>
       <c r="AD7">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE7">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF7">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AG7">
         <v>2</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AK7">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="O8">
-        <v>3.3</v>
+        <v>3.03</v>
       </c>
       <c r="P8">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="Q8">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="R8">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S8">
         <v>1.35</v>
@@ -1634,7 +1634,7 @@
         <v>2.9</v>
       </c>
       <c r="U8">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="V8">
         <v>1.44</v>
@@ -1646,7 +1646,7 @@
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z8">
         <v>3.58</v>
@@ -1658,19 +1658,19 @@
         <v>1.96</v>
       </c>
       <c r="AC8">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AD8">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE8">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF8">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AG8">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.28</v>
       </c>
       <c r="AK8">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="O12">
         <v>4.2</v>
@@ -2274,52 +2274,52 @@
         <v>7.39</v>
       </c>
       <c r="Q12">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="R12">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="S12">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T12">
-        <v>2.96</v>
+        <v>2.89</v>
       </c>
       <c r="U12">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="V12">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W12">
+        <v>1.02</v>
+      </c>
+      <c r="X12">
         <v>1.03</v>
       </c>
-      <c r="X12">
-        <v>1.06</v>
-      </c>
       <c r="Y12">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z12">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AA12">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB12">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AC12">
         <v>3.6</v>
       </c>
       <c r="AD12">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE12">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF12">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AG12">
         <v>1.55</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK12">
         <v>2.8</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.93</v>
+        <v>4.5</v>
       </c>
       <c r="O13">
-        <v>3.7</v>
+        <v>4.15</v>
       </c>
       <c r="P13">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q13">
-        <v>4.36</v>
+        <v>4.33</v>
       </c>
       <c r="R13">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="S13">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T13">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="U13">
-        <v>2.43</v>
+        <v>2.31</v>
       </c>
       <c r="V13">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W13">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X13">
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z13">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="AA13">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AB13">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AC13">
-        <v>2.55</v>
+        <v>2.32</v>
       </c>
       <c r="AD13">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AE13">
         <v>1.17</v>
       </c>
       <c r="AF13">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG13">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK13">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O16">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P16">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q16">
         <v>3.9</v>
       </c>
       <c r="R16">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="S16">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T16">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="U16">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V16">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="W16">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z16">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="AA16">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AB16">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AC16">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AD16">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AE16">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF16">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AG16">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="AK16">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,31 +3080,31 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="O17">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P17">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q17">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="R17">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="S17">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T17">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="U17">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="V17">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W17">
         <v>1.08</v>
@@ -3116,28 +3116,28 @@
         <v>1.19</v>
       </c>
       <c r="Z17">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="AA17">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AB17">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AC17">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AD17">
         <v>1.37</v>
       </c>
       <c r="AE17">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF17">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG17">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.26</v>
       </c>
       <c r="AK17">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="O22">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P22">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="Q22">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="R22">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="S22">
         <v>1.25</v>
       </c>
       <c r="T22">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="U22">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="V22">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W22">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X22">
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z22">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="AA22">
         <v>1.5</v>
       </c>
       <c r="AB22">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AC22">
         <v>2.25</v>
       </c>
       <c r="AD22">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AE22">
         <v>1.22</v>
       </c>
       <c r="AF22">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AG22">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="AK22">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="O23">
-        <v>3.4</v>
+        <v>3.82</v>
       </c>
       <c r="P23">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="Q23">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R23">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="S23">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T23">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="U23">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="V23">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W23">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X23">
         <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z23">
-        <v>4.2</v>
+        <v>4.55</v>
       </c>
       <c r="AA23">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AB23">
-        <v>2.16</v>
+        <v>2.29</v>
       </c>
       <c r="AC23">
-        <v>2.71</v>
+        <v>2.55</v>
       </c>
       <c r="AD23">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AE23">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF23">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG23">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK23">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,40 +4221,40 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="O24">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P24">
-        <v>4.45</v>
+        <v>4.1</v>
       </c>
       <c r="Q24">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="R24">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="S24">
         <v>1.22</v>
       </c>
       <c r="T24">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U24">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="V24">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="W24">
         <v>1.13</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z24">
         <v>5.35</v>
@@ -4263,22 +4263,22 @@
         <v>1.47</v>
       </c>
       <c r="AB24">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="AC24">
-        <v>2.22</v>
+        <v>2.09</v>
       </c>
       <c r="AD24">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AE24">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AF24">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AG24">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AK24">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="O27">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P27">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q27">
-        <v>4.05</v>
+        <v>4.45</v>
       </c>
       <c r="R27">
-        <v>2.24</v>
+        <v>2.09</v>
       </c>
       <c r="S27">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T27">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="U27">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="V27">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W27">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z27">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AA27">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AB27">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AC27">
-        <v>3.48</v>
+        <v>2.99</v>
       </c>
       <c r="AD27">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AE27">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF27">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AG27">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4876,61 +4876,61 @@
         <v>2.45</v>
       </c>
       <c r="O28">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="P28">
         <v>2.7</v>
       </c>
       <c r="Q28">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="R28">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="S28">
         <v>1.36</v>
       </c>
       <c r="T28">
-        <v>2.89</v>
+        <v>2.77</v>
       </c>
       <c r="U28">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="V28">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W28">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X28">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z28">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
       <c r="AA28">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AB28">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC28">
         <v>3.1</v>
       </c>
       <c r="AD28">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE28">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF28">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AG28">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5036,19 +5036,19 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="O29">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="P29">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="Q29">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="R29">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="S29">
         <v>1.38</v>
@@ -5063,7 +5063,7 @@
         <v>1.35</v>
       </c>
       <c r="W29">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X29">
         <v>1</v>
@@ -5078,7 +5078,7 @@
         <v>1.98</v>
       </c>
       <c r="AB29">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AC29">
         <v>3.25</v>
@@ -5087,13 +5087,13 @@
         <v>1.3</v>
       </c>
       <c r="AE29">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF29">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AG29">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK29">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5371,16 +5371,16 @@
         <v>3.75</v>
       </c>
       <c r="Q31">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R31">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S31">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T31">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="U31">
         <v>2.78</v>
@@ -5525,43 +5525,43 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="O32">
         <v>3.56</v>
       </c>
       <c r="P32">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="Q32">
-        <v>2.57</v>
+        <v>2.3</v>
       </c>
       <c r="R32">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S32">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="T32">
         <v>2.93</v>
       </c>
       <c r="U32">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="V32">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W32">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X32">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z32">
-        <v>3.54</v>
+        <v>3.84</v>
       </c>
       <c r="AA32">
         <v>1.87</v>
@@ -5570,13 +5570,13 @@
         <v>1.94</v>
       </c>
       <c r="AC32">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="AD32">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AE32">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF32">
         <v>1.73</v>
@@ -5598,7 +5598,7 @@
         <v>1.32</v>
       </c>
       <c r="AK32">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5860,43 +5860,43 @@
         <v>3.85</v>
       </c>
       <c r="Q34">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="R34">
         <v>1.83</v>
       </c>
       <c r="S34">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T34">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="U34">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="V34">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W34">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X34">
         <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z34">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="AA34">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AB34">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC34">
-        <v>4.24</v>
+        <v>4.18</v>
       </c>
       <c r="AD34">
         <v>1.2</v>
@@ -5905,10 +5905,10 @@
         <v>1.01</v>
       </c>
       <c r="AF34">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AG34">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>1.95</v>
       </c>
       <c r="O35">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="P35">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="Q35">
         <v>2.6</v>
@@ -6053,7 +6053,7 @@
         <v>2.97</v>
       </c>
       <c r="AA35">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB35">
         <v>1.75</v>
@@ -6065,7 +6065,7 @@
         <v>1.22</v>
       </c>
       <c r="AE35">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF35">
         <v>1.83</v>
@@ -6177,19 +6177,19 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="O36">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="P36">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Q36">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="R36">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S36">
         <v>1.47</v>
@@ -6198,7 +6198,7 @@
         <v>2.48</v>
       </c>
       <c r="U36">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="V36">
         <v>1.26</v>
@@ -6207,7 +6207,7 @@
         <v>1.05</v>
       </c>
       <c r="X36">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
         <v>1.45</v>
@@ -6219,13 +6219,13 @@
         <v>2.35</v>
       </c>
       <c r="AB36">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AC36">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AD36">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE36">
         <v>1.01</v>
@@ -6250,7 +6250,7 @@
         <v>1.32</v>
       </c>
       <c r="AK36">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AL36">
         <v>0</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -2446,13 +2446,13 @@
         <v>1.29</v>
       </c>
       <c r="T13">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U13">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="V13">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W13">
         <v>1.11</v>
@@ -2464,28 +2464,28 @@
         <v>1.2</v>
       </c>
       <c r="Z13">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AA13">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AB13">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="AC13">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AD13">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AE13">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF13">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG13">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -5371,25 +5371,25 @@
         <v>3.75</v>
       </c>
       <c r="Q31">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R31">
         <v>2.3</v>
       </c>
       <c r="S31">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T31">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="U31">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="V31">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W31">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X31">
         <v>1.01</v>
@@ -5398,28 +5398,28 @@
         <v>1.23</v>
       </c>
       <c r="Z31">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AA31">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AB31">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AC31">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="AD31">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE31">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF31">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG31">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK31">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5854,10 +5854,10 @@
         <v>1.95</v>
       </c>
       <c r="O34">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P34">
-        <v>3.85</v>
+        <v>3.58</v>
       </c>
       <c r="Q34">
         <v>2.61</v>
@@ -5866,16 +5866,16 @@
         <v>1.83</v>
       </c>
       <c r="S34">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="T34">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="U34">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="V34">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W34">
         <v>1.03</v>
@@ -5884,19 +5884,19 @@
         <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z34">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="AA34">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AB34">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC34">
-        <v>4.18</v>
+        <v>4.29</v>
       </c>
       <c r="AD34">
         <v>1.2</v>
@@ -5905,10 +5905,10 @@
         <v>1.01</v>
       </c>
       <c r="AF34">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AG34">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK34">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6177,16 +6177,16 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="O36">
-        <v>2.87</v>
+        <v>2.98</v>
       </c>
       <c r="P36">
         <v>3</v>
       </c>
       <c r="Q36">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="R36">
         <v>2.04</v>
@@ -6195,7 +6195,7 @@
         <v>1.47</v>
       </c>
       <c r="T36">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="U36">
         <v>3.2</v>
@@ -6216,7 +6216,7 @@
         <v>2.7</v>
       </c>
       <c r="AA36">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="AB36">
         <v>1.55</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -828,19 +828,19 @@
         <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z3">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="AA3">
         <v>1.81</v>
       </c>
       <c r="AB3">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AC3">
         <v>2.92</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK3">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -2600,10 +2600,10 @@
         <v>6</v>
       </c>
       <c r="Q14">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R14">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S14">
         <v>1.28</v>
@@ -2612,10 +2612,10 @@
         <v>3.15</v>
       </c>
       <c r="U14">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="V14">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W14">
         <v>1.08</v>
@@ -2624,22 +2624,22 @@
         <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z14">
-        <v>3.9</v>
+        <v>4.16</v>
       </c>
       <c r="AA14">
         <v>1.57</v>
       </c>
       <c r="AB14">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AC14">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AD14">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AE14">
         <v>1.13</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AK14">
-        <v>2.63</v>
+        <v>2.76</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O15">
         <v>3.1</v>
       </c>
       <c r="P15">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q15">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="R15">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S15">
         <v>1.42</v>
       </c>
       <c r="T15">
-        <v>2.56</v>
+        <v>2.79</v>
       </c>
       <c r="U15">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V15">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W15">
         <v>1.03</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z15">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AA15">
         <v>2.1</v>
       </c>
       <c r="AB15">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AC15">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AD15">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE15">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF15">
         <v>1.75</v>
       </c>
       <c r="AG15">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.37</v>
+        <v>1.92</v>
       </c>
       <c r="O22">
-        <v>3.4</v>
+        <v>3.82</v>
       </c>
       <c r="P22">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="Q22">
-        <v>2.91</v>
+        <v>2.5</v>
       </c>
       <c r="R22">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="S22">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T22">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="U22">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="V22">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="W22">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y22">
         <v>1.13</v>
       </c>
       <c r="Z22">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="AA22">
+        <v>1.6</v>
+      </c>
+      <c r="AB22">
+        <v>2.29</v>
+      </c>
+      <c r="AC22">
+        <v>2.55</v>
+      </c>
+      <c r="AD22">
+        <v>1.46</v>
+      </c>
+      <c r="AE22">
+        <v>1.14</v>
+      </c>
+      <c r="AF22">
         <v>1.5</v>
       </c>
-      <c r="AB22">
-        <v>2.7</v>
-      </c>
-      <c r="AC22">
-        <v>2.25</v>
-      </c>
-      <c r="AD22">
-        <v>1.57</v>
-      </c>
-      <c r="AE22">
-        <v>1.22</v>
-      </c>
-      <c r="AF22">
-        <v>1.41</v>
-      </c>
       <c r="AG22">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="AK22">
-        <v>1.49</v>
+        <v>1.82</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.92</v>
+        <v>2.37</v>
       </c>
       <c r="O23">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="P23">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q23">
-        <v>2.5</v>
+        <v>2.91</v>
       </c>
       <c r="R23">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="S23">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T23">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="U23">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="V23">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="W23">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
         <v>1.13</v>
       </c>
       <c r="Z23">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="AA23">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AB23">
-        <v>2.29</v>
+        <v>2.7</v>
       </c>
       <c r="AC23">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AD23">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AE23">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AF23">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AG23">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="AK23">
-        <v>1.82</v>
+        <v>1.49</v>
       </c>
       <c r="AL23">
         <v>0</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -631,35 +631,35 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="O2">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P2">
-        <v>4.6</v>
+        <v>6.31</v>
       </c>
       <c r="Q2">
         <v>2</v>
       </c>
       <c r="R2">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="S2">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T2">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="U2">
         <v>2.45</v>
       </c>
       <c r="V2">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W2">
         <v>1.11</v>
@@ -668,35 +668,35 @@
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z2">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA2">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB2">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AC2">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="AD2">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE2">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF2">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AG2">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -705,37 +705,37 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AK2">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -775,26 +775,26 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -859,12 +859,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9", "16", "25", "65"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+7", "89"]</t>
         </is>
       </c>
       <c r="AJ3">
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -950,42 +950,42 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
         <v>2.14</v>
       </c>
       <c r="O4">
-        <v>3.18</v>
+        <v>3.53</v>
       </c>
       <c r="P4">
-        <v>2.7</v>
+        <v>2.32</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
       </c>
       <c r="R4">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S4">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T4">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="U4">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="V4">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W4">
         <v>1.11</v>
@@ -997,19 +997,19 @@
         <v>1.16</v>
       </c>
       <c r="Z4">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AA4">
         <v>1.51</v>
       </c>
       <c r="AB4">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="AC4">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AD4">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AE4">
         <v>1.24</v>
@@ -1018,11 +1018,11 @@
         <v>1.44</v>
       </c>
       <c r="AG4">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["82"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="AK4">
         <v>1.49</v>
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>28</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1116,88 +1116,88 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>1.82</v>
+        <v>1.99</v>
       </c>
       <c r="O5">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="P5">
-        <v>5.31</v>
+        <v>4.25</v>
       </c>
       <c r="Q5">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="R5">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="S5">
         <v>1.75</v>
       </c>
       <c r="T5">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="U5">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="V5">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
+        <v>1.14</v>
+      </c>
+      <c r="Y5">
+        <v>1.89</v>
+      </c>
+      <c r="Z5">
+        <v>1.81</v>
+      </c>
+      <c r="AA5">
+        <v>3.68</v>
+      </c>
+      <c r="AB5">
         <v>1.2</v>
       </c>
-      <c r="Y5">
-        <v>1.93</v>
-      </c>
-      <c r="Z5">
-        <v>1.8</v>
-      </c>
-      <c r="AA5">
-        <v>3.85</v>
-      </c>
-      <c r="AB5">
-        <v>1.22</v>
-      </c>
       <c r="AC5">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF5">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="AG5">
         <v>1.3</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53"]</t>
         </is>
       </c>
       <c r="AJ5">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK5">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="O6">
         <v>3.05</v>
@@ -1296,7 +1296,7 @@
         <v>2.62</v>
       </c>
       <c r="Q6">
-        <v>3.52</v>
+        <v>3.35</v>
       </c>
       <c r="R6">
         <v>2.05</v>
@@ -1305,25 +1305,25 @@
         <v>1.44</v>
       </c>
       <c r="T6">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="U6">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V6">
         <v>1.36</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X6">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y6">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z6">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA6">
         <v>2.1</v>
@@ -1332,7 +1332,7 @@
         <v>1.7</v>
       </c>
       <c r="AC6">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AD6">
         <v>1.25</v>
@@ -1341,10 +1341,10 @@
         <v>1.07</v>
       </c>
       <c r="AF6">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG6">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AK6">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="O9">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P9">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA9">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB9">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1945,58 +1945,58 @@
         <v>4.35</v>
       </c>
       <c r="P10">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="Q10">
-        <v>5.5</v>
+        <v>5.39</v>
       </c>
       <c r="R10">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="S10">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T10">
         <v>3.9</v>
       </c>
       <c r="U10">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="V10">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W10">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
         <v>1.13</v>
       </c>
       <c r="Z10">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AA10">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AB10">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AC10">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AD10">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AE10">
         <v>1.25</v>
       </c>
       <c r="AF10">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG10">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>2.5</v>
+        <v>1.14</v>
       </c>
       <c r="AK10">
         <v>1.08</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="O11">
         <v>3.6</v>
       </c>
       <c r="P11">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q11">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="R11">
         <v>2.25</v>
       </c>
       <c r="S11">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T11">
-        <v>2.85</v>
+        <v>3.08</v>
       </c>
       <c r="U11">
         <v>2.5</v>
       </c>
       <c r="V11">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z11">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="AA11">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB11">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AC11">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AD11">
         <v>1.38</v>
       </c>
       <c r="AE11">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF11">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG11">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK11">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2268,61 +2268,61 @@
         <v>1.36</v>
       </c>
       <c r="O12">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P12">
-        <v>7.39</v>
+        <v>6.5</v>
       </c>
       <c r="Q12">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R12">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="S12">
         <v>1.41</v>
       </c>
       <c r="T12">
-        <v>2.89</v>
+        <v>2.59</v>
       </c>
       <c r="U12">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="V12">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W12">
         <v>1.02</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z12">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="AA12">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB12">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC12">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AD12">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AE12">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF12">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="AG12">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.15</v>
       </c>
       <c r="AK12">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.43</v>
+        <v>2.3</v>
       </c>
       <c r="O14">
-        <v>4.4</v>
+        <v>3.02</v>
       </c>
       <c r="P14">
-        <v>6</v>
+        <v>2.85</v>
       </c>
       <c r="Q14">
-        <v>1.86</v>
+        <v>3.39</v>
       </c>
       <c r="R14">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="S14">
+        <v>1.42</v>
+      </c>
+      <c r="T14">
+        <v>2.79</v>
+      </c>
+      <c r="U14">
+        <v>2.88</v>
+      </c>
+      <c r="V14">
+        <v>1.34</v>
+      </c>
+      <c r="W14">
+        <v>1.05</v>
+      </c>
+      <c r="X14">
+        <v>1.02</v>
+      </c>
+      <c r="Y14">
         <v>1.28</v>
       </c>
-      <c r="T14">
-        <v>3.15</v>
-      </c>
-      <c r="U14">
-        <v>2.44</v>
-      </c>
-      <c r="V14">
-        <v>1.5</v>
-      </c>
-      <c r="W14">
-        <v>1.08</v>
-      </c>
-      <c r="X14">
-        <v>1.03</v>
-      </c>
-      <c r="Y14">
-        <v>1.23</v>
-      </c>
       <c r="Z14">
-        <v>4.16</v>
+        <v>3.08</v>
       </c>
       <c r="AA14">
-        <v>1.57</v>
+        <v>1.96</v>
       </c>
       <c r="AB14">
-        <v>2.09</v>
+        <v>1.75</v>
       </c>
       <c r="AC14">
-        <v>2.59</v>
+        <v>3.28</v>
       </c>
       <c r="AD14">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AE14">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF14">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AG14">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>2.76</v>
+        <v>1.4</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.5</v>
+        <v>1.45</v>
       </c>
       <c r="O15">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="P15">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="Q15">
-        <v>3.26</v>
+        <v>1.82</v>
       </c>
       <c r="R15">
-        <v>1.95</v>
+        <v>2.48</v>
       </c>
       <c r="S15">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="T15">
-        <v>2.79</v>
+        <v>3.34</v>
       </c>
       <c r="U15">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
       <c r="V15">
-        <v>1.34</v>
+        <v>1.56</v>
       </c>
       <c r="W15">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="Z15">
-        <v>3.08</v>
+        <v>4.5</v>
       </c>
       <c r="AA15">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AB15">
-        <v>1.8</v>
+        <v>2.27</v>
       </c>
       <c r="AC15">
-        <v>3.28</v>
+        <v>2.35</v>
       </c>
       <c r="AD15">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="AE15">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AF15">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG15">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK15">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="O18">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="P18">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="Q18">
         <v>5</v>
       </c>
       <c r="R18">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="S18">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T18">
-        <v>3.34</v>
+        <v>4.5</v>
       </c>
       <c r="U18">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="V18">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="W18">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
+        <v>1.12</v>
+      </c>
+      <c r="Z18">
+        <v>6.38</v>
+      </c>
+      <c r="AA18">
+        <v>1.47</v>
+      </c>
+      <c r="AB18">
+        <v>3.02</v>
+      </c>
+      <c r="AC18">
+        <v>2.16</v>
+      </c>
+      <c r="AD18">
+        <v>1.78</v>
+      </c>
+      <c r="AE18">
+        <v>1.33</v>
+      </c>
+      <c r="AF18">
+        <v>1.52</v>
+      </c>
+      <c r="AG18">
+        <v>2.34</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
         <v>1.15</v>
       </c>
-      <c r="Z18">
-        <v>5</v>
-      </c>
-      <c r="AA18">
-        <v>1.56</v>
-      </c>
-      <c r="AB18">
-        <v>2.4</v>
-      </c>
-      <c r="AC18">
-        <v>2.3</v>
-      </c>
-      <c r="AD18">
-        <v>1.53</v>
-      </c>
-      <c r="AE18">
-        <v>1.18</v>
-      </c>
-      <c r="AF18">
-        <v>1.64</v>
-      </c>
-      <c r="AG18">
-        <v>2.1</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.18</v>
-      </c>
       <c r="AK18">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,25 +3406,25 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="O19">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P19">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="Q19">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R19">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="S19">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="T19">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="U19">
         <v>3.18</v>
@@ -3433,37 +3433,37 @@
         <v>1.28</v>
       </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
         <v>1.07</v>
       </c>
       <c r="Y19">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z19">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AA19">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AB19">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AC19">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AD19">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE19">
         <v>1.02</v>
       </c>
       <c r="AF19">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AG19">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AK19">
         <v>2.31</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="O20">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="P20">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="Q20">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="R20">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="S20">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T20">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="U20">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V20">
+        <v>1.79</v>
+      </c>
+      <c r="W20">
+        <v>1.14</v>
+      </c>
+      <c r="X20">
+        <v>1.01</v>
+      </c>
+      <c r="Y20">
+        <v>1.07</v>
+      </c>
+      <c r="Z20">
+        <v>6.46</v>
+      </c>
+      <c r="AA20">
+        <v>1.36</v>
+      </c>
+      <c r="AB20">
+        <v>2.72</v>
+      </c>
+      <c r="AC20">
+        <v>2.08</v>
+      </c>
+      <c r="AD20">
         <v>1.77</v>
       </c>
-      <c r="W20">
-        <v>1.16</v>
-      </c>
-      <c r="X20">
-        <v>1.02</v>
-      </c>
-      <c r="Y20">
-        <v>1.08</v>
-      </c>
-      <c r="Z20">
-        <v>5.6</v>
-      </c>
-      <c r="AA20">
-        <v>1.45</v>
-      </c>
-      <c r="AB20">
-        <v>2.7</v>
-      </c>
-      <c r="AC20">
-        <v>2.1</v>
-      </c>
-      <c r="AD20">
-        <v>1.7</v>
-      </c>
       <c r="AE20">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AF20">
         <v>1.38</v>
       </c>
       <c r="AG20">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK20">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3735,61 +3735,61 @@
         <v>1.51</v>
       </c>
       <c r="O21">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P21">
-        <v>4.4</v>
+        <v>5.75</v>
       </c>
       <c r="Q21">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="R21">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="S21">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="T21">
-        <v>2.79</v>
+        <v>2.56</v>
       </c>
       <c r="U21">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V21">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W21">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z21">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="AA21">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="AB21">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC21">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="AD21">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AE21">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF21">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AG21">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK21">
         <v>2.4</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="O25">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P25">
-        <v>5</v>
+        <v>4.83</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4423,10 +4423,10 @@
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AB25">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AC25">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>1.4</v>
       </c>
       <c r="O26">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="P26">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB26">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -5688,19 +5688,19 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="O33">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="P33">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q33">
-        <v>2.86</v>
+        <v>3.36</v>
       </c>
       <c r="R33">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S33">
         <v>1.52</v>
@@ -5721,7 +5721,7 @@
         <v>1.04</v>
       </c>
       <c r="Y33">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Z33">
         <v>2.62</v>
@@ -5730,10 +5730,10 @@
         <v>2.29</v>
       </c>
       <c r="AB33">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AC33">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AD33">
         <v>1.15</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK33">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AL33">
         <v>0</v>

--- a/jogos_2026-09-03.xlsx
+++ b/jogos_2026-09-03.xlsx
@@ -1264,26 +1264,26 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "57"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14", "88"]</t>
         </is>
       </c>
       <c r="AJ6">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1430,84 +1430,84 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="O7">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P7">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="Q7">
         <v>2.2</v>
       </c>
       <c r="R7">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="S7">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="U7">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V7">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W7">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z7">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="AA7">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AB7">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC7">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="AD7">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE7">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF7">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG7">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1516,41 +1516,41 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "76", "89"]</t>
         </is>
       </c>
       <c r="AJ7">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK7">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1590,130 +1590,130 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
-        <v>2.13</v>
+        <v>2.51</v>
       </c>
       <c r="O8">
-        <v>3.03</v>
+        <v>3.2</v>
       </c>
       <c r="P8">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="Q8">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="R8">
         <v>2.25</v>
       </c>
       <c r="S8">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="T8">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="U8">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V8">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z8">
-        <v>3.58</v>
+        <v>4.78</v>
       </c>
       <c r="AA8">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB8">
-        <v>1.96</v>
+        <v>2.09</v>
       </c>
       <c r="AC8">
+        <v>2.59</v>
+      </c>
+      <c r="AD8">
+        <v>1.4</v>
+      </c>
+      <c r="AE8">
+        <v>1.11</v>
+      </c>
+      <c r="AF8">
+        <v>1.57</v>
+      </c>
+      <c r="AG8">
+        <v>2.3</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>["79"]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>["6", "34"]</t>
+        </is>
+      </c>
+      <c r="AJ8">
+        <v>1.29</v>
+      </c>
+      <c r="AK8">
+        <v>1.57</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
         <v>3</v>
       </c>
-      <c r="AD8">
-        <v>1.33</v>
-      </c>
-      <c r="AE8">
-        <v>1.1</v>
-      </c>
-      <c r="AF8">
-        <v>1.68</v>
-      </c>
-      <c r="AG8">
-        <v>2.15</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
+      <c r="AN8">
+        <v>3</v>
+      </c>
+      <c r="AO8">
+        <v>12</v>
+      </c>
+      <c r="AP8">
+        <v>10</v>
+      </c>
+      <c r="AQ8">
+        <v>1.48</v>
+      </c>
+      <c r="AR8">
         <v>1.28</v>
       </c>
-      <c r="AK8">
-        <v>1.58</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>-1</v>
-      </c>
-      <c r="AN8">
-        <v>-1</v>
-      </c>
-      <c r="AO8">
-        <v>-1</v>
-      </c>
-      <c r="AP8">
-        <v>-1</v>
-      </c>
-      <c r="AQ8">
-        <v>0</v>
-      </c>
-      <c r="AR8">
-        <v>0</v>
-      </c>
       <c r="AS8">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1753,13 +1753,13 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -1855,28 +1855,28 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1919,23 +1919,23 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45", "77"]</t>
         </is>
       </c>
       <c r="AJ10">
@@ -2018,28 +2018,28 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2079,13 +2079,13 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["37", "39", "45"]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -2181,28 +2181,28 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -2254,14 +2254,14 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["87"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
@@ -2344,28 +2344,28 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -2420,39 +2420,39 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
+        <v>4.68</v>
+      </c>
+      <c r="O13">
+        <v>4.1</v>
+      </c>
+      <c r="P13">
+        <v>1.61</v>
+      </c>
+      <c r="Q13">
         <v>4.5</v>
       </c>
-      <c r="O13">
-        <v>4.15</v>
-      </c>
-      <c r="P13">
-        <v>1.68</v>
-      </c>
-      <c r="Q13">
-        <v>4.33</v>
-      </c>
       <c r="R13">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="S13">
         <v>1.29</v>
       </c>
       <c r="T13">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U13">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="V13">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W13">
         <v>1.11</v>
@@ -2461,25 +2461,25 @@
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z13">
-        <v>4.6</v>
+        <v>4.52</v>
       </c>
       <c r="AA13">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AB13">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="AC13">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AD13">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AE13">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF13">
         <v>1.58</v>
@@ -2494,41 +2494,41 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["60", "64"]</t>
         </is>
       </c>
       <c r="AJ13">
         <v>1.18</v>
       </c>
       <c r="AK13">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
@@ -2670,28 +2670,28 @@
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2731,26 +2731,26 @@
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45", "58", "67", "77"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
@@ -2833,28 +2833,28 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2897,84 +2897,84 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
         <v>3.75</v>
       </c>
       <c r="O16">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P16">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q16">
-        <v>3.9</v>
+        <v>4.56</v>
       </c>
       <c r="R16">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="S16">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="T16">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="U16">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="V16">
+        <v>1.58</v>
+      </c>
+      <c r="W16">
+        <v>1.14</v>
+      </c>
+      <c r="X16">
+        <v>1.02</v>
+      </c>
+      <c r="Y16">
+        <v>1.16</v>
+      </c>
+      <c r="Z16">
+        <v>4.6</v>
+      </c>
+      <c r="AA16">
+        <v>1.49</v>
+      </c>
+      <c r="AB16">
+        <v>2.4</v>
+      </c>
+      <c r="AC16">
+        <v>2.38</v>
+      </c>
+      <c r="AD16">
         <v>1.56</v>
       </c>
-      <c r="W16">
-        <v>1.11</v>
-      </c>
-      <c r="X16">
-        <v>1.03</v>
-      </c>
-      <c r="Y16">
-        <v>1.14</v>
-      </c>
-      <c r="Z16">
-        <v>4.5</v>
-      </c>
-      <c r="AA16">
-        <v>1.51</v>
-      </c>
-      <c r="AB16">
-        <v>2.35</v>
-      </c>
-      <c r="AC16">
-        <v>2.35</v>
-      </c>
-      <c r="AD16">
-        <v>1.55</v>
-      </c>
       <c r="AE16">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF16">
         <v>1.53</v>
       </c>
       <c r="AG16">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2983,41 +2983,41 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27", "70", "72"]</t>
         </is>
       </c>
       <c r="AJ16">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AK16">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AL16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3057,78 +3057,78 @@
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="O17">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P17">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="Q17">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="R17">
         <v>2.18</v>
       </c>
       <c r="S17">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T17">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="U17">
-        <v>2.57</v>
+        <v>2.49</v>
       </c>
       <c r="V17">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="W17">
         <v>1.08</v>
       </c>
       <c r="X17">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
         <v>1.19</v>
       </c>
       <c r="Z17">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="AA17">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AB17">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AC17">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AD17">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AE17">
         <v>1.17</v>
@@ -3137,50 +3137,50 @@
         <v>1.57</v>
       </c>
       <c r="AG17">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
+          <t>["17", "73", "82"]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ17">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK17">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -3235,11 +3235,11 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51", "58"]</t>
         </is>
       </c>
       <c r="AJ18">
@@ -3322,28 +3322,28 @@
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -3398,11 +3398,11 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["78"]</t>
         </is>
       </c>
       <c r="AJ19">
@@ -3485,28 +3485,28 @@
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3546,13 +3546,13 @@
         </is>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8", "31"]</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
@@ -3648,28 +3648,28 @@
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3709,13 +3709,13 @@
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9", "18"]</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
@@ -3811,28 +3811,28 @@
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -3895,61 +3895,61 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="O22">
-        <v>3.82</v>
+        <v>3.52</v>
       </c>
       <c r="P22">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="Q22">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="R22">
+        <v>2.29</v>
+      </c>
+      <c r="S22">
+        <v>1.27</v>
+      </c>
+      <c r="T22">
+        <v>3.4</v>
+      </c>
+      <c r="U22">
         <v>2.33</v>
-      </c>
-      <c r="S22">
-        <v>1.3</v>
-      </c>
-      <c r="T22">
-        <v>3.2</v>
-      </c>
-      <c r="U22">
-        <v>2.38</v>
       </c>
       <c r="V22">
         <v>1.53</v>
       </c>
       <c r="W22">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X22">
         <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z22">
-        <v>4.55</v>
+        <v>4.15</v>
       </c>
       <c r="AA22">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AB22">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="AC22">
-        <v>2.55</v>
+        <v>2.78</v>
       </c>
       <c r="AD22">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AE22">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF22">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG22">
         <v>2.37</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK22">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,25 +4058,25 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.37</v>
+        <v>2.72</v>
       </c>
       <c r="O23">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="P23">
-        <v>2.6</v>
+        <v>2.22</v>
       </c>
       <c r="Q23">
-        <v>2.91</v>
+        <v>3.18</v>
       </c>
       <c r="R23">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S23">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T23">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U23">
         <v>2.15</v>
@@ -4085,37 +4085,37 @@
         <v>1.62</v>
       </c>
       <c r="W23">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X23">
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z23">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="AA23">
         <v>1.5</v>
       </c>
       <c r="AB23">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC23">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD23">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE23">
         <v>1.22</v>
       </c>
       <c r="AF23">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG23">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AK23">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="O24">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P24">
-        <v>4.1</v>
+        <v>4.51</v>
       </c>
       <c r="Q24">
         <v>2.1</v>
       </c>
       <c r="R24">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="S24">
         <v>1.22</v>
       </c>
       <c r="T24">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U24">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V24">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W24">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z24">
-        <v>5.35</v>
+        <v>6</v>
       </c>
       <c r="AA24">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AB24">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AC24">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AD24">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="AE24">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AF24">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG24">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK24">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4361,7 +4361,7 @@
         </is>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -4373,14 +4373,14 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N25">
@@ -4445,14 +4445,14 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
+          <t>["46"]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ25">
         <v>0</v>
       </c>
@@ -4463,28 +4463,28 @@
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN25">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO25">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
@@ -4524,13 +4524,13 @@
         </is>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26">
         <v>0</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N26">
@@ -4608,14 +4608,14 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
+          <t>["43"]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ26">
         <v>0</v>
       </c>
@@ -4626,28 +4626,28 @@
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN26">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO26">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
@@ -4710,19 +4710,19 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="O27">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P27">
+        <v>1.89</v>
+      </c>
+      <c r="Q27">
+        <v>4.55</v>
+      </c>
+      <c r="R27">
         <v>2.05</v>
-      </c>
-      <c r="Q27">
-        <v>4.45</v>
-      </c>
-      <c r="R27">
-        <v>2.09</v>
       </c>
       <c r="S27">
         <v>1.42</v>
@@ -4731,43 +4731,43 @@
         <v>2.85</v>
       </c>
       <c r="U27">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="V27">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W27">
         <v>1.07</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y27">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z27">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="AA27">
+        <v>1.96</v>
+      </c>
+      <c r="AB27">
         <v>1.98</v>
       </c>
-      <c r="AB27">
-        <v>1.96</v>
-      </c>
       <c r="AC27">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="AD27">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AE27">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF27">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG27">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4850,130 +4850,130 @@
         </is>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N28">
         <v>2.45</v>
       </c>
       <c r="O28">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
         <v>2.7</v>
       </c>
       <c r="Q28">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="R28">
-        <v>2.32</v>
+        <v>2.43</v>
       </c>
       <c r="S28">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T28">
-        <v>2.77</v>
+        <v>3.15</v>
       </c>
       <c r="U28">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="V28">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="W28">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X28">
         <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="Z28">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA28">
         <v>1.86</v>
       </c>
       <c r="AB28">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AC28">
-        <v>3.1</v>
+        <v>2.54</v>
       </c>
       <c r="AD28">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AE28">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AF28">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AG28">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51"]</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "43", "66"]</t>
         </is>
       </c>
       <c r="AJ28">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK28">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AL28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO28">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP28">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
@@ -5013,13 +5013,13 @@
         </is>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -5028,24 +5028,24 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N29">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="O29">
+        <v>3.1</v>
+      </c>
+      <c r="P29">
         <v>3.45</v>
       </c>
-      <c r="P29">
-        <v>3.64</v>
-      </c>
       <c r="Q29">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="R29">
         <v>2.04</v>
@@ -5063,7 +5063,7 @@
         <v>1.35</v>
       </c>
       <c r="W29">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
         <v>1</v>
@@ -5075,7 +5075,7 @@
         <v>3.2</v>
       </c>
       <c r="AA29">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AB29">
         <v>1.77</v>
@@ -5084,7 +5084,7 @@
         <v>3.25</v>
       </c>
       <c r="AD29">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE29">
         <v>1.05</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+5"]</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["65"]</t>
         </is>
       </c>
       <c r="AJ29">
@@ -5115,28 +5115,28 @@
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN29">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO29">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="O31">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P31">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="Q31">
+        <v>2.32</v>
+      </c>
+      <c r="R31">
         <v>2.28</v>
       </c>
-      <c r="R31">
-        <v>2.3</v>
-      </c>
       <c r="S31">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T31">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="U31">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="V31">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="W31">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X31">
         <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z31">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AA31">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AB31">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AC31">
-        <v>3.38</v>
+        <v>3.54</v>
       </c>
       <c r="AD31">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE31">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF31">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG31">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK31">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="O32">
-        <v>3.56</v>
+        <v>3.52</v>
       </c>
       <c r="P32">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="Q32">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="R32">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="S32">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T32">
-        <v>2.93</v>
+        <v>3.02</v>
       </c>
       <c r="U32">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="V32">
         <v>1.43</v>
       </c>
       <c r="W32">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z32">
-        <v>3.84</v>
+        <v>3.3</v>
       </c>
       <c r="AA32">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AB32">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AC32">
-        <v>3.25</v>
+        <v>2.83</v>
       </c>
       <c r="AD32">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AE32">
         <v>1.08</v>
       </c>
       <c r="AF32">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG32">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AK32">
         <v>1.9</v>
@@ -5703,25 +5703,25 @@
         <v>1.91</v>
       </c>
       <c r="S33">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="T33">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="U33">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="V33">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W33">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X33">
         <v>1.04</v>
       </c>
       <c r="Y33">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z33">
         <v>2.62</v>
@@ -5736,16 +5736,16 @@
         <v>4.5</v>
       </c>
       <c r="AD33">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE33">
         <v>1.01</v>
       </c>
       <c r="AF33">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG33">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK33">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="O34">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P34">
-        <v>3.58</v>
+        <v>3.33</v>
       </c>
       <c r="Q34">
         <v>2.61</v>
@@ -5866,49 +5866,49 @@
         <v>1.83</v>
       </c>
       <c r="S34">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="T34">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="U34">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="V34">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="W34">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X34">
         <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z34">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="AA34">
-        <v>2.32</v>
+        <v>1.99</v>
       </c>
       <c r="AB34">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AC34">
         <v>4.29</v>
       </c>
       <c r="AD34">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AE34">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF34">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG34">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AK34">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,31 +6014,31 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="O35">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="P35">
-        <v>3.18</v>
+        <v>4.1</v>
       </c>
       <c r="Q35">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="R35">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S35">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T35">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U35">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V35">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W35">
         <v>1.02</v>
@@ -6047,19 +6047,19 @@
         <v>1.04</v>
       </c>
       <c r="Y35">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="Z35">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AA35">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB35">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AC35">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AD35">
         <v>1.22</v>
@@ -6087,7 +6087,7 @@
         <v>1.3</v>
       </c>
       <c r="AK35">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>2.25</v>
       </c>
       <c r="O36">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="P36">
         <v>3</v>
       </c>
       <c r="Q36">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="R36">
         <v>2.04</v>
@@ -6195,37 +6195,37 @@
         <v>1.47</v>
       </c>
       <c r="T36">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="U36">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V36">
         <v>1.26</v>
       </c>
       <c r="W36">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y36">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="Z36">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AA36">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AB36">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AC36">
         <v>4.3</v>
       </c>
       <c r="AD36">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE36">
         <v>1.01</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AL36">
         <v>0</v>
